--- a/System Scanner/test_report.xlsx
+++ b/System Scanner/test_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="300">
   <si>
     <t>Finding ID</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>d815f6b5</t>
+    <t>080b3e27</t>
   </si>
   <si>
     <t>SystemScanner</t>
@@ -53,28 +53,28 @@
     <t>INFO</t>
   </si>
   <si>
-    <t>2026-06-21T19:39:23.375933</t>
-  </si>
-  <si>
-    <t>915fe6cf</t>
+    <t>2026-06-21T20:05:34.236219</t>
+  </si>
+  <si>
+    <t>073e52b8</t>
   </si>
   <si>
     <t>GPU Detected: NVIDIA GeForce GTX 1650</t>
   </si>
   <si>
-    <t>2026-06-21T19:39:23.444614</t>
-  </si>
-  <si>
-    <t>71219d96</t>
+    <t>2026-06-21T20:05:35.287632</t>
+  </si>
+  <si>
+    <t>3c14a8ab</t>
   </si>
   <si>
     <t>Microsoft Copilot — Registry Configuration Detected</t>
   </si>
   <si>
-    <t>2026-06-21T19:39:23.452685</t>
-  </si>
-  <si>
-    <t>edb2b1d0</t>
+    <t>2026-06-21T20:05:35.441495</t>
+  </si>
+  <si>
+    <t>29e244bb</t>
   </si>
   <si>
     <t>APIScanner</t>
@@ -86,67 +86,580 @@
     <t>HIGH</t>
   </si>
   <si>
-    <t>2026-06-21T19:39:23.383375</t>
-  </si>
-  <si>
-    <t>3c5f460e</t>
-  </si>
-  <si>
-    <t>2026-06-21T19:39:23.383621</t>
-  </si>
-  <si>
-    <t>44d37614</t>
+    <t>2026-06-21T20:05:35.451316</t>
+  </si>
+  <si>
+    <t>affa9304</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.451456</t>
+  </si>
+  <si>
+    <t>1abec80e</t>
   </si>
   <si>
     <t>Exposed Generic API Key/Token</t>
   </si>
   <si>
-    <t>2026-06-21T19:39:23.384040</t>
-  </si>
-  <si>
-    <t>7f866514</t>
+    <t>2026-06-21T20:05:35.451700</t>
+  </si>
+  <si>
+    <t>60f56a0e</t>
   </si>
   <si>
     <t>Exposed AWS Access Key ID</t>
   </si>
   <si>
-    <t>2026-06-21T19:39:23.384083</t>
-  </si>
-  <si>
-    <t>1c610945</t>
-  </si>
-  <si>
-    <t>2026-06-21T19:39:23.384504</t>
-  </si>
-  <si>
-    <t>3edc50f9</t>
+    <t>2026-06-21T20:05:35.451720</t>
+  </si>
+  <si>
+    <t>cd10ee3f</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.452002</t>
+  </si>
+  <si>
+    <t>aa383033</t>
   </si>
   <si>
     <t>Environment Variable: ANTIGRAVITY_CSRF_TOKEN</t>
   </si>
   <si>
-    <t>2026-06-21T19:39:23.449716</t>
-  </si>
-  <si>
-    <t>b5ee97ac</t>
+    <t>2026-06-21T20:05:35.537861</t>
+  </si>
+  <si>
+    <t>599e4051</t>
   </si>
   <si>
     <t>Environment Variable: GEMINI_API_KEY</t>
   </si>
   <si>
-    <t>2026-06-21T19:39:23.449778</t>
-  </si>
-  <si>
-    <t>9725b652</t>
+    <t>2026-06-21T20:05:35.538078</t>
+  </si>
+  <si>
+    <t>7b980b0c</t>
   </si>
   <si>
     <t>LicenseScanner</t>
   </si>
   <si>
+    <t>Code Snippet: GPL Mention</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:33.569992</t>
+  </si>
+  <si>
+    <t>c66f5dcf</t>
+  </si>
+  <si>
+    <t>Code Snippet: LGPL Mention</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:33.637836</t>
+  </si>
+  <si>
+    <t>9f767bbe</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:33.640232</t>
+  </si>
+  <si>
+    <t>7f7c6c1d</t>
+  </si>
+  <si>
+    <t>Code Snippet: AGPL Mention</t>
+  </si>
+  <si>
+    <t>CRITICAL</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:33.642964</t>
+  </si>
+  <si>
+    <t>50d81190</t>
+  </si>
+  <si>
+    <t>Code Snippet: Polyform Shield Mention</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:33.644703</t>
+  </si>
+  <si>
+    <t>15c12e0f</t>
+  </si>
+  <si>
+    <t>Code Snippet: Proprietary Mention</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:33.647592</t>
+  </si>
+  <si>
+    <t>dcae47ba</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:33.650721</t>
+  </si>
+  <si>
+    <t>eafdf3ef</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:33.652913</t>
+  </si>
+  <si>
+    <t>29ef9079</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:33.655656</t>
+  </si>
+  <si>
+    <t>dec953f5</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:33.657008</t>
+  </si>
+  <si>
+    <t>59aaa94a</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:33.659975</t>
+  </si>
+  <si>
+    <t>af520d2a</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:33.663885</t>
+  </si>
+  <si>
+    <t>e0b5cf20</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:33.666262</t>
+  </si>
+  <si>
+    <t>5feaa11c</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:33.673895</t>
+  </si>
+  <si>
+    <t>6cecec93</t>
+  </si>
+  <si>
     <t>Code License: MIT Header</t>
   </si>
   <si>
-    <t>2026-06-21T19:39:22.974844</t>
+    <t>2026-06-21T20:05:35.310970</t>
+  </si>
+  <si>
+    <t>d96b4ccc</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.330538</t>
+  </si>
+  <si>
+    <t>a6b06a92</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.337802</t>
+  </si>
+  <si>
+    <t>9c6f0854</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.343039</t>
+  </si>
+  <si>
+    <t>f5340a9b</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.346724</t>
+  </si>
+  <si>
+    <t>6a0147b5</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.353028</t>
+  </si>
+  <si>
+    <t>50e687c6</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.354490</t>
+  </si>
+  <si>
+    <t>d8c5a0dc</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.359420</t>
+  </si>
+  <si>
+    <t>af1ff2a4</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.374844</t>
+  </si>
+  <si>
+    <t>b5ea1223</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.381154</t>
+  </si>
+  <si>
+    <t>b09602dd</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.402555</t>
+  </si>
+  <si>
+    <t>bbcfe9cb</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.408470</t>
+  </si>
+  <si>
+    <t>214df928</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.420092</t>
+  </si>
+  <si>
+    <t>1ac774d2</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.424097</t>
+  </si>
+  <si>
+    <t>ecd9839b</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.441710</t>
+  </si>
+  <si>
+    <t>8da932bb</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.448405</t>
+  </si>
+  <si>
+    <t>9681f970</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.450985</t>
+  </si>
+  <si>
+    <t>773fc210</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.458594</t>
+  </si>
+  <si>
+    <t>fe4e481e</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.467342</t>
+  </si>
+  <si>
+    <t>2bc87c2a</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.472228</t>
+  </si>
+  <si>
+    <t>053dd0bf</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.487198</t>
+  </si>
+  <si>
+    <t>0b239f95</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.495582</t>
+  </si>
+  <si>
+    <t>7aa4ff72</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.502423</t>
+  </si>
+  <si>
+    <t>aff12159</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.750732</t>
+  </si>
+  <si>
+    <t>6f03e516</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.751334</t>
+  </si>
+  <si>
+    <t>0855a566</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.752136</t>
+  </si>
+  <si>
+    <t>8dbd3721</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.752631</t>
+  </si>
+  <si>
+    <t>7bc13a3a</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.752946</t>
+  </si>
+  <si>
+    <t>b78bda4c</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.753628</t>
+  </si>
+  <si>
+    <t>d06207c5</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.754338</t>
+  </si>
+  <si>
+    <t>a6d79c51</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.754706</t>
+  </si>
+  <si>
+    <t>c1df3d84</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.755254</t>
+  </si>
+  <si>
+    <t>f43c1e3f</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.756340</t>
+  </si>
+  <si>
+    <t>4fa6bf28</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.756790</t>
+  </si>
+  <si>
+    <t>680d5c5d</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.757552</t>
+  </si>
+  <si>
+    <t>ea110151</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.761492</t>
+  </si>
+  <si>
+    <t>0e950a3b</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.762135</t>
+  </si>
+  <si>
+    <t>d12e980b</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.762549</t>
+  </si>
+  <si>
+    <t>f60514e3</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.762996</t>
+  </si>
+  <si>
+    <t>e420a58e</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.763453</t>
+  </si>
+  <si>
+    <t>db6331bd</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.763977</t>
+  </si>
+  <si>
+    <t>de50d8de</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.764267</t>
+  </si>
+  <si>
+    <t>22a6b111</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.764562</t>
+  </si>
+  <si>
+    <t>f8766e5c</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.764839</t>
+  </si>
+  <si>
+    <t>1ac08f2f</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.765513</t>
+  </si>
+  <si>
+    <t>30fc045a</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.765850</t>
+  </si>
+  <si>
+    <t>7094773e</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.766224</t>
+  </si>
+  <si>
+    <t>465da2c6</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.766520</t>
+  </si>
+  <si>
+    <t>226d8e32</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.766807</t>
+  </si>
+  <si>
+    <t>6a128bb7</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.767259</t>
+  </si>
+  <si>
+    <t>8b75b7a8</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.767977</t>
+  </si>
+  <si>
+    <t>fada95df</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.768420</t>
+  </si>
+  <si>
+    <t>c539f622</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.768926</t>
+  </si>
+  <si>
+    <t>aa6db482</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.769218</t>
+  </si>
+  <si>
+    <t>3b1579e0</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.769486</t>
+  </si>
+  <si>
+    <t>8cdac66c</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.770118</t>
+  </si>
+  <si>
+    <t>155c07fb</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.770416</t>
+  </si>
+  <si>
+    <t>b3d68036</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.770659</t>
+  </si>
+  <si>
+    <t>654526ee</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.770970</t>
+  </si>
+  <si>
+    <t>d7db29e1</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.771175</t>
+  </si>
+  <si>
+    <t>c64d12ca</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.771380</t>
+  </si>
+  <si>
+    <t>745fe3d7</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.771674</t>
+  </si>
+  <si>
+    <t>4950c6e9</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.772325</t>
+  </si>
+  <si>
+    <t>e7dc1bed</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.772607</t>
+  </si>
+  <si>
+    <t>d9bea58a</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.772848</t>
+  </si>
+  <si>
+    <t>b64c9930</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.773089</t>
+  </si>
+  <si>
+    <t>672ea090</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.773337</t>
+  </si>
+  <si>
+    <t>9c88e36a</t>
+  </si>
+  <si>
+    <t>ComplianceScanner</t>
+  </si>
+  <si>
+    <t>CERT-In Risk: Missing Audit Logging</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:33.564090</t>
   </si>
   <si>
     <t>Package / Library</t>
@@ -164,7 +677,7 @@
     <t>Location / Endpoint</t>
   </si>
   <si>
-    <t>4c6369a4</t>
+    <t>17d804e1</t>
   </si>
   <si>
     <t>AgentScanner</t>
@@ -176,79 +689,76 @@
     <t>AI Agent</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>2026-06-21T19:39:23.225955</t>
-  </si>
-  <si>
-    <t>1a5bc24c</t>
+    <t>2026-06-21T20:05:35.339732</t>
+  </si>
+  <si>
+    <t>e9764f50</t>
   </si>
   <si>
     <t>Agent Usage: CrewAI Import</t>
   </si>
   <si>
-    <t>2026-06-21T19:39:23.235572</t>
-  </si>
-  <si>
-    <t>9a4ef3e4</t>
+    <t>2026-06-21T20:05:35.346275</t>
+  </si>
+  <si>
+    <t>90e39b6e</t>
   </si>
   <si>
     <t>Agent Usage: Agent Instantiation</t>
   </si>
   <si>
-    <t>2026-06-21T19:39:23.245142</t>
-  </si>
-  <si>
-    <t>ddabc25f</t>
+    <t>2026-06-21T20:05:35.349952</t>
+  </si>
+  <si>
+    <t>0c4a7ba1</t>
   </si>
   <si>
     <t>Agent Usage: Crew Instantiation</t>
   </si>
   <si>
-    <t>2026-06-21T19:39:23.254499</t>
-  </si>
-  <si>
-    <t>b0de8c61</t>
+    <t>2026-06-21T20:05:35.357175</t>
+  </si>
+  <si>
+    <t>030cf0e8</t>
   </si>
   <si>
     <t>Agent Usage: AssistantAgent Instantiation</t>
   </si>
   <si>
-    <t>2026-06-21T19:39:23.268915</t>
-  </si>
-  <si>
-    <t>63a26f8f</t>
-  </si>
-  <si>
-    <t>2026-06-21T19:39:23.278404</t>
-  </si>
-  <si>
-    <t>2f319512</t>
-  </si>
-  <si>
-    <t>2026-06-21T19:39:23.284937</t>
-  </si>
-  <si>
-    <t>7ebc4509</t>
-  </si>
-  <si>
-    <t>2026-06-21T19:39:23.289467</t>
-  </si>
-  <si>
-    <t>e1df879e</t>
-  </si>
-  <si>
-    <t>2026-06-21T19:39:23.293885</t>
-  </si>
-  <si>
-    <t>f9c572ee</t>
-  </si>
-  <si>
-    <t>2026-06-21T19:39:23.331870</t>
-  </si>
-  <si>
-    <t>bb460bb0</t>
+    <t>2026-06-21T20:05:35.366371</t>
+  </si>
+  <si>
+    <t>d5e4278b</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.377749</t>
+  </si>
+  <si>
+    <t>bd9c6d8e</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.402167</t>
+  </si>
+  <si>
+    <t>ac508b32</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.408101</t>
+  </si>
+  <si>
+    <t>fef96daf</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.419434</t>
+  </si>
+  <si>
+    <t>c5e145e7</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:05:35.450013</t>
+  </si>
+  <si>
+    <t>f580a6b9</t>
   </si>
   <si>
     <t>RuntimeScanner</t>
@@ -260,7 +770,7 @@
     <t>LLM Runtime</t>
   </si>
   <si>
-    <t>2026-06-21T19:39:24.920140</t>
+    <t>2026-06-21T20:05:35.872243</t>
   </si>
   <si>
     <t>AI Discovery Scanner — Scan Summary Report</t>
@@ -275,13 +785,13 @@
     <t>Scan ID</t>
   </si>
   <si>
-    <t>494a9ead-152</t>
+    <t>8c9762fe-960</t>
   </si>
   <si>
     <t>Scan Timestamp</t>
   </si>
   <si>
-    <t>2026-06-21T19:39:22.791558</t>
+    <t>2026-06-21T20:05:33.488412</t>
   </si>
   <si>
     <t>Hostname</t>
@@ -380,19 +890,19 @@
     <t>25%</t>
   </si>
   <si>
+    <t>Data Privacy</t>
+  </si>
+  <si>
+    <t>Compliance</t>
+  </si>
+  <si>
+    <t>Supply Chain</t>
+  </si>
+  <si>
+    <t>15%</t>
+  </si>
+  <si>
     <t>LOW</t>
-  </si>
-  <si>
-    <t>Data Privacy</t>
-  </si>
-  <si>
-    <t>Compliance</t>
-  </si>
-  <si>
-    <t>Supply Chain</t>
-  </si>
-  <si>
-    <t>15%</t>
   </si>
   <si>
     <t>Operational</t>
@@ -931,22 +1441,2452 @@
       </c>
       <c r="D12" t="inlineStr" s="14">
         <is>
-          <t>License signature 'MIT' detected in file docstring header of 'license_scanner.py'. Taxonomy classification: Approved. Permissive license. Allowed for enterprise usage.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'debug_test.py' at line 10. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:1</t>
-        </is>
-      </c>
-      <c r="F12" t="s" s="8">
-        <v>11</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/debug_test.py:10</t>
+        </is>
+      </c>
+      <c r="F12" t="s" s="6">
+        <v>22</v>
       </c>
       <c r="G12" s="10">
-        <v>90.0</v>
+        <v>85.0</v>
       </c>
       <c r="H12" t="s" s="10">
         <v>43</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="11">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s" s="4">
+        <v>45</v>
+      </c>
+      <c r="D13" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
+        </is>
+      </c>
+      <c r="F13" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G13" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H13" t="s" s="11">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="10">
+        <v>48</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D14" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
+        </is>
+      </c>
+      <c r="F14" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G14" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H14" t="s" s="10">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="11">
+        <v>50</v>
+      </c>
+      <c r="B15" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D15" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
+        </is>
+      </c>
+      <c r="F15" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G15" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H15" t="s" s="11">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="10">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="D16" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
+        </is>
+      </c>
+      <c r="F16" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G16" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H16" t="s" s="10">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="11">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="D17" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
+        </is>
+      </c>
+      <c r="F17" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G17" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H17" t="s" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="10">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D18" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:35</t>
+        </is>
+      </c>
+      <c r="F18" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G18" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H18" t="s" s="10">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="11">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D19" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 36. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:36</t>
+        </is>
+      </c>
+      <c r="F19" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G19" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H19" t="s" s="11">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="10">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D20" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 37. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:37</t>
+        </is>
+      </c>
+      <c r="F20" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G20" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H20" t="s" s="10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="11">
+        <v>66</v>
+      </c>
+      <c r="B21" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s" s="4">
+        <v>55</v>
+      </c>
+      <c r="D21" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'verify_implementation.py' at line 38. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:38</t>
+        </is>
+      </c>
+      <c r="F21" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G21" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H21" t="s" s="11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="10">
+        <v>68</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="D22" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'verify_implementation.py' at line 39. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:39</t>
+        </is>
+      </c>
+      <c r="F22" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G22" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H22" t="s" s="10">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="11">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s" s="4">
+        <v>45</v>
+      </c>
+      <c r="D23" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 53. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:53</t>
+        </is>
+      </c>
+      <c r="F23" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G23" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H23" t="s" s="11">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="10">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D24" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 54. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:54</t>
+        </is>
+      </c>
+      <c r="F24" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G24" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H24" t="s" s="10">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="11">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C25" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D25" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 55. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:55</t>
+        </is>
+      </c>
+      <c r="F25" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G25" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H25" t="s" s="11">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="10">
+        <v>76</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="D26" t="inlineStr" s="14">
+        <is>
+          <t>License signature 'MIT' detected in file docstring header of 'license_scanner.py'. Taxonomy classification: Approved. Permissive license. Allowed for enterprise usage.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:1</t>
+        </is>
+      </c>
+      <c r="F26" t="s" s="8">
+        <v>11</v>
+      </c>
+      <c r="G26" s="10">
+        <v>90.0</v>
+      </c>
+      <c r="H26" t="s" s="10">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="11">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C27" t="s" s="4">
+        <v>45</v>
+      </c>
+      <c r="D27" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+        </is>
+      </c>
+      <c r="F27" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G27" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H27" t="s" s="11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="10">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D28" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+        </is>
+      </c>
+      <c r="F28" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G28" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H28" t="s" s="10">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="11">
+        <v>83</v>
+      </c>
+      <c r="B29" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C29" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D29" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+        </is>
+      </c>
+      <c r="F29" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G29" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H29" t="s" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="10">
+        <v>85</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="D30" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+        </is>
+      </c>
+      <c r="F30" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G30" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H30" t="s" s="10">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="11">
+        <v>87</v>
+      </c>
+      <c r="B31" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C31" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="D31" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+        </is>
+      </c>
+      <c r="F31" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G31" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H31" t="s" s="11">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="10">
+        <v>89</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D32" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 7. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:7</t>
+        </is>
+      </c>
+      <c r="F32" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G32" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H32" t="s" s="10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="11">
+        <v>91</v>
+      </c>
+      <c r="B33" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C33" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D33" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 7. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:7</t>
+        </is>
+      </c>
+      <c r="F33" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G33" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H33" t="s" s="11">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="10">
+        <v>93</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D34" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 41. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:41</t>
+        </is>
+      </c>
+      <c r="F34" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G34" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H34" t="s" s="10">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="11">
+        <v>95</v>
+      </c>
+      <c r="B35" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C35" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D35" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 45. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:45</t>
+        </is>
+      </c>
+      <c r="F35" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G35" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H35" t="s" s="11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="10">
+        <v>97</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D36" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:47</t>
+        </is>
+      </c>
+      <c r="F36" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G36" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H36" t="s" s="10">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="11">
+        <v>99</v>
+      </c>
+      <c r="B37" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C37" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="D37" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 50. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:50</t>
+        </is>
+      </c>
+      <c r="F37" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G37" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H37" t="s" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="10">
+        <v>101</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D38" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 53. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:53</t>
+        </is>
+      </c>
+      <c r="F38" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G38" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H38" t="s" s="10">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="11">
+        <v>103</v>
+      </c>
+      <c r="B39" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C39" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D39" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 56. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:56</t>
+        </is>
+      </c>
+      <c r="F39" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G39" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H39" t="s" s="11">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="10">
+        <v>105</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D40" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 56. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:56</t>
+        </is>
+      </c>
+      <c r="F40" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G40" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H40" t="s" s="10">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="11">
+        <v>107</v>
+      </c>
+      <c r="B41" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C41" t="s" s="4">
+        <v>55</v>
+      </c>
+      <c r="D41" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'license_scanner.py' at line 59. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:59</t>
+        </is>
+      </c>
+      <c r="F41" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G41" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H41" t="s" s="11">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="10">
+        <v>109</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="D42" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 65. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:65</t>
+        </is>
+      </c>
+      <c r="F42" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G42" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H42" t="s" s="10">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="11">
+        <v>111</v>
+      </c>
+      <c r="B43" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C43" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="D43" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 68. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:68</t>
+        </is>
+      </c>
+      <c r="F43" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G43" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H43" t="s" s="11">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="10">
+        <v>113</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D44" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 75. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:75</t>
+        </is>
+      </c>
+      <c r="F44" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G44" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H44" t="s" s="10">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="11">
+        <v>115</v>
+      </c>
+      <c r="B45" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C45" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D45" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 76. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:76</t>
+        </is>
+      </c>
+      <c r="F45" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G45" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H45" t="s" s="11">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="10">
+        <v>117</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D46" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 77. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:77</t>
+        </is>
+      </c>
+      <c r="F46" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G46" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H46" t="s" s="10">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="11">
+        <v>119</v>
+      </c>
+      <c r="B47" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C47" t="s" s="4">
+        <v>45</v>
+      </c>
+      <c r="D47" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 78. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:78</t>
+        </is>
+      </c>
+      <c r="F47" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G47" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H47" t="s" s="11">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="10">
+        <v>121</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D48" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 79. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:79</t>
+        </is>
+      </c>
+      <c r="F48" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G48" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H48" t="s" s="10">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="11">
+        <v>123</v>
+      </c>
+      <c r="B49" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C49" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D49" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:21</t>
+        </is>
+      </c>
+      <c r="F49" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G49" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H49" t="s" s="11">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="10">
+        <v>125</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D50" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 23. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:23</t>
+        </is>
+      </c>
+      <c r="F50" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G50" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H50" t="s" s="10">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="11">
+        <v>127</v>
+      </c>
+      <c r="B51" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C51" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D51" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 34. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:34</t>
+        </is>
+      </c>
+      <c r="F51" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G51" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H51" t="s" s="11">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="10">
+        <v>129</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D52" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 39. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:39</t>
+        </is>
+      </c>
+      <c r="F52" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G52" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H52" t="s" s="10">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="11">
+        <v>131</v>
+      </c>
+      <c r="B53" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C53" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D53" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 40. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:40</t>
+        </is>
+      </c>
+      <c r="F53" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G53" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H53" t="s" s="11">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="10">
+        <v>133</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D54" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:47</t>
+        </is>
+      </c>
+      <c r="F54" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G54" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H54" t="s" s="10">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="11">
+        <v>135</v>
+      </c>
+      <c r="B55" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C55" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D55" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:61</t>
+        </is>
+      </c>
+      <c r="F55" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G55" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H55" t="s" s="11">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="10">
+        <v>137</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D56" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 62. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:62</t>
+        </is>
+      </c>
+      <c r="F56" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G56" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H56" t="s" s="10">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="11">
+        <v>139</v>
+      </c>
+      <c r="B57" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C57" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D57" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 70. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:70</t>
+        </is>
+      </c>
+      <c r="F57" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G57" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H57" t="s" s="11">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="10">
+        <v>141</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D58" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 100. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:100</t>
+        </is>
+      </c>
+      <c r="F58" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G58" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H58" t="s" s="10">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="11">
+        <v>143</v>
+      </c>
+      <c r="B59" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C59" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D59" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 112. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:112</t>
+        </is>
+      </c>
+      <c r="F59" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G59" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H59" t="s" s="11">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="10">
+        <v>145</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D60" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 113. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:113</t>
+        </is>
+      </c>
+      <c r="F60" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G60" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H60" t="s" s="10">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="11">
+        <v>147</v>
+      </c>
+      <c r="B61" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C61" t="s" s="4">
+        <v>45</v>
+      </c>
+      <c r="D61" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+        </is>
+      </c>
+      <c r="F61" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G61" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H61" t="s" s="11">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="10">
+        <v>149</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D62" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+        </is>
+      </c>
+      <c r="F62" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G62" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H62" t="s" s="10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="11">
+        <v>151</v>
+      </c>
+      <c r="B63" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C63" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D63" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+        </is>
+      </c>
+      <c r="F63" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G63" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H63" t="s" s="11">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="10">
+        <v>153</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="D64" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+        </is>
+      </c>
+      <c r="F64" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G64" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H64" t="s" s="10">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="11">
+        <v>155</v>
+      </c>
+      <c r="B65" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C65" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="D65" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+        </is>
+      </c>
+      <c r="F65" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G65" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H65" t="s" s="11">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="10">
+        <v>157</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D66" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 30. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:30</t>
+        </is>
+      </c>
+      <c r="F66" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G66" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H66" t="s" s="10">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="11">
+        <v>159</v>
+      </c>
+      <c r="B67" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C67" t="s" s="4">
+        <v>45</v>
+      </c>
+      <c r="D67" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 31. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:31</t>
+        </is>
+      </c>
+      <c r="F67" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G67" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H67" t="s" s="11">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="10">
+        <v>161</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D68" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 32. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:32</t>
+        </is>
+      </c>
+      <c r="F68" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G68" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H68" t="s" s="10">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="11">
+        <v>163</v>
+      </c>
+      <c r="B69" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C69" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D69" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 34. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:34</t>
+        </is>
+      </c>
+      <c r="F69" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G69" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H69" t="s" s="11">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="10">
+        <v>165</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D70" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:35</t>
+        </is>
+      </c>
+      <c r="F70" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G70" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H70" t="s" s="10">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="11">
+        <v>167</v>
+      </c>
+      <c r="B71" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C71" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D71" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 36. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:36</t>
+        </is>
+      </c>
+      <c r="F71" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G71" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H71" t="s" s="11">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="10">
+        <v>169</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D72" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 38. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:38</t>
+        </is>
+      </c>
+      <c r="F72" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G72" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H72" t="s" s="10">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="11">
+        <v>171</v>
+      </c>
+      <c r="B73" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C73" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D73" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 39. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:39</t>
+        </is>
+      </c>
+      <c r="F73" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G73" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H73" t="s" s="11">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="10">
+        <v>173</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C74" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D74" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 40. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:40</t>
+        </is>
+      </c>
+      <c r="F74" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G74" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H74" t="s" s="10">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="11">
+        <v>175</v>
+      </c>
+      <c r="B75" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C75" t="s" s="4">
+        <v>55</v>
+      </c>
+      <c r="D75" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 42. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:42</t>
+        </is>
+      </c>
+      <c r="F75" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G75" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H75" t="s" s="11">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="10">
+        <v>177</v>
+      </c>
+      <c r="B76" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C76" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="D76" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 43. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:43</t>
+        </is>
+      </c>
+      <c r="F76" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G76" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H76" t="s" s="10">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="11">
+        <v>179</v>
+      </c>
+      <c r="B77" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C77" t="s" s="4">
+        <v>55</v>
+      </c>
+      <c r="D77" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 44. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:44</t>
+        </is>
+      </c>
+      <c r="F77" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G77" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H77" t="s" s="11">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="10">
+        <v>181</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C78" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="D78" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 46. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:46</t>
+        </is>
+      </c>
+      <c r="F78" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G78" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H78" t="s" s="10">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="11">
+        <v>183</v>
+      </c>
+      <c r="B79" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C79" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="D79" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:47</t>
+        </is>
+      </c>
+      <c r="F79" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G79" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H79" t="s" s="11">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="10">
+        <v>185</v>
+      </c>
+      <c r="B80" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C80" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="D80" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 48. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:48</t>
+        </is>
+      </c>
+      <c r="F80" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G80" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H80" t="s" s="10">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="11">
+        <v>187</v>
+      </c>
+      <c r="B81" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C81" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D81" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 57. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:57</t>
+        </is>
+      </c>
+      <c r="F81" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G81" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H81" t="s" s="11">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="10">
+        <v>189</v>
+      </c>
+      <c r="B82" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C82" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D82" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 60. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:60</t>
+        </is>
+      </c>
+      <c r="F82" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G82" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H82" t="s" s="10">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="11">
+        <v>191</v>
+      </c>
+      <c r="B83" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C83" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="D83" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:61</t>
+        </is>
+      </c>
+      <c r="F83" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G83" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H83" t="s" s="11">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="10">
+        <v>193</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C84" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D84" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 71. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:71</t>
+        </is>
+      </c>
+      <c r="F84" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G84" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H84" t="s" s="10">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="11">
+        <v>195</v>
+      </c>
+      <c r="B85" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C85" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D85" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 72. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:72</t>
+        </is>
+      </c>
+      <c r="F85" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G85" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H85" t="s" s="11">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="10">
+        <v>197</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C86" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D86" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 73. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:73</t>
+        </is>
+      </c>
+      <c r="F86" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G86" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H86" t="s" s="10">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="11">
+        <v>199</v>
+      </c>
+      <c r="B87" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C87" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D87" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 79. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:79</t>
+        </is>
+      </c>
+      <c r="F87" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G87" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H87" t="s" s="11">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="10">
+        <v>201</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C88" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D88" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 101. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:101</t>
+        </is>
+      </c>
+      <c r="F88" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G88" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H88" t="s" s="10">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="11">
+        <v>203</v>
+      </c>
+      <c r="B89" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C89" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D89" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 105. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:105</t>
+        </is>
+      </c>
+      <c r="F89" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G89" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H89" t="s" s="11">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="10">
+        <v>205</v>
+      </c>
+      <c r="B90" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C90" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D90" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 109. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:109</t>
+        </is>
+      </c>
+      <c r="F90" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G90" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H90" t="s" s="10">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="11">
+        <v>207</v>
+      </c>
+      <c r="B91" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C91" t="s" s="4">
+        <v>45</v>
+      </c>
+      <c r="D91" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 113. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:113</t>
+        </is>
+      </c>
+      <c r="F91" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G91" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H91" t="s" s="11">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="10">
+        <v>209</v>
+      </c>
+      <c r="B92" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C92" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D92" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 117. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:117</t>
+        </is>
+      </c>
+      <c r="F92" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G92" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H92" t="s" s="10">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="11">
+        <v>211</v>
+      </c>
+      <c r="B93" t="s" s="4">
+        <v>212</v>
+      </c>
+      <c r="C93" t="s" s="4">
+        <v>213</v>
+      </c>
+      <c r="D93" t="inlineStr" s="15">
+        <is>
+          <t>The primary audit log (ai_scanner.log) is missing. CERT-In mandates active logging for incident readiness and forensic timelines.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr" s="15">
+        <is>
+          <t>ai_scanner.log</t>
+        </is>
+      </c>
+      <c r="F93" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G93" s="11">
+        <v>90.0</v>
+      </c>
+      <c r="H93" t="s" s="11">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -974,13 +3914,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>44</v>
+        <v>215</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>3</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c r="F1" t="s" s="1">
         <v>5</v>
@@ -1018,16 +3958,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>46</v>
+        <v>217</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>3</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>47</v>
+        <v>218</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>48</v>
+        <v>219</v>
       </c>
       <c r="G1" t="s" s="1">
         <v>5</v>
@@ -1041,13 +3981,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="10">
-        <v>49</v>
+        <v>220</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>51</v>
+        <v>222</v>
       </c>
       <c r="D2" t="inlineStr" s="14">
         <is>
@@ -1055,7 +3995,7 @@
         </is>
       </c>
       <c r="E2" t="s" s="10">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F2" t="inlineStr" s="14">
         <is>
@@ -1063,24 +4003,24 @@
         </is>
       </c>
       <c r="G2" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H2" s="10">
         <v>85.0</v>
       </c>
       <c r="I2" t="s" s="10">
-        <v>54</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="11">
-        <v>55</v>
+        <v>225</v>
       </c>
       <c r="B3" t="s" s="4">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C3" t="s" s="4">
-        <v>56</v>
+        <v>226</v>
       </c>
       <c r="D3" t="inlineStr" s="15">
         <is>
@@ -1088,7 +4028,7 @@
         </is>
       </c>
       <c r="E3" t="s" s="11">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F3" t="inlineStr" s="15">
         <is>
@@ -1096,24 +4036,24 @@
         </is>
       </c>
       <c r="G3" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H3" s="11">
         <v>85.0</v>
       </c>
       <c r="I3" t="s" s="11">
-        <v>57</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="10">
-        <v>58</v>
+        <v>228</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>59</v>
+        <v>229</v>
       </c>
       <c r="D4" t="inlineStr" s="14">
         <is>
@@ -1121,7 +4061,7 @@
         </is>
       </c>
       <c r="E4" t="s" s="10">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F4" t="inlineStr" s="14">
         <is>
@@ -1129,24 +4069,24 @@
         </is>
       </c>
       <c r="G4" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H4" s="10">
         <v>85.0</v>
       </c>
       <c r="I4" t="s" s="10">
-        <v>60</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="11">
-        <v>61</v>
+        <v>231</v>
       </c>
       <c r="B5" t="s" s="4">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C5" t="s" s="4">
-        <v>62</v>
+        <v>232</v>
       </c>
       <c r="D5" t="inlineStr" s="15">
         <is>
@@ -1154,7 +4094,7 @@
         </is>
       </c>
       <c r="E5" t="s" s="11">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F5" t="inlineStr" s="15">
         <is>
@@ -1162,24 +4102,24 @@
         </is>
       </c>
       <c r="G5" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H5" s="11">
         <v>85.0</v>
       </c>
       <c r="I5" t="s" s="11">
-        <v>63</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="10">
-        <v>64</v>
+        <v>234</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>65</v>
+        <v>235</v>
       </c>
       <c r="D6" t="inlineStr" s="14">
         <is>
@@ -1187,7 +4127,7 @@
         </is>
       </c>
       <c r="E6" t="s" s="10">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F6" t="inlineStr" s="14">
         <is>
@@ -1195,24 +4135,24 @@
         </is>
       </c>
       <c r="G6" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H6" s="10">
         <v>85.0</v>
       </c>
       <c r="I6" t="s" s="10">
-        <v>66</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="11">
-        <v>67</v>
+        <v>237</v>
       </c>
       <c r="B7" t="s" s="4">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C7" t="s" s="4">
-        <v>56</v>
+        <v>226</v>
       </c>
       <c r="D7" t="inlineStr" s="15">
         <is>
@@ -1220,7 +4160,7 @@
         </is>
       </c>
       <c r="E7" t="s" s="11">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F7" t="inlineStr" s="15">
         <is>
@@ -1228,24 +4168,24 @@
         </is>
       </c>
       <c r="G7" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H7" s="11">
         <v>85.0</v>
       </c>
       <c r="I7" t="s" s="11">
-        <v>68</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="10">
-        <v>69</v>
+        <v>239</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>51</v>
+        <v>222</v>
       </c>
       <c r="D8" t="inlineStr" s="14">
         <is>
@@ -1253,7 +4193,7 @@
         </is>
       </c>
       <c r="E8" t="s" s="10">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F8" t="inlineStr" s="14">
         <is>
@@ -1261,24 +4201,24 @@
         </is>
       </c>
       <c r="G8" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H8" s="10">
         <v>85.0</v>
       </c>
       <c r="I8" t="s" s="10">
-        <v>70</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="11">
-        <v>71</v>
+        <v>241</v>
       </c>
       <c r="B9" t="s" s="4">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C9" t="s" s="4">
-        <v>51</v>
+        <v>222</v>
       </c>
       <c r="D9" t="inlineStr" s="15">
         <is>
@@ -1286,7 +4226,7 @@
         </is>
       </c>
       <c r="E9" t="s" s="11">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F9" t="inlineStr" s="15">
         <is>
@@ -1294,24 +4234,24 @@
         </is>
       </c>
       <c r="G9" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H9" s="11">
         <v>85.0</v>
       </c>
       <c r="I9" t="s" s="11">
-        <v>72</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="10">
-        <v>73</v>
+        <v>243</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>56</v>
+        <v>226</v>
       </c>
       <c r="D10" t="inlineStr" s="14">
         <is>
@@ -1319,7 +4259,7 @@
         </is>
       </c>
       <c r="E10" t="s" s="10">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F10" t="inlineStr" s="14">
         <is>
@@ -1327,24 +4267,24 @@
         </is>
       </c>
       <c r="G10" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H10" s="10">
         <v>85.0</v>
       </c>
       <c r="I10" t="s" s="10">
-        <v>74</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="11">
-        <v>75</v>
+        <v>245</v>
       </c>
       <c r="B11" t="s" s="4">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C11" t="s" s="4">
-        <v>59</v>
+        <v>229</v>
       </c>
       <c r="D11" t="inlineStr" s="15">
         <is>
@@ -1352,7 +4292,7 @@
         </is>
       </c>
       <c r="E11" t="s" s="11">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F11" t="inlineStr" s="15">
         <is>
@@ -1360,24 +4300,24 @@
         </is>
       </c>
       <c r="G11" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H11" s="11">
         <v>85.0</v>
       </c>
       <c r="I11" t="s" s="11">
-        <v>76</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="10">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>79</v>
+        <v>249</v>
       </c>
       <c r="D12" t="inlineStr" s="14">
         <is>
@@ -1385,7 +4325,7 @@
         </is>
       </c>
       <c r="E12" t="s" s="10">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="F12" t="inlineStr" s="14">
         <is>
@@ -1393,13 +4333,13 @@
         </is>
       </c>
       <c r="G12" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H12" s="10">
         <v>90.0</v>
       </c>
       <c r="I12" t="s" s="10">
-        <v>81</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -1417,102 +4357,102 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" t="s" s="1">
-        <v>83</v>
+        <v>253</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>84</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="9">
-        <v>85</v>
+        <v>255</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>86</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="9">
-        <v>87</v>
+        <v>257</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>88</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="9">
-        <v>89</v>
+        <v>259</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>90</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="9">
-        <v>91</v>
+        <v>261</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>92</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="9">
-        <v>93</v>
+        <v>263</v>
       </c>
       <c r="B8" s="10">
-        <v>2.317</v>
+        <v>2.573</v>
       </c>
     </row>
     <row r="9"/>
     <row r="10">
       <c r="A10" t="s" s="3">
-        <v>94</v>
+        <v>264</v>
       </c>
       <c r="B10" t="s" s="3">
-        <v>95</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="9">
-        <v>96</v>
+        <v>266</v>
       </c>
       <c r="B11" s="10">
-        <v>22</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="9">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="B12" s="10">
-        <v>48.9</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="9">
-        <v>98</v>
+        <v>268</v>
       </c>
       <c r="B13" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="9">
-        <v>99</v>
+        <v>269</v>
       </c>
       <c r="B14" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="9">
-        <v>100</v>
+        <v>270</v>
       </c>
       <c r="B15" s="10">
         <v>0</v>
@@ -1524,13 +4464,13 @@
         <v>1</v>
       </c>
       <c r="B17" t="s" s="1">
-        <v>101</v>
+        <v>271</v>
       </c>
       <c r="C17" t="s" s="1">
-        <v>102</v>
+        <v>272</v>
       </c>
       <c r="D17" t="s" s="1">
-        <v>103</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18">
@@ -1538,10 +4478,10 @@
         <v>9</v>
       </c>
       <c r="B18" t="s" s="10">
-        <v>104</v>
+        <v>274</v>
       </c>
       <c r="C18" s="10">
-        <v>0.653</v>
+        <v>1.946</v>
       </c>
       <c r="D18" s="10">
         <v>3</v>
@@ -1549,13 +4489,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="4">
-        <v>105</v>
+        <v>275</v>
       </c>
       <c r="B19" t="s" s="11">
-        <v>104</v>
+        <v>274</v>
       </c>
       <c r="C19" s="11">
-        <v>0.106</v>
+        <v>0.084</v>
       </c>
       <c r="D19" s="11">
         <v>0</v>
@@ -1563,13 +4503,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>106</v>
+        <v>276</v>
       </c>
       <c r="B20" t="s" s="10">
-        <v>104</v>
+        <v>274</v>
       </c>
       <c r="C20" s="10">
-        <v>0.064</v>
+        <v>0.047</v>
       </c>
       <c r="D20" s="10">
         <v>0</v>
@@ -1577,13 +4517,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="4">
-        <v>107</v>
+        <v>277</v>
       </c>
       <c r="B21" t="s" s="11">
-        <v>104</v>
+        <v>274</v>
       </c>
       <c r="C21" s="11">
-        <v>1.448</v>
+        <v>2.195</v>
       </c>
       <c r="D21" s="11">
         <v>0</v>
@@ -1591,13 +4531,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s" s="10">
-        <v>104</v>
+        <v>274</v>
       </c>
       <c r="C22" s="10">
-        <v>0.598</v>
+        <v>2.152</v>
       </c>
       <c r="D22" s="10">
         <v>10</v>
@@ -1605,13 +4545,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="4">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="B23" t="s" s="11">
-        <v>104</v>
+        <v>274</v>
       </c>
       <c r="C23" s="11">
-        <v>2.054</v>
+        <v>2.329</v>
       </c>
       <c r="D23" s="11">
         <v>1</v>
@@ -1622,10 +4562,10 @@
         <v>20</v>
       </c>
       <c r="B24" t="s" s="10">
-        <v>104</v>
+        <v>274</v>
       </c>
       <c r="C24" s="10">
-        <v>0.582</v>
+        <v>1.994</v>
       </c>
       <c r="D24" s="10">
         <v>7</v>
@@ -1633,13 +4573,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="4">
-        <v>108</v>
+        <v>278</v>
       </c>
       <c r="B25" t="s" s="11">
-        <v>104</v>
+        <v>274</v>
       </c>
       <c r="C25" s="11">
-        <v>0.878</v>
+        <v>2.224</v>
       </c>
       <c r="D25" s="11">
         <v>0</v>
@@ -1650,12 +4590,26 @@
         <v>41</v>
       </c>
       <c r="B26" t="s" s="10">
-        <v>104</v>
+        <v>274</v>
       </c>
       <c r="C26" s="10">
-        <v>0.322</v>
+        <v>2.302</v>
       </c>
       <c r="D26" s="10">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="4">
+        <v>212</v>
+      </c>
+      <c r="B27" t="s" s="11">
+        <v>274</v>
+      </c>
+      <c r="C27" s="11">
+        <v>0.018</v>
+      </c>
+      <c r="D27" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1685,19 +4639,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>109</v>
+        <v>279</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>3</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>110</v>
+        <v>280</v>
       </c>
       <c r="F1" t="s" s="1">
         <v>5</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>111</v>
+        <v>281</v>
       </c>
       <c r="H1" t="s" s="1">
         <v>6</v>
@@ -1722,7 +4676,7 @@
         </is>
       </c>
       <c r="E2" t="s" s="10">
-        <v>112</v>
+        <v>282</v>
       </c>
       <c r="F2" t="s" s="8">
         <v>11</v>
@@ -1755,7 +4709,7 @@
         </is>
       </c>
       <c r="E3" t="s" s="11">
-        <v>112</v>
+        <v>282</v>
       </c>
       <c r="F3" t="s" s="8">
         <v>11</v>
@@ -1788,7 +4742,7 @@
         </is>
       </c>
       <c r="E4" t="s" s="10">
-        <v>112</v>
+        <v>282</v>
       </c>
       <c r="F4" t="s" s="8">
         <v>11</v>
@@ -1807,13 +4761,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="11">
-        <v>49</v>
+        <v>220</v>
       </c>
       <c r="B5" t="s" s="4">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C5" t="s" s="4">
-        <v>51</v>
+        <v>222</v>
       </c>
       <c r="D5" t="inlineStr" s="15">
         <is>
@@ -1821,10 +4775,10 @@
         </is>
       </c>
       <c r="E5" t="s" s="11">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F5" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G5" t="inlineStr" s="15">
         <is>
@@ -1835,18 +4789,18 @@
         <v>85.0</v>
       </c>
       <c r="I5" t="s" s="11">
-        <v>54</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="10">
-        <v>55</v>
+        <v>225</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>56</v>
+        <v>226</v>
       </c>
       <c r="D6" t="inlineStr" s="14">
         <is>
@@ -1854,10 +4808,10 @@
         </is>
       </c>
       <c r="E6" t="s" s="10">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F6" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G6" t="inlineStr" s="14">
         <is>
@@ -1868,18 +4822,18 @@
         <v>85.0</v>
       </c>
       <c r="I6" t="s" s="10">
-        <v>57</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="11">
-        <v>58</v>
+        <v>228</v>
       </c>
       <c r="B7" t="s" s="4">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C7" t="s" s="4">
-        <v>59</v>
+        <v>229</v>
       </c>
       <c r="D7" t="inlineStr" s="15">
         <is>
@@ -1887,10 +4841,10 @@
         </is>
       </c>
       <c r="E7" t="s" s="11">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F7" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G7" t="inlineStr" s="15">
         <is>
@@ -1901,18 +4855,18 @@
         <v>85.0</v>
       </c>
       <c r="I7" t="s" s="11">
-        <v>60</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="10">
-        <v>61</v>
+        <v>231</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>62</v>
+        <v>232</v>
       </c>
       <c r="D8" t="inlineStr" s="14">
         <is>
@@ -1920,10 +4874,10 @@
         </is>
       </c>
       <c r="E8" t="s" s="10">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F8" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G8" t="inlineStr" s="14">
         <is>
@@ -1934,18 +4888,18 @@
         <v>85.0</v>
       </c>
       <c r="I8" t="s" s="10">
-        <v>63</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="11">
-        <v>64</v>
+        <v>234</v>
       </c>
       <c r="B9" t="s" s="4">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C9" t="s" s="4">
-        <v>65</v>
+        <v>235</v>
       </c>
       <c r="D9" t="inlineStr" s="15">
         <is>
@@ -1953,10 +4907,10 @@
         </is>
       </c>
       <c r="E9" t="s" s="11">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F9" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G9" t="inlineStr" s="15">
         <is>
@@ -1967,18 +4921,18 @@
         <v>85.0</v>
       </c>
       <c r="I9" t="s" s="11">
-        <v>66</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="10">
-        <v>67</v>
+        <v>237</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>56</v>
+        <v>226</v>
       </c>
       <c r="D10" t="inlineStr" s="14">
         <is>
@@ -1986,10 +4940,10 @@
         </is>
       </c>
       <c r="E10" t="s" s="10">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F10" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G10" t="inlineStr" s="14">
         <is>
@@ -2000,18 +4954,18 @@
         <v>85.0</v>
       </c>
       <c r="I10" t="s" s="10">
-        <v>68</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="11">
-        <v>69</v>
+        <v>239</v>
       </c>
       <c r="B11" t="s" s="4">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C11" t="s" s="4">
-        <v>51</v>
+        <v>222</v>
       </c>
       <c r="D11" t="inlineStr" s="15">
         <is>
@@ -2019,10 +4973,10 @@
         </is>
       </c>
       <c r="E11" t="s" s="11">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F11" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G11" t="inlineStr" s="15">
         <is>
@@ -2033,18 +4987,18 @@
         <v>85.0</v>
       </c>
       <c r="I11" t="s" s="11">
-        <v>70</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="10">
-        <v>71</v>
+        <v>241</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>51</v>
+        <v>222</v>
       </c>
       <c r="D12" t="inlineStr" s="14">
         <is>
@@ -2052,10 +5006,10 @@
         </is>
       </c>
       <c r="E12" t="s" s="10">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F12" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G12" t="inlineStr" s="14">
         <is>
@@ -2066,18 +5020,18 @@
         <v>85.0</v>
       </c>
       <c r="I12" t="s" s="10">
-        <v>72</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="11">
-        <v>73</v>
+        <v>243</v>
       </c>
       <c r="B13" t="s" s="4">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C13" t="s" s="4">
-        <v>56</v>
+        <v>226</v>
       </c>
       <c r="D13" t="inlineStr" s="15">
         <is>
@@ -2085,10 +5039,10 @@
         </is>
       </c>
       <c r="E13" t="s" s="11">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F13" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G13" t="inlineStr" s="15">
         <is>
@@ -2099,18 +5053,18 @@
         <v>85.0</v>
       </c>
       <c r="I13" t="s" s="11">
-        <v>74</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="10">
-        <v>75</v>
+        <v>245</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>59</v>
+        <v>229</v>
       </c>
       <c r="D14" t="inlineStr" s="14">
         <is>
@@ -2118,10 +5072,10 @@
         </is>
       </c>
       <c r="E14" t="s" s="10">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="F14" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G14" t="inlineStr" s="14">
         <is>
@@ -2132,18 +5086,18 @@
         <v>85.0</v>
       </c>
       <c r="I14" t="s" s="10">
-        <v>76</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="11">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="B15" t="s" s="4">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="C15" t="s" s="4">
-        <v>79</v>
+        <v>249</v>
       </c>
       <c r="D15" t="inlineStr" s="15">
         <is>
@@ -2151,10 +5105,10 @@
         </is>
       </c>
       <c r="E15" t="s" s="11">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="F15" t="s" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G15" t="inlineStr" s="15">
         <is>
@@ -2165,7 +5119,7 @@
         <v>90.0</v>
       </c>
       <c r="I15" t="s" s="11">
-        <v>81</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16">
@@ -2184,7 +5138,7 @@
         </is>
       </c>
       <c r="E16" t="s" s="10">
-        <v>113</v>
+        <v>283</v>
       </c>
       <c r="F16" t="s" s="6">
         <v>22</v>
@@ -2217,7 +5171,7 @@
         </is>
       </c>
       <c r="E17" t="s" s="11">
-        <v>113</v>
+        <v>283</v>
       </c>
       <c r="F17" t="s" s="6">
         <v>22</v>
@@ -2250,7 +5204,7 @@
         </is>
       </c>
       <c r="E18" t="s" s="10">
-        <v>113</v>
+        <v>283</v>
       </c>
       <c r="F18" t="s" s="6">
         <v>22</v>
@@ -2283,7 +5237,7 @@
         </is>
       </c>
       <c r="E19" t="s" s="11">
-        <v>113</v>
+        <v>283</v>
       </c>
       <c r="F19" t="s" s="6">
         <v>22</v>
@@ -2316,7 +5270,7 @@
         </is>
       </c>
       <c r="E20" t="s" s="10">
-        <v>113</v>
+        <v>283</v>
       </c>
       <c r="F20" t="s" s="6">
         <v>22</v>
@@ -2349,7 +5303,7 @@
         </is>
       </c>
       <c r="E21" t="s" s="11">
-        <v>113</v>
+        <v>283</v>
       </c>
       <c r="F21" t="s" s="6">
         <v>22</v>
@@ -2382,7 +5336,7 @@
         </is>
       </c>
       <c r="E22" t="s" s="10">
-        <v>113</v>
+        <v>283</v>
       </c>
       <c r="F22" t="s" s="6">
         <v>22</v>
@@ -2411,25 +5365,2698 @@
       </c>
       <c r="D23" t="inlineStr" s="15">
         <is>
-          <t>License signature 'MIT' detected in file docstring header of 'license_scanner.py'. Taxonomy classification: Approved. Permissive license. Allowed for enterprise usage.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'debug_test.py' at line 10. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E23" t="s" s="11">
-        <v>113</v>
-      </c>
-      <c r="F23" t="s" s="8">
-        <v>11</v>
+        <v>283</v>
+      </c>
+      <c r="F23" t="s" s="6">
+        <v>22</v>
       </c>
       <c r="G23" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:1</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/debug_test.py:10</t>
         </is>
       </c>
       <c r="H23" s="11">
-        <v>90.0</v>
+        <v>85.0</v>
       </c>
       <c r="I23" t="s" s="11">
         <v>43</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="10">
+        <v>44</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D24" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E24" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F24" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G24" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
+        </is>
+      </c>
+      <c r="H24" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I24" t="s" s="10">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="11">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C25" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D25" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E25" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F25" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G25" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
+        </is>
+      </c>
+      <c r="H25" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I25" t="s" s="11">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="10">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D26" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E26" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F26" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G26" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
+        </is>
+      </c>
+      <c r="H26" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I26" t="s" s="10">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="11">
+        <v>54</v>
+      </c>
+      <c r="B27" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C27" t="s" s="4">
+        <v>55</v>
+      </c>
+      <c r="D27" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E27" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F27" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G27" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
+        </is>
+      </c>
+      <c r="H27" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I27" t="s" s="11">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="10">
+        <v>57</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="D28" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E28" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F28" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G28" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
+        </is>
+      </c>
+      <c r="H28" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I28" t="s" s="10">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="11">
+        <v>60</v>
+      </c>
+      <c r="B29" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C29" t="s" s="4">
+        <v>45</v>
+      </c>
+      <c r="D29" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E29" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F29" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G29" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:35</t>
+        </is>
+      </c>
+      <c r="H29" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I29" t="s" s="11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="10">
+        <v>62</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D30" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 36. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E30" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F30" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G30" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:36</t>
+        </is>
+      </c>
+      <c r="H30" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I30" t="s" s="10">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="11">
+        <v>64</v>
+      </c>
+      <c r="B31" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C31" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D31" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 37. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E31" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F31" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G31" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:37</t>
+        </is>
+      </c>
+      <c r="H31" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I31" t="s" s="11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="10">
+        <v>66</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="D32" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'verify_implementation.py' at line 38. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E32" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F32" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G32" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:38</t>
+        </is>
+      </c>
+      <c r="H32" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I32" t="s" s="10">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="11">
+        <v>68</v>
+      </c>
+      <c r="B33" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C33" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="D33" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'verify_implementation.py' at line 39. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E33" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F33" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G33" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:39</t>
+        </is>
+      </c>
+      <c r="H33" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I33" t="s" s="11">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="10">
+        <v>70</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D34" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 53. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E34" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F34" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G34" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:53</t>
+        </is>
+      </c>
+      <c r="H34" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I34" t="s" s="10">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="11">
+        <v>72</v>
+      </c>
+      <c r="B35" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C35" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D35" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 54. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E35" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F35" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G35" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:54</t>
+        </is>
+      </c>
+      <c r="H35" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I35" t="s" s="11">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="10">
+        <v>74</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D36" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 55. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E36" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F36" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G36" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:55</t>
+        </is>
+      </c>
+      <c r="H36" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I36" t="s" s="10">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="11">
+        <v>76</v>
+      </c>
+      <c r="B37" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C37" t="s" s="4">
+        <v>77</v>
+      </c>
+      <c r="D37" t="inlineStr" s="15">
+        <is>
+          <t>License signature 'MIT' detected in file docstring header of 'license_scanner.py'. Taxonomy classification: Approved. Permissive license. Allowed for enterprise usage.</t>
+        </is>
+      </c>
+      <c r="E37" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F37" t="s" s="8">
+        <v>11</v>
+      </c>
+      <c r="G37" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:1</t>
+        </is>
+      </c>
+      <c r="H37" s="11">
+        <v>90.0</v>
+      </c>
+      <c r="I37" t="s" s="11">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="10">
+        <v>79</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D38" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E38" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F38" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G38" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+        </is>
+      </c>
+      <c r="H38" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I38" t="s" s="10">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="11">
+        <v>81</v>
+      </c>
+      <c r="B39" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C39" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D39" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E39" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F39" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G39" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+        </is>
+      </c>
+      <c r="H39" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I39" t="s" s="11">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="10">
+        <v>83</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D40" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E40" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F40" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G40" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+        </is>
+      </c>
+      <c r="H40" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I40" t="s" s="10">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="11">
+        <v>85</v>
+      </c>
+      <c r="B41" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C41" t="s" s="4">
+        <v>55</v>
+      </c>
+      <c r="D41" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E41" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F41" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G41" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+        </is>
+      </c>
+      <c r="H41" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I41" t="s" s="11">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="10">
+        <v>87</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="D42" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E42" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F42" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G42" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+        </is>
+      </c>
+      <c r="H42" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I42" t="s" s="10">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="11">
+        <v>89</v>
+      </c>
+      <c r="B43" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C43" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D43" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 7. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E43" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F43" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G43" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:7</t>
+        </is>
+      </c>
+      <c r="H43" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I43" t="s" s="11">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="10">
+        <v>91</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D44" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 7. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E44" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F44" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G44" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:7</t>
+        </is>
+      </c>
+      <c r="H44" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I44" t="s" s="10">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="11">
+        <v>93</v>
+      </c>
+      <c r="B45" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C45" t="s" s="4">
+        <v>45</v>
+      </c>
+      <c r="D45" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 41. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E45" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F45" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G45" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:41</t>
+        </is>
+      </c>
+      <c r="H45" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I45" t="s" s="11">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="10">
+        <v>95</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D46" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 45. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E46" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F46" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G46" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:45</t>
+        </is>
+      </c>
+      <c r="H46" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I46" t="s" s="10">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="11">
+        <v>97</v>
+      </c>
+      <c r="B47" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C47" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D47" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E47" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F47" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G47" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:47</t>
+        </is>
+      </c>
+      <c r="H47" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I47" t="s" s="11">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="10">
+        <v>99</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="D48" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 50. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E48" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F48" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G48" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:50</t>
+        </is>
+      </c>
+      <c r="H48" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I48" t="s" s="10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="11">
+        <v>101</v>
+      </c>
+      <c r="B49" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C49" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D49" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 53. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E49" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F49" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G49" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:53</t>
+        </is>
+      </c>
+      <c r="H49" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I49" t="s" s="11">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="10">
+        <v>103</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D50" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 56. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E50" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F50" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G50" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:56</t>
+        </is>
+      </c>
+      <c r="H50" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I50" t="s" s="10">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="11">
+        <v>105</v>
+      </c>
+      <c r="B51" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C51" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D51" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 56. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E51" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F51" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G51" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:56</t>
+        </is>
+      </c>
+      <c r="H51" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I51" t="s" s="11">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="10">
+        <v>107</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="D52" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'license_scanner.py' at line 59. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E52" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F52" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G52" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:59</t>
+        </is>
+      </c>
+      <c r="H52" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I52" t="s" s="10">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="11">
+        <v>109</v>
+      </c>
+      <c r="B53" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C53" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="D53" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 65. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E53" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F53" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G53" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:65</t>
+        </is>
+      </c>
+      <c r="H53" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I53" t="s" s="11">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="10">
+        <v>111</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="D54" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 68. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E54" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F54" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G54" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:68</t>
+        </is>
+      </c>
+      <c r="H54" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I54" t="s" s="10">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="11">
+        <v>113</v>
+      </c>
+      <c r="B55" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C55" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D55" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 75. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E55" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F55" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G55" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:75</t>
+        </is>
+      </c>
+      <c r="H55" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I55" t="s" s="11">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="10">
+        <v>115</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D56" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 76. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E56" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F56" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G56" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:76</t>
+        </is>
+      </c>
+      <c r="H56" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I56" t="s" s="10">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="11">
+        <v>117</v>
+      </c>
+      <c r="B57" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C57" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D57" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 77. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E57" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F57" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G57" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:77</t>
+        </is>
+      </c>
+      <c r="H57" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I57" t="s" s="11">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="10">
+        <v>119</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D58" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 78. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E58" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F58" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G58" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:78</t>
+        </is>
+      </c>
+      <c r="H58" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I58" t="s" s="10">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="11">
+        <v>121</v>
+      </c>
+      <c r="B59" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C59" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D59" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 79. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E59" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F59" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G59" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:79</t>
+        </is>
+      </c>
+      <c r="H59" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I59" t="s" s="11">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="10">
+        <v>123</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D60" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E60" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F60" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G60" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:21</t>
+        </is>
+      </c>
+      <c r="H60" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I60" t="s" s="10">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="11">
+        <v>125</v>
+      </c>
+      <c r="B61" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C61" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D61" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 23. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E61" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F61" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G61" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:23</t>
+        </is>
+      </c>
+      <c r="H61" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I61" t="s" s="11">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="10">
+        <v>127</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D62" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 34. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E62" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F62" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G62" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:34</t>
+        </is>
+      </c>
+      <c r="H62" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I62" t="s" s="10">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="11">
+        <v>129</v>
+      </c>
+      <c r="B63" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C63" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D63" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 39. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E63" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F63" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G63" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:39</t>
+        </is>
+      </c>
+      <c r="H63" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I63" t="s" s="11">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="10">
+        <v>131</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D64" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 40. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E64" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F64" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G64" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:40</t>
+        </is>
+      </c>
+      <c r="H64" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I64" t="s" s="10">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="11">
+        <v>133</v>
+      </c>
+      <c r="B65" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C65" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D65" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E65" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F65" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G65" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:47</t>
+        </is>
+      </c>
+      <c r="H65" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I65" t="s" s="11">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="10">
+        <v>135</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D66" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E66" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F66" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G66" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:61</t>
+        </is>
+      </c>
+      <c r="H66" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I66" t="s" s="10">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="11">
+        <v>137</v>
+      </c>
+      <c r="B67" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C67" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D67" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 62. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E67" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F67" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G67" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:62</t>
+        </is>
+      </c>
+      <c r="H67" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I67" t="s" s="11">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="10">
+        <v>139</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D68" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 70. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E68" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F68" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G68" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:70</t>
+        </is>
+      </c>
+      <c r="H68" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I68" t="s" s="10">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="11">
+        <v>141</v>
+      </c>
+      <c r="B69" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C69" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D69" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 100. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E69" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F69" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G69" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:100</t>
+        </is>
+      </c>
+      <c r="H69" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I69" t="s" s="11">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="10">
+        <v>143</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D70" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 112. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E70" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F70" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G70" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:112</t>
+        </is>
+      </c>
+      <c r="H70" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I70" t="s" s="10">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="11">
+        <v>145</v>
+      </c>
+      <c r="B71" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C71" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D71" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 113. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E71" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F71" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G71" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:113</t>
+        </is>
+      </c>
+      <c r="H71" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I71" t="s" s="11">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="10">
+        <v>147</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D72" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E72" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F72" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G72" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+        </is>
+      </c>
+      <c r="H72" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I72" t="s" s="10">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="11">
+        <v>149</v>
+      </c>
+      <c r="B73" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C73" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D73" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E73" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F73" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G73" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+        </is>
+      </c>
+      <c r="H73" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I73" t="s" s="11">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="10">
+        <v>151</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C74" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D74" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E74" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F74" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G74" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+        </is>
+      </c>
+      <c r="H74" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I74" t="s" s="10">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="11">
+        <v>153</v>
+      </c>
+      <c r="B75" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C75" t="s" s="4">
+        <v>55</v>
+      </c>
+      <c r="D75" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E75" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F75" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G75" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+        </is>
+      </c>
+      <c r="H75" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I75" t="s" s="11">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="10">
+        <v>155</v>
+      </c>
+      <c r="B76" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C76" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="D76" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E76" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F76" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G76" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+        </is>
+      </c>
+      <c r="H76" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I76" t="s" s="10">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="11">
+        <v>157</v>
+      </c>
+      <c r="B77" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C77" t="s" s="4">
+        <v>45</v>
+      </c>
+      <c r="D77" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 30. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E77" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F77" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G77" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:30</t>
+        </is>
+      </c>
+      <c r="H77" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I77" t="s" s="11">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="10">
+        <v>159</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C78" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D78" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 31. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E78" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F78" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G78" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:31</t>
+        </is>
+      </c>
+      <c r="H78" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I78" t="s" s="10">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="11">
+        <v>161</v>
+      </c>
+      <c r="B79" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C79" t="s" s="4">
+        <v>45</v>
+      </c>
+      <c r="D79" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 32. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E79" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F79" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G79" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:32</t>
+        </is>
+      </c>
+      <c r="H79" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I79" t="s" s="11">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="10">
+        <v>163</v>
+      </c>
+      <c r="B80" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C80" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D80" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 34. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E80" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F80" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G80" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:34</t>
+        </is>
+      </c>
+      <c r="H80" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I80" t="s" s="10">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="11">
+        <v>165</v>
+      </c>
+      <c r="B81" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C81" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D81" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E81" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F81" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G81" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:35</t>
+        </is>
+      </c>
+      <c r="H81" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I81" t="s" s="11">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="10">
+        <v>167</v>
+      </c>
+      <c r="B82" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C82" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D82" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 36. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E82" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F82" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G82" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:36</t>
+        </is>
+      </c>
+      <c r="H82" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I82" t="s" s="10">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="11">
+        <v>169</v>
+      </c>
+      <c r="B83" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C83" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D83" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 38. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E83" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F83" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G83" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:38</t>
+        </is>
+      </c>
+      <c r="H83" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I83" t="s" s="11">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="10">
+        <v>171</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C84" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D84" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 39. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E84" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F84" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G84" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:39</t>
+        </is>
+      </c>
+      <c r="H84" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I84" t="s" s="10">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="11">
+        <v>173</v>
+      </c>
+      <c r="B85" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C85" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="D85" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 40. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E85" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F85" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="G85" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:40</t>
+        </is>
+      </c>
+      <c r="H85" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I85" t="s" s="11">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="10">
+        <v>175</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C86" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="D86" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 42. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E86" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F86" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G86" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:42</t>
+        </is>
+      </c>
+      <c r="H86" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I86" t="s" s="10">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="11">
+        <v>177</v>
+      </c>
+      <c r="B87" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C87" t="s" s="4">
+        <v>55</v>
+      </c>
+      <c r="D87" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 43. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E87" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F87" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G87" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:43</t>
+        </is>
+      </c>
+      <c r="H87" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I87" t="s" s="11">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="10">
+        <v>179</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C88" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="D88" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 44. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E88" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F88" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G88" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:44</t>
+        </is>
+      </c>
+      <c r="H88" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I88" t="s" s="10">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="11">
+        <v>181</v>
+      </c>
+      <c r="B89" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C89" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="D89" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 46. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E89" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F89" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G89" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:46</t>
+        </is>
+      </c>
+      <c r="H89" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I89" t="s" s="11">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="10">
+        <v>183</v>
+      </c>
+      <c r="B90" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C90" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="D90" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E90" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F90" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G90" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:47</t>
+        </is>
+      </c>
+      <c r="H90" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I90" t="s" s="10">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="11">
+        <v>185</v>
+      </c>
+      <c r="B91" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C91" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="D91" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 48. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E91" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F91" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G91" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:48</t>
+        </is>
+      </c>
+      <c r="H91" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I91" t="s" s="11">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="10">
+        <v>187</v>
+      </c>
+      <c r="B92" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C92" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D92" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 57. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E92" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F92" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G92" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:57</t>
+        </is>
+      </c>
+      <c r="H92" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I92" t="s" s="10">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="11">
+        <v>189</v>
+      </c>
+      <c r="B93" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C93" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D93" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 60. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E93" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F93" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G93" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:60</t>
+        </is>
+      </c>
+      <c r="H93" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I93" t="s" s="11">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="10">
+        <v>191</v>
+      </c>
+      <c r="B94" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C94" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="D94" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E94" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F94" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G94" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:61</t>
+        </is>
+      </c>
+      <c r="H94" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I94" t="s" s="10">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="11">
+        <v>193</v>
+      </c>
+      <c r="B95" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C95" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D95" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 71. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E95" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F95" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G95" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:71</t>
+        </is>
+      </c>
+      <c r="H95" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I95" t="s" s="11">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="10">
+        <v>195</v>
+      </c>
+      <c r="B96" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C96" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D96" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 72. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E96" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F96" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G96" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:72</t>
+        </is>
+      </c>
+      <c r="H96" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I96" t="s" s="10">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="11">
+        <v>197</v>
+      </c>
+      <c r="B97" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C97" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D97" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 73. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E97" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F97" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G97" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:73</t>
+        </is>
+      </c>
+      <c r="H97" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I97" t="s" s="11">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B98" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C98" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D98" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 79. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E98" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F98" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G98" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:79</t>
+        </is>
+      </c>
+      <c r="H98" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I98" t="s" s="10">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="11">
+        <v>201</v>
+      </c>
+      <c r="B99" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C99" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D99" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 101. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E99" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F99" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G99" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:101</t>
+        </is>
+      </c>
+      <c r="H99" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I99" t="s" s="11">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="10">
+        <v>203</v>
+      </c>
+      <c r="B100" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C100" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D100" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 105. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E100" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F100" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G100" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:105</t>
+        </is>
+      </c>
+      <c r="H100" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I100" t="s" s="10">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="11">
+        <v>205</v>
+      </c>
+      <c r="B101" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C101" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D101" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 109. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E101" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F101" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G101" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:109</t>
+        </is>
+      </c>
+      <c r="H101" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I101" t="s" s="11">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="10">
+        <v>207</v>
+      </c>
+      <c r="B102" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C102" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D102" t="inlineStr" s="14">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 113. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E102" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F102" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="G102" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:113</t>
+        </is>
+      </c>
+      <c r="H102" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I102" t="s" s="10">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="11">
+        <v>209</v>
+      </c>
+      <c r="B103" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C103" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="D103" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 117. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E103" t="s" s="11">
+        <v>283</v>
+      </c>
+      <c r="F103" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G103" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:117</t>
+        </is>
+      </c>
+      <c r="H103" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I103" t="s" s="11">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="10">
+        <v>211</v>
+      </c>
+      <c r="B104" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="C104" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="D104" t="inlineStr" s="14">
+        <is>
+          <t>The primary audit log (ai_scanner.log) is missing. CERT-In mandates active logging for incident readiness and forensic timelines.</t>
+        </is>
+      </c>
+      <c r="E104" t="s" s="10">
+        <v>283</v>
+      </c>
+      <c r="F104" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="G104" t="inlineStr" s="14">
+        <is>
+          <t>ai_scanner.log</t>
+        </is>
+      </c>
+      <c r="H104" s="10">
+        <v>90.0</v>
+      </c>
+      <c r="I104" t="s" s="10">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2447,107 +8074,107 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>114</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" t="s" s="1">
-        <v>115</v>
+        <v>285</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>116</v>
+        <v>286</v>
       </c>
       <c r="C3" t="s" s="1">
-        <v>117</v>
+        <v>287</v>
       </c>
       <c r="D3" t="s" s="1">
-        <v>118</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>119</v>
+        <v>289</v>
       </c>
       <c r="B4" t="s" s="10">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="C4" s="10">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s" s="8">
-        <v>121</v>
+        <v>52</v>
+      </c>
+      <c r="D4" t="s" s="6">
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="4">
-        <v>122</v>
+        <v>291</v>
       </c>
       <c r="B5" t="s" s="11">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="C5" s="11">
-        <v>55</v>
-      </c>
-      <c r="D5" t="s" s="6">
-        <v>22</v>
+        <v>78</v>
+      </c>
+      <c r="D5" t="s" s="5">
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>123</v>
+        <v>292</v>
       </c>
       <c r="B6" t="s" s="10">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="C6" s="10">
-        <v>39</v>
-      </c>
-      <c r="D6" t="s" s="7">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="D6" t="s" s="6">
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="4">
-        <v>124</v>
+        <v>293</v>
       </c>
       <c r="B7" t="s" s="11">
-        <v>125</v>
+        <v>294</v>
       </c>
       <c r="C7" s="11">
         <v>0</v>
       </c>
       <c r="D7" t="s" s="8">
-        <v>121</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>126</v>
+        <v>296</v>
       </c>
       <c r="B8" t="s" s="10">
-        <v>127</v>
+        <v>297</v>
       </c>
       <c r="C8" s="10">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s" s="8">
-        <v>121</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9"/>
     <row r="10">
       <c r="A10" t="s" s="9">
-        <v>128</v>
+        <v>298</v>
       </c>
       <c r="B10" s="10">
-        <v>48.9</v>
+        <v>68.7</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>95</v>
+        <v>265</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>95</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -2563,31 +8190,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>110</v>
+        <v>280</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>129</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>52</v>
+        <v>283</v>
       </c>
       <c r="B2" s="10">
-        <v>10</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="4">
-        <v>113</v>
+        <v>223</v>
       </c>
       <c r="B3" s="11">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>112</v>
+        <v>282</v>
       </c>
       <c r="B4" s="10">
         <v>3</v>
@@ -2595,7 +8222,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="4">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="B5" s="11">
         <v>1</v>
@@ -2617,30 +8244,38 @@
         <v>5</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>129</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="6">
-        <v>22</v>
-      </c>
-      <c r="B2" s="11">
-        <v>7</v>
+      <c r="A2" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="B2" s="10">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s" s="7">
-        <v>53</v>
-      </c>
-      <c r="B3" s="10">
+      <c r="A3" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="B3" s="11">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="B4" s="10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="8">
         <v>11</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="8">
-        <v>11</v>
-      </c>
-      <c r="B4" s="10">
+      <c r="B5" s="10">
         <v>4</v>
       </c>
     </row>

--- a/System Scanner/test_report.xlsx
+++ b/System Scanner/test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>621d65fa</t>
+    <t>2f386a55</t>
   </si>
   <si>
     <t>SystemScanner</t>
@@ -54,19 +54,19 @@
     <t>INFO</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.693029</t>
-  </si>
-  <si>
-    <t>739f9089</t>
+    <t>2026-06-22T17:44:21.750509</t>
+  </si>
+  <si>
+    <t>cd809eaf</t>
   </si>
   <si>
     <t>GPU Detected: NVIDIA GeForce GTX 1650</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.825571</t>
-  </si>
-  <si>
-    <t>694af5c9</t>
+    <t>2026-06-22T17:44:21.908236</t>
+  </si>
+  <si>
+    <t>78625e0f</t>
   </si>
   <si>
     <t>APIScanner</t>
@@ -78,58 +78,58 @@
     <t>HIGH</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.914935</t>
-  </si>
-  <si>
-    <t>bff05453</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.915071</t>
-  </si>
-  <si>
-    <t>2b0cc64d</t>
+    <t>2026-06-22T17:44:21.993095</t>
+  </si>
+  <si>
+    <t>ebb267d7</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.993233</t>
+  </si>
+  <si>
+    <t>00cbefd3</t>
   </si>
   <si>
     <t>Exposed Generic API Key/Token</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.915303</t>
-  </si>
-  <si>
-    <t>06fb4b7e</t>
+    <t>2026-06-22T17:44:21.993483</t>
+  </si>
+  <si>
+    <t>4e0e1a9f</t>
   </si>
   <si>
     <t>Exposed AWS Access Key ID</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.915321</t>
-  </si>
-  <si>
-    <t>f6305a9d</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.915589</t>
-  </si>
-  <si>
-    <t>a4f1252d</t>
+    <t>2026-06-22T17:44:21.993508</t>
+  </si>
+  <si>
+    <t>b22be501</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.993768</t>
+  </si>
+  <si>
+    <t>a7647b62</t>
   </si>
   <si>
     <t>Environment Variable: ANTIGRAVITY_CSRF_TOKEN</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.985053</t>
-  </si>
-  <si>
-    <t>0d12afc6</t>
+    <t>2026-06-22T17:44:22.046695</t>
+  </si>
+  <si>
+    <t>318ca722</t>
   </si>
   <si>
     <t>Environment Variable: GEMINI_API_KEY</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.985204</t>
-  </si>
-  <si>
-    <t>484853bc</t>
+    <t>2026-06-22T17:44:22.046753</t>
+  </si>
+  <si>
+    <t>3c3c0ec5</t>
   </si>
   <si>
     <t>LicenseScanner</t>
@@ -138,10 +138,10 @@
     <t>Code Snippet: GPL Mention</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.276234</t>
-  </si>
-  <si>
-    <t>6b782d46</t>
+    <t>2026-06-22T17:44:21.335268</t>
+  </si>
+  <si>
+    <t>23ad3913</t>
   </si>
   <si>
     <t>Code Snippet: LGPL Mention</t>
@@ -150,31 +150,31 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.349600</t>
-  </si>
-  <si>
-    <t>fc2c4147</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.352564</t>
-  </si>
-  <si>
-    <t>855ac586</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.353709</t>
-  </si>
-  <si>
-    <t>6da6a129</t>
+    <t>2026-06-22T17:44:21.411285</t>
+  </si>
+  <si>
+    <t>a535e19d</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.412371</t>
+  </si>
+  <si>
+    <t>196e7b5e</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.414709</t>
+  </si>
+  <si>
+    <t>8883157f</t>
   </si>
   <si>
     <t>Code Snippet: Proprietary Mention</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.356148</t>
-  </si>
-  <si>
-    <t>e938f0b0</t>
+    <t>2026-06-22T17:44:21.417472</t>
+  </si>
+  <si>
+    <t>6c60c6f1</t>
   </si>
   <si>
     <t>Code Snippet: AGPL Mention</t>
@@ -183,595 +183,595 @@
     <t>CRITICAL</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.357226</t>
-  </si>
-  <si>
-    <t>7099069d</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.359731</t>
-  </si>
-  <si>
-    <t>6277edc9</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.361675</t>
-  </si>
-  <si>
-    <t>73494172</t>
+    <t>2026-06-22T17:44:21.418732</t>
+  </si>
+  <si>
+    <t>837b4feb</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.420319</t>
+  </si>
+  <si>
+    <t>27b0bc89</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.423129</t>
+  </si>
+  <si>
+    <t>2cd0d8c1</t>
   </si>
   <si>
     <t>Code Snippet: Polyform Shield Mention</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.364487</t>
-  </si>
-  <si>
-    <t>2a067f79</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.365678</t>
-  </si>
-  <si>
-    <t>217936f6</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.369346</t>
-  </si>
-  <si>
-    <t>3a99e860</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.370559</t>
-  </si>
-  <si>
-    <t>c7237721</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.374586</t>
-  </si>
-  <si>
-    <t>a62fa91f</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.377563</t>
-  </si>
-  <si>
-    <t>150c35cb</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.378968</t>
-  </si>
-  <si>
-    <t>e3d1faea</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.380292</t>
-  </si>
-  <si>
-    <t>480eec97</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.381911</t>
-  </si>
-  <si>
-    <t>1979e2f8</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.383212</t>
-  </si>
-  <si>
-    <t>ee0559e3</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.386470</t>
-  </si>
-  <si>
-    <t>11c47675</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.390492</t>
-  </si>
-  <si>
-    <t>8cdcba86</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.391765</t>
-  </si>
-  <si>
-    <t>b43573a9</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.394360</t>
-  </si>
-  <si>
-    <t>5629e97f</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.408613</t>
-  </si>
-  <si>
-    <t>a348684b</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.409605</t>
-  </si>
-  <si>
-    <t>6d92dbf6</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.419670</t>
-  </si>
-  <si>
-    <t>bacac7cf</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.427278</t>
-  </si>
-  <si>
-    <t>0f3a6895</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.432709</t>
-  </si>
-  <si>
-    <t>bb9b3e11</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.440555</t>
-  </si>
-  <si>
-    <t>1bd2aa23</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.448245</t>
-  </si>
-  <si>
-    <t>519c62e4</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.483415</t>
-  </si>
-  <si>
-    <t>02c12fe6</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.511451</t>
-  </si>
-  <si>
-    <t>141998f3</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.514270</t>
-  </si>
-  <si>
-    <t>9cb539f7</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.522749</t>
-  </si>
-  <si>
-    <t>7411485e</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.528115</t>
-  </si>
-  <si>
-    <t>874f338f</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.558319</t>
-  </si>
-  <si>
-    <t>4286c3d9</t>
+    <t>2026-06-22T17:44:21.425631</t>
+  </si>
+  <si>
+    <t>73cb5ed4</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.427821</t>
+  </si>
+  <si>
+    <t>65599c08</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.432251</t>
+  </si>
+  <si>
+    <t>2b74ce7f</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.435135</t>
+  </si>
+  <si>
+    <t>8aa6dd08</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.436201</t>
+  </si>
+  <si>
+    <t>f9588ac6</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.437857</t>
+  </si>
+  <si>
+    <t>92806092</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.438787</t>
+  </si>
+  <si>
+    <t>2723c8ca</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.440377</t>
+  </si>
+  <si>
+    <t>57c4332f</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.446530</t>
+  </si>
+  <si>
+    <t>96cd3abb</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.448806</t>
+  </si>
+  <si>
+    <t>ae474ef7</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.451910</t>
+  </si>
+  <si>
+    <t>84e36da0</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.453189</t>
+  </si>
+  <si>
+    <t>fec35c58</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.456388</t>
+  </si>
+  <si>
+    <t>db15c77c</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.462305</t>
+  </si>
+  <si>
+    <t>d1cfb211</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.480937</t>
+  </si>
+  <si>
+    <t>1d22435d</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.484208</t>
+  </si>
+  <si>
+    <t>230f9f09</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.486634</t>
+  </si>
+  <si>
+    <t>98bcf835</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.490041</t>
+  </si>
+  <si>
+    <t>d255d64f</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.490984</t>
+  </si>
+  <si>
+    <t>ab36ebf6</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.493973</t>
+  </si>
+  <si>
+    <t>6f1a6f48</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.500817</t>
+  </si>
+  <si>
+    <t>b6c681ed</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.511420</t>
+  </si>
+  <si>
+    <t>08eae7df</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.518336</t>
+  </si>
+  <si>
+    <t>d9e856d2</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.521089</t>
+  </si>
+  <si>
+    <t>2d71eabd</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.526974</t>
+  </si>
+  <si>
+    <t>7731c89f</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.548249</t>
+  </si>
+  <si>
+    <t>ef84a9d7</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.572524</t>
+  </si>
+  <si>
+    <t>4d3005e5</t>
   </si>
   <si>
     <t>Code License: MIT Header</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.886284</t>
-  </si>
-  <si>
-    <t>18a985af</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.910498</t>
-  </si>
-  <si>
-    <t>d0a5ae06</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.911890</t>
-  </si>
-  <si>
-    <t>56e1f6a8</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.918518</t>
-  </si>
-  <si>
-    <t>5469d8d8</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.923428</t>
-  </si>
-  <si>
-    <t>47a94b81</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.931369</t>
-  </si>
-  <si>
-    <t>0c2a1965</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.934423</t>
-  </si>
-  <si>
-    <t>1193f5f1</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.941335</t>
-  </si>
-  <si>
-    <t>58304f3f</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.949409</t>
-  </si>
-  <si>
-    <t>8092ba30</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.958361</t>
-  </si>
-  <si>
-    <t>19deb94e</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.964497</t>
-  </si>
-  <si>
-    <t>4bd67552</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.972280</t>
-  </si>
-  <si>
-    <t>c8855777</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.978470</t>
-  </si>
-  <si>
-    <t>38249650</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.983946</t>
-  </si>
-  <si>
-    <t>91ab25bb</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.985918</t>
-  </si>
-  <si>
-    <t>6ee1edb9</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.988660</t>
-  </si>
-  <si>
-    <t>1fcfe719</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.990279</t>
-  </si>
-  <si>
-    <t>6f8b725a</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.992214</t>
-  </si>
-  <si>
-    <t>3a8102f8</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.993033</t>
-  </si>
-  <si>
-    <t>52b9bf4e</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.993757</t>
-  </si>
-  <si>
-    <t>76f66462</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.994528</t>
-  </si>
-  <si>
-    <t>bc9f60f7</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.994980</t>
-  </si>
-  <si>
-    <t>2f31f3a4</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.995744</t>
-  </si>
-  <si>
-    <t>814c8002</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.996109</t>
-  </si>
-  <si>
-    <t>7ed37d2a</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.262761</t>
-  </si>
-  <si>
-    <t>109307b5</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.263559</t>
-  </si>
-  <si>
-    <t>05e0bb5d</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.265032</t>
-  </si>
-  <si>
-    <t>ac0f4ab8</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.265903</t>
-  </si>
-  <si>
-    <t>0e0912da</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.266620</t>
-  </si>
-  <si>
-    <t>4968c85e</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.267541</t>
-  </si>
-  <si>
-    <t>78eea0f6</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.269005</t>
-  </si>
-  <si>
-    <t>80e4ae1a</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.269730</t>
-  </si>
-  <si>
-    <t>d49d42d3</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.270569</t>
-  </si>
-  <si>
-    <t>fcace28d</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.272295</t>
-  </si>
-  <si>
-    <t>2613d132</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.273768</t>
-  </si>
-  <si>
-    <t>0d24cd71</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.274525</t>
-  </si>
-  <si>
-    <t>640080ec</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.279490</t>
-  </si>
-  <si>
-    <t>36021978</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.280834</t>
-  </si>
-  <si>
-    <t>662ef1e1</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.281642</t>
-  </si>
-  <si>
-    <t>24c4d930</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.282836</t>
-  </si>
-  <si>
-    <t>f4fc978a</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.283567</t>
-  </si>
-  <si>
-    <t>ff491805</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.284521</t>
-  </si>
-  <si>
-    <t>e4678804</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.285176</t>
-  </si>
-  <si>
-    <t>13045dbf</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.286320</t>
-  </si>
-  <si>
-    <t>f67f945f</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.287270</t>
-  </si>
-  <si>
-    <t>23db47ef</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.288104</t>
-  </si>
-  <si>
-    <t>51f8a23d</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.288783</t>
-  </si>
-  <si>
-    <t>dac02a94</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.290097</t>
-  </si>
-  <si>
-    <t>eabee9b4</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.290766</t>
-  </si>
-  <si>
-    <t>1524ddbe</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.291519</t>
-  </si>
-  <si>
-    <t>a2cacc45</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.292167</t>
-  </si>
-  <si>
-    <t>e86f50ca</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.293082</t>
-  </si>
-  <si>
-    <t>b032d057</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.294483</t>
-  </si>
-  <si>
-    <t>e1261aa8</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.295431</t>
-  </si>
-  <si>
-    <t>397bce3d</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.295842</t>
-  </si>
-  <si>
-    <t>b00745bb</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.296530</t>
-  </si>
-  <si>
-    <t>4e1039a1</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.297313</t>
-  </si>
-  <si>
-    <t>1ce9bbe0</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.298103</t>
-  </si>
-  <si>
-    <t>db0c146d</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.298771</t>
-  </si>
-  <si>
-    <t>2dcba38c</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.299551</t>
-  </si>
-  <si>
-    <t>292c736b</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.300233</t>
-  </si>
-  <si>
-    <t>d7faa8df</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.300807</t>
-  </si>
-  <si>
-    <t>c42f3b69</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.301611</t>
-  </si>
-  <si>
-    <t>ce20fc31</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.302943</t>
-  </si>
-  <si>
-    <t>a64a9f0d</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.303661</t>
-  </si>
-  <si>
-    <t>8a6a6ac4</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.304289</t>
-  </si>
-  <si>
-    <t>d4bac4e7</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.304820</t>
-  </si>
-  <si>
-    <t>ce2066ee</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:52.305650</t>
+    <t>2026-06-22T17:44:21.897827</t>
+  </si>
+  <si>
+    <t>34676d8c</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.920866</t>
+  </si>
+  <si>
+    <t>99e0aa92</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.932811</t>
+  </si>
+  <si>
+    <t>8a37d963</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.945280</t>
+  </si>
+  <si>
+    <t>5bc277a3</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.955175</t>
+  </si>
+  <si>
+    <t>87c6818a</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.964452</t>
+  </si>
+  <si>
+    <t>f5b1dfb0</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.983154</t>
+  </si>
+  <si>
+    <t>9f997aa1</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.991817</t>
+  </si>
+  <si>
+    <t>0ca6e80f</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.998795</t>
+  </si>
+  <si>
+    <t>909bc706</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.001533</t>
+  </si>
+  <si>
+    <t>7c0a1673</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.009128</t>
+  </si>
+  <si>
+    <t>7bb442c2</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.015160</t>
+  </si>
+  <si>
+    <t>b9e448b3</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.022310</t>
+  </si>
+  <si>
+    <t>762f0fa2</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.031017</t>
+  </si>
+  <si>
+    <t>2d879644</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.034385</t>
+  </si>
+  <si>
+    <t>8cca4304</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.041388</t>
+  </si>
+  <si>
+    <t>552ba3e5</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.045962</t>
+  </si>
+  <si>
+    <t>b0e2cf5c</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.047131</t>
+  </si>
+  <si>
+    <t>b4e30e7f</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.047700</t>
+  </si>
+  <si>
+    <t>464b9b26</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.048365</t>
+  </si>
+  <si>
+    <t>3568243e</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.049051</t>
+  </si>
+  <si>
+    <t>0cafba22</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.049909</t>
+  </si>
+  <si>
+    <t>e647d65b</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.050315</t>
+  </si>
+  <si>
+    <t>6abb968f</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.050968</t>
+  </si>
+  <si>
+    <t>4d39f728</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.637813</t>
+  </si>
+  <si>
+    <t>89e12956</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.657698</t>
+  </si>
+  <si>
+    <t>361a4f40</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.670977</t>
+  </si>
+  <si>
+    <t>68e10400</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.683954</t>
+  </si>
+  <si>
+    <t>6b7d86dc</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.690332</t>
+  </si>
+  <si>
+    <t>4d38444d</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.704361</t>
+  </si>
+  <si>
+    <t>b6fac91d</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.718143</t>
+  </si>
+  <si>
+    <t>d37f8381</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.727554</t>
+  </si>
+  <si>
+    <t>c60950b2</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.737104</t>
+  </si>
+  <si>
+    <t>95951a9d</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.761326</t>
+  </si>
+  <si>
+    <t>4881a3de</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.774091</t>
+  </si>
+  <si>
+    <t>0f8d2ca8</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.781688</t>
+  </si>
+  <si>
+    <t>726b3abc</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.862530</t>
+  </si>
+  <si>
+    <t>de32dbe4</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.874251</t>
+  </si>
+  <si>
+    <t>5458412f</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.889122</t>
+  </si>
+  <si>
+    <t>f0512153</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.899820</t>
+  </si>
+  <si>
+    <t>34fb9f31</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.910980</t>
+  </si>
+  <si>
+    <t>e4293771</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.932282</t>
+  </si>
+  <si>
+    <t>89f6e2f0</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.944730</t>
+  </si>
+  <si>
+    <t>95c1a2d6</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.960047</t>
+  </si>
+  <si>
+    <t>54e9fad1</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.978008</t>
+  </si>
+  <si>
+    <t>342ec8e2</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:22.993786</t>
+  </si>
+  <si>
+    <t>b07aadab</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.009155</t>
+  </si>
+  <si>
+    <t>c5dc52fa</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.021112</t>
+  </si>
+  <si>
+    <t>0bd2cfc8</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.034618</t>
+  </si>
+  <si>
+    <t>b8af0e90</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.048953</t>
+  </si>
+  <si>
+    <t>5f2c0c6d</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.062511</t>
+  </si>
+  <si>
+    <t>4cd80535</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.080733</t>
+  </si>
+  <si>
+    <t>aee8b0fb</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.096194</t>
+  </si>
+  <si>
+    <t>dd0c3304</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.111226</t>
+  </si>
+  <si>
+    <t>a1f2e96a</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.126370</t>
+  </si>
+  <si>
+    <t>fcf3e196</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.142257</t>
+  </si>
+  <si>
+    <t>05adb035</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.157365</t>
+  </si>
+  <si>
+    <t>cdaf12f2</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.170192</t>
+  </si>
+  <si>
+    <t>f9dcaa88</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.189380</t>
+  </si>
+  <si>
+    <t>9a3a8c13</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.205339</t>
+  </si>
+  <si>
+    <t>a60accc2</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.221553</t>
+  </si>
+  <si>
+    <t>83eeb194</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.238651</t>
+  </si>
+  <si>
+    <t>9766cd10</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.253736</t>
+  </si>
+  <si>
+    <t>d7988c26</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.273415</t>
+  </si>
+  <si>
+    <t>cdeace7a</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.286759</t>
+  </si>
+  <si>
+    <t>69d9b3a8</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.302394</t>
+  </si>
+  <si>
+    <t>ef0e2c01</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.326042</t>
+  </si>
+  <si>
+    <t>d07d122b</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:23.395089</t>
   </si>
   <si>
     <t>Package / Library</t>
@@ -780,7 +780,7 @@
     <t>Location / Source</t>
   </si>
   <si>
-    <t>a6decc34</t>
+    <t>50b7f811</t>
   </si>
   <si>
     <t>PackageScanner</t>
@@ -789,43 +789,43 @@
     <t>[UNVERIFIED] Package: google-generativeai (0.8.6)</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:52.211464</t>
-  </si>
-  <si>
-    <t>3bb4513f</t>
+    <t>2026-06-22T17:44:22.282197</t>
+  </si>
+  <si>
+    <t>61969347</t>
   </si>
   <si>
     <t>[UNVERIFIED] Package: huggingface_hub (1.14.0)</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:52.219334</t>
-  </si>
-  <si>
-    <t>efe833ba</t>
+    <t>2026-06-22T17:44:22.287109</t>
+  </si>
+  <si>
+    <t>a35e29b1</t>
   </si>
   <si>
     <t>[UNVERIFIED] Package: openai (2.36.0)</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:52.226121</t>
-  </si>
-  <si>
-    <t>6aa4b057</t>
+    <t>2026-06-22T17:44:22.292259</t>
+  </si>
+  <si>
+    <t>685e9158</t>
   </si>
   <si>
     <t>[UNVERIFIED] Package: torch (2.11.0)</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:52.236044</t>
-  </si>
-  <si>
-    <t>6743be2a</t>
+    <t>2026-06-22T17:44:22.299024</t>
+  </si>
+  <si>
+    <t>2c288cbe</t>
   </si>
   <si>
     <t>[UNVERIFIED] Package: transformers (5.8.0)</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:52.249129</t>
+    <t>2026-06-22T17:44:22.304537</t>
   </si>
   <si>
     <t>AI Model / Agent / Runtime</t>
@@ -837,7 +837,7 @@
     <t>Location / Endpoint</t>
   </si>
   <si>
-    <t>25eb3663</t>
+    <t>f0146d9c</t>
   </si>
   <si>
     <t>Copilot Agent — Registry Configuration Detected</t>
@@ -846,19 +846,19 @@
     <t>AI Agent</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.991685</t>
-  </si>
-  <si>
-    <t>95d34f3f</t>
+    <t>2026-06-22T17:44:22.050731</t>
+  </si>
+  <si>
+    <t>2fd56bad</t>
   </si>
   <si>
     <t>Codex Agent — Registry Configuration Detected</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.991716</t>
-  </si>
-  <si>
-    <t>5e249421</t>
+    <t>2026-06-22T17:44:22.050747</t>
+  </si>
+  <si>
+    <t>6bb85034</t>
   </si>
   <si>
     <t>ProcessScanner</t>
@@ -870,127 +870,127 @@
     <t>LLM Runtime</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:54.692860</t>
-  </si>
-  <si>
-    <t>b8f40051</t>
+    <t>2026-06-22T17:44:28.859001</t>
+  </si>
+  <si>
+    <t>a572c229</t>
   </si>
   <si>
     <t>Antigravity (PID: 5080)</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:56.834913</t>
-  </si>
-  <si>
-    <t>dcbb8c7f</t>
+    <t>2026-06-22T17:44:32.270723</t>
+  </si>
+  <si>
+    <t>446197da</t>
   </si>
   <si>
     <t>Antigravity (PID: 12880)</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:58.924741</t>
-  </si>
-  <si>
-    <t>f2bf2584</t>
+    <t>2026-06-22T17:44:34.335937</t>
+  </si>
+  <si>
+    <t>909b26d1</t>
   </si>
   <si>
     <t>Antigravity (PID: 14808)</t>
   </si>
   <si>
-    <t>2026-06-22T16:59:00.936267</t>
-  </si>
-  <si>
-    <t>a86c4e81</t>
+    <t>2026-06-22T17:44:36.350058</t>
+  </si>
+  <si>
+    <t>e9ad8a04</t>
   </si>
   <si>
     <t>Antigravity (PID: 16908)</t>
   </si>
   <si>
-    <t>2026-06-22T16:59:02.906489</t>
-  </si>
-  <si>
-    <t>021d7db7</t>
+    <t>2026-06-22T17:44:38.224089</t>
+  </si>
+  <si>
+    <t>7c06708d</t>
   </si>
   <si>
     <t>Antigravity (PID: 17460)</t>
   </si>
   <si>
-    <t>2026-06-22T16:59:04.982785</t>
-  </si>
-  <si>
-    <t>53c9db59</t>
+    <t>2026-06-22T17:44:40.186993</t>
+  </si>
+  <si>
+    <t>9d63d040</t>
   </si>
   <si>
     <t>Antigravity (PID: 17620)</t>
   </si>
   <si>
-    <t>2026-06-22T16:59:07.144048</t>
-  </si>
-  <si>
-    <t>a2851671</t>
+    <t>2026-06-22T17:44:42.146717</t>
+  </si>
+  <si>
+    <t>29cb2fee</t>
   </si>
   <si>
     <t>Antigravity (PID: 17640)</t>
   </si>
   <si>
-    <t>2026-06-22T16:59:09.151602</t>
-  </si>
-  <si>
-    <t>69be06e3</t>
+    <t>2026-06-22T17:44:43.866428</t>
+  </si>
+  <si>
+    <t>8ffbbd46</t>
   </si>
   <si>
     <t>Antigravity (PID: 17704)</t>
   </si>
   <si>
-    <t>2026-06-22T16:59:11.088370</t>
-  </si>
-  <si>
-    <t>6646f4b4</t>
+    <t>2026-06-22T17:44:45.668886</t>
+  </si>
+  <si>
+    <t>991cfd15</t>
   </si>
   <si>
     <t>Antigravity (PID: 17896)</t>
   </si>
   <si>
-    <t>2026-06-22T16:59:13.058550</t>
-  </si>
-  <si>
-    <t>07b014a8</t>
+    <t>2026-06-22T17:44:47.398422</t>
+  </si>
+  <si>
+    <t>98e943ba</t>
   </si>
   <si>
     <t>Antigravity (PID: 18372)</t>
   </si>
   <si>
-    <t>2026-06-22T16:59:15.047811</t>
-  </si>
-  <si>
-    <t>a491d364</t>
+    <t>2026-06-22T17:44:49.145330</t>
+  </si>
+  <si>
+    <t>d751a7d0</t>
   </si>
   <si>
     <t>Antigravity (PID: 18684)</t>
   </si>
   <si>
-    <t>2026-06-22T16:59:16.997426</t>
-  </si>
-  <si>
-    <t>894209f1</t>
+    <t>2026-06-22T17:44:50.902622</t>
+  </si>
+  <si>
+    <t>eabcdcd1</t>
   </si>
   <si>
     <t>Antigravity (PID: 19180)</t>
   </si>
   <si>
-    <t>2026-06-22T16:59:19.026820</t>
-  </si>
-  <si>
-    <t>f84533ff</t>
+    <t>2026-06-22T17:44:52.750325</t>
+  </si>
+  <si>
+    <t>4ff95aa2</t>
   </si>
   <si>
     <t>Antigravity (PID: 19948)</t>
   </si>
   <si>
-    <t>2026-06-22T16:59:21.079468</t>
-  </si>
-  <si>
-    <t>c1a593a4</t>
+    <t>2026-06-22T17:44:54.492027</t>
+  </si>
+  <si>
+    <t>421c0dab</t>
   </si>
   <si>
     <t>AgentScanner</t>
@@ -999,76 +999,76 @@
     <t>Agent Usage: LangChain Import</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.653289</t>
-  </si>
-  <si>
-    <t>697e8702</t>
+    <t>2026-06-22T17:44:21.595983</t>
+  </si>
+  <si>
+    <t>9e25b330</t>
   </si>
   <si>
     <t>Agent Usage: CrewAI Import</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.670459</t>
-  </si>
-  <si>
-    <t>e66bf209</t>
+    <t>2026-06-22T17:44:21.605384</t>
+  </si>
+  <si>
+    <t>de7080c8</t>
   </si>
   <si>
     <t>Agent Usage: Agent Instantiation</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.707964</t>
-  </si>
-  <si>
-    <t>ab19b4d2</t>
+    <t>2026-06-22T17:44:21.607564</t>
+  </si>
+  <si>
+    <t>0863caec</t>
   </si>
   <si>
     <t>Agent Usage: Crew Instantiation</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.728128</t>
-  </si>
-  <si>
-    <t>c2523b76</t>
+    <t>2026-06-22T17:44:21.628028</t>
+  </si>
+  <si>
+    <t>c3df3405</t>
   </si>
   <si>
     <t>Agent Usage: AssistantAgent Instantiation</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.738541</t>
-  </si>
-  <si>
-    <t>832d6c25</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.753647</t>
-  </si>
-  <si>
-    <t>4adafcc5</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.761946</t>
-  </si>
-  <si>
-    <t>9236c2c2</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.778235</t>
-  </si>
-  <si>
-    <t>70824060</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.798898</t>
-  </si>
-  <si>
-    <t>b1d515a5</t>
-  </si>
-  <si>
-    <t>2026-06-22T16:58:51.878765</t>
-  </si>
-  <si>
-    <t>ba89c3af</t>
+    <t>2026-06-22T17:44:21.657849</t>
+  </si>
+  <si>
+    <t>dd744037</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.706700</t>
+  </si>
+  <si>
+    <t>6599711b</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.728480</t>
+  </si>
+  <si>
+    <t>7f1d6a84</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.748454</t>
+  </si>
+  <si>
+    <t>ecf97914</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.762482</t>
+  </si>
+  <si>
+    <t>01b48c3e</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:44:21.791817</t>
+  </si>
+  <si>
+    <t>04554913</t>
   </si>
   <si>
     <t>RuntimeScanner</t>
@@ -1077,7 +1077,7 @@
     <t>Active LLM Service Port: 8080</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:53.226048</t>
+    <t>2026-06-22T17:44:23.381117</t>
   </si>
   <si>
     <t>AI Discovery Scanner — Scan Summary Report (v1.4.0)</t>
@@ -1092,13 +1092,13 @@
     <t>Scan ID</t>
   </si>
   <si>
-    <t>7dc47cff-d3e</t>
+    <t>4c1c9b41-a4b</t>
   </si>
   <si>
     <t>Scan Timestamp</t>
   </si>
   <si>
-    <t>2026-06-22T16:58:51.122963</t>
+    <t>2026-06-22T17:44:21.190492</t>
   </si>
   <si>
     <t>Hostname</t>
@@ -1170,7 +1170,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-06-22T16:59:21.300863</t>
+    <t>2026-06-22T17:44:54.711631</t>
   </si>
   <si>
     <t>Python Version</t>
@@ -1200,7 +1200,7 @@
     <t>System Memory Availability</t>
   </si>
   <si>
-    <t>Total: 7.6 GB (Available: 0.6 GB)</t>
+    <t>Total: 7.6 GB (Available: 1.0 GB)</t>
   </si>
   <si>
     <t>WARNING</t>
@@ -1209,13 +1209,13 @@
     <t>Process Memory Usage</t>
   </si>
   <si>
-    <t>50.1 MB used by scanner</t>
+    <t>47.5 MB used by scanner</t>
   </si>
   <si>
     <t>CPU Utilization Check</t>
   </si>
   <si>
-    <t>8.3% utilization</t>
+    <t>0.0% utilization</t>
   </si>
   <si>
     <t>Workspace Write Permissions</t>
@@ -1245,7 +1245,7 @@
     <t>Scan Execution Duration</t>
   </si>
   <si>
-    <t>30.276 seconds total run time</t>
+    <t>33.585 seconds total run time</t>
   </si>
   <si>
     <t>Active Modules Executed</t>
@@ -6099,7 +6099,7 @@
         <v>365</v>
       </c>
       <c r="B8" s="10">
-        <v>30.276</v>
+        <v>33.585</v>
       </c>
     </row>
     <row r="9"/>
@@ -6174,7 +6174,7 @@
         <v>376</v>
       </c>
       <c r="C18" s="10">
-        <v>0.829</v>
+        <v>0.825</v>
       </c>
       <c r="D18" s="10">
         <v>4</v>
@@ -6188,7 +6188,7 @@
         <v>376</v>
       </c>
       <c r="C19" s="11">
-        <v>0.099</v>
+        <v>0.096</v>
       </c>
       <c r="D19" s="11">
         <v>0</v>
@@ -6202,7 +6202,7 @@
         <v>376</v>
       </c>
       <c r="C20" s="10">
-        <v>29.916</v>
+        <v>33.267</v>
       </c>
       <c r="D20" s="10">
         <v>14</v>
@@ -6216,7 +6216,7 @@
         <v>376</v>
       </c>
       <c r="C21" s="11">
-        <v>5.83</v>
+        <v>10.629</v>
       </c>
       <c r="D21" s="11">
         <v>5</v>
@@ -6230,7 +6230,7 @@
         <v>376</v>
       </c>
       <c r="C22" s="10">
-        <v>0.807</v>
+        <v>0.788</v>
       </c>
       <c r="D22" s="10">
         <v>10</v>
@@ -6244,7 +6244,7 @@
         <v>376</v>
       </c>
       <c r="C23" s="11">
-        <v>2.04</v>
+        <v>2.137</v>
       </c>
       <c r="D23" s="11">
         <v>1</v>
@@ -6258,7 +6258,7 @@
         <v>376</v>
       </c>
       <c r="C24" s="10">
-        <v>0.797</v>
+        <v>0.802</v>
       </c>
       <c r="D24" s="10">
         <v>7</v>
@@ -6272,7 +6272,7 @@
         <v>376</v>
       </c>
       <c r="C25" s="11">
-        <v>1.218</v>
+        <v>1.998</v>
       </c>
       <c r="D25" s="11">
         <v>0</v>
@@ -6286,7 +6286,7 @@
         <v>376</v>
       </c>
       <c r="C26" s="10">
-        <v>1.214</v>
+        <v>2.52</v>
       </c>
       <c r="D26" s="10">
         <v>103</v>
@@ -6300,7 +6300,7 @@
         <v>376</v>
       </c>
       <c r="C27" s="11">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
       <c r="D27" s="11">
         <v>0</v>

--- a/System Scanner/test_report.xlsx
+++ b/System Scanner/test_report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="425">
   <si>
     <t>Finding ID</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>2f386a55</t>
+    <t>6be9616a</t>
   </si>
   <si>
     <t>SystemScanner</t>
@@ -54,19 +54,19 @@
     <t>INFO</t>
   </si>
   <si>
-    <t>2026-06-22T17:44:21.750509</t>
-  </si>
-  <si>
-    <t>cd809eaf</t>
+    <t>2026-06-23T12:43:57.471905</t>
+  </si>
+  <si>
+    <t>995dfc4d</t>
   </si>
   <si>
     <t>GPU Detected: NVIDIA GeForce GTX 1650</t>
   </si>
   <si>
-    <t>2026-06-22T17:44:21.908236</t>
-  </si>
-  <si>
-    <t>78625e0f</t>
+    <t>2026-06-23T12:43:57.579040</t>
+  </si>
+  <si>
+    <t>4d6357ce</t>
   </si>
   <si>
     <t>APIScanner</t>
@@ -78,58 +78,58 @@
     <t>HIGH</t>
   </si>
   <si>
-    <t>2026-06-22T17:44:21.993095</t>
-  </si>
-  <si>
-    <t>ebb267d7</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.993233</t>
-  </si>
-  <si>
-    <t>00cbefd3</t>
+    <t>2026-06-23T12:43:57.662042</t>
+  </si>
+  <si>
+    <t>3c26b0fe</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.662453</t>
+  </si>
+  <si>
+    <t>133f2e72</t>
   </si>
   <si>
     <t>Exposed Generic API Key/Token</t>
   </si>
   <si>
-    <t>2026-06-22T17:44:21.993483</t>
-  </si>
-  <si>
-    <t>4e0e1a9f</t>
+    <t>2026-06-23T12:43:57.662736</t>
+  </si>
+  <si>
+    <t>75d630dd</t>
   </si>
   <si>
     <t>Exposed AWS Access Key ID</t>
   </si>
   <si>
-    <t>2026-06-22T17:44:21.993508</t>
-  </si>
-  <si>
-    <t>b22be501</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.993768</t>
-  </si>
-  <si>
-    <t>a7647b62</t>
+    <t>2026-06-23T12:43:57.662757</t>
+  </si>
+  <si>
+    <t>02cd2e1c</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.663028</t>
+  </si>
+  <si>
+    <t>486ab488</t>
   </si>
   <si>
     <t>Environment Variable: ANTIGRAVITY_CSRF_TOKEN</t>
   </si>
   <si>
-    <t>2026-06-22T17:44:22.046695</t>
-  </si>
-  <si>
-    <t>318ca722</t>
+    <t>2026-06-23T12:43:57.733711</t>
+  </si>
+  <si>
+    <t>66653b99</t>
   </si>
   <si>
     <t>Environment Variable: GEMINI_API_KEY</t>
   </si>
   <si>
-    <t>2026-06-22T17:44:22.046753</t>
-  </si>
-  <si>
-    <t>3c3c0ec5</t>
+    <t>2026-06-23T12:43:57.733798</t>
+  </si>
+  <si>
+    <t>d009eabe</t>
   </si>
   <si>
     <t>LicenseScanner</t>
@@ -138,10 +138,10 @@
     <t>Code Snippet: GPL Mention</t>
   </si>
   <si>
-    <t>2026-06-22T17:44:21.335268</t>
-  </si>
-  <si>
-    <t>23ad3913</t>
+    <t>2026-06-23T12:43:57.016595</t>
+  </si>
+  <si>
+    <t>855300a7</t>
   </si>
   <si>
     <t>Code Snippet: LGPL Mention</t>
@@ -150,31 +150,31 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>2026-06-22T17:44:21.411285</t>
-  </si>
-  <si>
-    <t>a535e19d</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.412371</t>
-  </si>
-  <si>
-    <t>196e7b5e</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.414709</t>
-  </si>
-  <si>
-    <t>8883157f</t>
+    <t>2026-06-23T12:43:57.096361</t>
+  </si>
+  <si>
+    <t>8b85b1b8</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.098716</t>
+  </si>
+  <si>
+    <t>7bfdb2f2</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.099746</t>
+  </si>
+  <si>
+    <t>4bf822cc</t>
   </si>
   <si>
     <t>Code Snippet: Proprietary Mention</t>
   </si>
   <si>
-    <t>2026-06-22T17:44:21.417472</t>
-  </si>
-  <si>
-    <t>6c60c6f1</t>
+    <t>2026-06-23T12:43:57.102198</t>
+  </si>
+  <si>
+    <t>a094e6e5</t>
   </si>
   <si>
     <t>Code Snippet: AGPL Mention</t>
@@ -183,595 +183,607 @@
     <t>CRITICAL</t>
   </si>
   <si>
-    <t>2026-06-22T17:44:21.418732</t>
-  </si>
-  <si>
-    <t>837b4feb</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.420319</t>
-  </si>
-  <si>
-    <t>27b0bc89</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.423129</t>
-  </si>
-  <si>
-    <t>2cd0d8c1</t>
+    <t>2026-06-23T12:43:57.105599</t>
+  </si>
+  <si>
+    <t>17ffdea8</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.107605</t>
+  </si>
+  <si>
+    <t>1057ae64</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.110605</t>
+  </si>
+  <si>
+    <t>02651054</t>
   </si>
   <si>
     <t>Code Snippet: Polyform Shield Mention</t>
   </si>
   <si>
-    <t>2026-06-22T17:44:21.425631</t>
-  </si>
-  <si>
-    <t>73cb5ed4</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.427821</t>
-  </si>
-  <si>
-    <t>65599c08</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.432251</t>
-  </si>
-  <si>
-    <t>2b74ce7f</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.435135</t>
-  </si>
-  <si>
-    <t>8aa6dd08</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.436201</t>
-  </si>
-  <si>
-    <t>f9588ac6</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.437857</t>
-  </si>
-  <si>
-    <t>92806092</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.438787</t>
-  </si>
-  <si>
-    <t>2723c8ca</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.440377</t>
-  </si>
-  <si>
-    <t>57c4332f</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.446530</t>
-  </si>
-  <si>
-    <t>96cd3abb</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.448806</t>
-  </si>
-  <si>
-    <t>ae474ef7</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.451910</t>
-  </si>
-  <si>
-    <t>84e36da0</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.453189</t>
-  </si>
-  <si>
-    <t>fec35c58</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.456388</t>
-  </si>
-  <si>
-    <t>db15c77c</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.462305</t>
-  </si>
-  <si>
-    <t>d1cfb211</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.480937</t>
-  </si>
-  <si>
-    <t>1d22435d</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.484208</t>
-  </si>
-  <si>
-    <t>230f9f09</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.486634</t>
-  </si>
-  <si>
-    <t>98bcf835</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.490041</t>
-  </si>
-  <si>
-    <t>d255d64f</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.490984</t>
-  </si>
-  <si>
-    <t>ab36ebf6</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.493973</t>
-  </si>
-  <si>
-    <t>6f1a6f48</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.500817</t>
-  </si>
-  <si>
-    <t>b6c681ed</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.511420</t>
-  </si>
-  <si>
-    <t>08eae7df</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.518336</t>
-  </si>
-  <si>
-    <t>d9e856d2</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.521089</t>
-  </si>
-  <si>
-    <t>2d71eabd</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.526974</t>
-  </si>
-  <si>
-    <t>7731c89f</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.548249</t>
-  </si>
-  <si>
-    <t>ef84a9d7</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.572524</t>
-  </si>
-  <si>
-    <t>4d3005e5</t>
+    <t>2026-06-23T12:43:57.114544</t>
+  </si>
+  <si>
+    <t>d5c1a702</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.117380</t>
+  </si>
+  <si>
+    <t>a8f8f6cc</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.120629</t>
+  </si>
+  <si>
+    <t>c06ebef7</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.124590</t>
+  </si>
+  <si>
+    <t>70140a67</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.127727</t>
+  </si>
+  <si>
+    <t>3daa33a1</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.129839</t>
+  </si>
+  <si>
+    <t>d00846c8</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.130942</t>
+  </si>
+  <si>
+    <t>85f8d91e</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.131816</t>
+  </si>
+  <si>
+    <t>9f6c0901</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.132917</t>
+  </si>
+  <si>
+    <t>2f21f0cc</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.139313</t>
+  </si>
+  <si>
+    <t>fc6738b3</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.140847</t>
+  </si>
+  <si>
+    <t>7d014567</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.143740</t>
+  </si>
+  <si>
+    <t>cedcac62</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.147910</t>
+  </si>
+  <si>
+    <t>11fa9a43</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.151838</t>
+  </si>
+  <si>
+    <t>0348032a</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.163704</t>
+  </si>
+  <si>
+    <t>4dd1413a</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.177198</t>
+  </si>
+  <si>
+    <t>94390090</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.180226</t>
+  </si>
+  <si>
+    <t>491a4c65</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.188305</t>
+  </si>
+  <si>
+    <t>9d7499b3</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.193859</t>
+  </si>
+  <si>
+    <t>bcc8c11d</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.202320</t>
+  </si>
+  <si>
+    <t>5286ab78</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.205532</t>
+  </si>
+  <si>
+    <t>2f06ccb2</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.216314</t>
+  </si>
+  <si>
+    <t>14672681</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.222180</t>
+  </si>
+  <si>
+    <t>67964c09</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.230352</t>
+  </si>
+  <si>
+    <t>ef6ae773</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.245923</t>
+  </si>
+  <si>
+    <t>a0a9ad4b</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.289268</t>
+  </si>
+  <si>
+    <t>60f6976a</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.296345</t>
+  </si>
+  <si>
+    <t>674569ef</t>
   </si>
   <si>
     <t>Code License: MIT Header</t>
   </si>
   <si>
-    <t>2026-06-22T17:44:21.897827</t>
-  </si>
-  <si>
-    <t>34676d8c</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.920866</t>
-  </si>
-  <si>
-    <t>99e0aa92</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.932811</t>
-  </si>
-  <si>
-    <t>8a37d963</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.945280</t>
-  </si>
-  <si>
-    <t>5bc277a3</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.955175</t>
-  </si>
-  <si>
-    <t>87c6818a</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.964452</t>
-  </si>
-  <si>
-    <t>f5b1dfb0</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.983154</t>
-  </si>
-  <si>
-    <t>9f997aa1</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.991817</t>
-  </si>
-  <si>
-    <t>0ca6e80f</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.998795</t>
-  </si>
-  <si>
-    <t>909bc706</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.001533</t>
-  </si>
-  <si>
-    <t>7c0a1673</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.009128</t>
-  </si>
-  <si>
-    <t>7bb442c2</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.015160</t>
-  </si>
-  <si>
-    <t>b9e448b3</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.022310</t>
-  </si>
-  <si>
-    <t>762f0fa2</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.031017</t>
-  </si>
-  <si>
-    <t>2d879644</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.034385</t>
-  </si>
-  <si>
-    <t>8cca4304</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.041388</t>
-  </si>
-  <si>
-    <t>552ba3e5</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.045962</t>
-  </si>
-  <si>
-    <t>b0e2cf5c</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.047131</t>
-  </si>
-  <si>
-    <t>b4e30e7f</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.047700</t>
-  </si>
-  <si>
-    <t>464b9b26</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.048365</t>
-  </si>
-  <si>
-    <t>3568243e</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.049051</t>
-  </si>
-  <si>
-    <t>0cafba22</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.049909</t>
-  </si>
-  <si>
-    <t>e647d65b</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.050315</t>
-  </si>
-  <si>
-    <t>6abb968f</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.050968</t>
-  </si>
-  <si>
-    <t>4d39f728</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.637813</t>
-  </si>
-  <si>
-    <t>89e12956</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.657698</t>
-  </si>
-  <si>
-    <t>361a4f40</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.670977</t>
-  </si>
-  <si>
-    <t>68e10400</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.683954</t>
-  </si>
-  <si>
-    <t>6b7d86dc</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.690332</t>
-  </si>
-  <si>
-    <t>4d38444d</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.704361</t>
-  </si>
-  <si>
-    <t>b6fac91d</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.718143</t>
-  </si>
-  <si>
-    <t>d37f8381</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.727554</t>
-  </si>
-  <si>
-    <t>c60950b2</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.737104</t>
-  </si>
-  <si>
-    <t>95951a9d</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.761326</t>
-  </si>
-  <si>
-    <t>4881a3de</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.774091</t>
-  </si>
-  <si>
-    <t>0f8d2ca8</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.781688</t>
-  </si>
-  <si>
-    <t>726b3abc</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.862530</t>
-  </si>
-  <si>
-    <t>de32dbe4</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.874251</t>
-  </si>
-  <si>
-    <t>5458412f</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.889122</t>
-  </si>
-  <si>
-    <t>f0512153</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.899820</t>
-  </si>
-  <si>
-    <t>34fb9f31</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.910980</t>
-  </si>
-  <si>
-    <t>e4293771</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.932282</t>
-  </si>
-  <si>
-    <t>89f6e2f0</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.944730</t>
-  </si>
-  <si>
-    <t>95c1a2d6</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.960047</t>
-  </si>
-  <si>
-    <t>54e9fad1</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.978008</t>
-  </si>
-  <si>
-    <t>342ec8e2</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.993786</t>
-  </si>
-  <si>
-    <t>b07aadab</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.009155</t>
-  </si>
-  <si>
-    <t>c5dc52fa</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.021112</t>
-  </si>
-  <si>
-    <t>0bd2cfc8</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.034618</t>
-  </si>
-  <si>
-    <t>b8af0e90</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.048953</t>
-  </si>
-  <si>
-    <t>5f2c0c6d</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.062511</t>
-  </si>
-  <si>
-    <t>4cd80535</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.080733</t>
-  </si>
-  <si>
-    <t>aee8b0fb</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.096194</t>
-  </si>
-  <si>
-    <t>dd0c3304</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.111226</t>
-  </si>
-  <si>
-    <t>a1f2e96a</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.126370</t>
-  </si>
-  <si>
-    <t>fcf3e196</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.142257</t>
-  </si>
-  <si>
-    <t>05adb035</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.157365</t>
-  </si>
-  <si>
-    <t>cdaf12f2</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.170192</t>
-  </si>
-  <si>
-    <t>f9dcaa88</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.189380</t>
-  </si>
-  <si>
-    <t>9a3a8c13</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.205339</t>
-  </si>
-  <si>
-    <t>a60accc2</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.221553</t>
-  </si>
-  <si>
-    <t>83eeb194</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.238651</t>
-  </si>
-  <si>
-    <t>9766cd10</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.253736</t>
-  </si>
-  <si>
-    <t>d7988c26</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.273415</t>
-  </si>
-  <si>
-    <t>cdeace7a</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.286759</t>
-  </si>
-  <si>
-    <t>69d9b3a8</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.302394</t>
-  </si>
-  <si>
-    <t>ef0e2c01</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.326042</t>
-  </si>
-  <si>
-    <t>d07d122b</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.395089</t>
+    <t>2026-06-23T12:43:57.653458</t>
+  </si>
+  <si>
+    <t>4b2a8bcb</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.663943</t>
+  </si>
+  <si>
+    <t>5210996d</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.669569</t>
+  </si>
+  <si>
+    <t>715dc84a</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.673934</t>
+  </si>
+  <si>
+    <t>92248c33</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.681106</t>
+  </si>
+  <si>
+    <t>60038293</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.687089</t>
+  </si>
+  <si>
+    <t>45d091db</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.695655</t>
+  </si>
+  <si>
+    <t>9e18da18</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.708510</t>
+  </si>
+  <si>
+    <t>23108bb4</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.712113</t>
+  </si>
+  <si>
+    <t>7e95f261</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.720675</t>
+  </si>
+  <si>
+    <t>7a322d0f</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.724770</t>
+  </si>
+  <si>
+    <t>931bbf1c</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.732607</t>
+  </si>
+  <si>
+    <t>032fde3e</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.736004</t>
+  </si>
+  <si>
+    <t>5334f2fe</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.739171</t>
+  </si>
+  <si>
+    <t>9185f5ff</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.740961</t>
+  </si>
+  <si>
+    <t>899ddf53</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.742565</t>
+  </si>
+  <si>
+    <t>0293ab61</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.744369</t>
+  </si>
+  <si>
+    <t>c612cabe</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.745608</t>
+  </si>
+  <si>
+    <t>788d50b7</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.746356</t>
+  </si>
+  <si>
+    <t>f710a360</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.747242</t>
+  </si>
+  <si>
+    <t>69f0b640</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.747837</t>
+  </si>
+  <si>
+    <t>03dc9d04</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.748352</t>
+  </si>
+  <si>
+    <t>f2f7cb8a</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.748879</t>
+  </si>
+  <si>
+    <t>034c9e70</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.749404</t>
+  </si>
+  <si>
+    <t>c1c1114f</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.054120</t>
+  </si>
+  <si>
+    <t>19c2396c</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.054558</t>
+  </si>
+  <si>
+    <t>73d27c49</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.055117</t>
+  </si>
+  <si>
+    <t>f9486925</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.055744</t>
+  </si>
+  <si>
+    <t>3e3a9708</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.056283</t>
+  </si>
+  <si>
+    <t>0a85fa9a</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.056962</t>
+  </si>
+  <si>
+    <t>df2c1c65</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.057912</t>
+  </si>
+  <si>
+    <t>a314847f</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.058664</t>
+  </si>
+  <si>
+    <t>4178dcb2</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.059863</t>
+  </si>
+  <si>
+    <t>f3a00c36</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.061333</t>
+  </si>
+  <si>
+    <t>fb1d2bb2</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.062322</t>
+  </si>
+  <si>
+    <t>223893e8</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.062698</t>
+  </si>
+  <si>
+    <t>06eec3fd</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.068123</t>
+  </si>
+  <si>
+    <t>326c1fcf</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.068515</t>
+  </si>
+  <si>
+    <t>e7e86e86</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.068829</t>
+  </si>
+  <si>
+    <t>244431be</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.069140</t>
+  </si>
+  <si>
+    <t>93c1099b</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.069413</t>
+  </si>
+  <si>
+    <t>70856ca9</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.069923</t>
+  </si>
+  <si>
+    <t>30f545bc</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.070238</t>
+  </si>
+  <si>
+    <t>531e66c7</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.070532</t>
+  </si>
+  <si>
+    <t>ba0b9735</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.070836</t>
+  </si>
+  <si>
+    <t>2cc89d65</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.071140</t>
+  </si>
+  <si>
+    <t>574642bf</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.071876</t>
+  </si>
+  <si>
+    <t>aa19fa64</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.072673</t>
+  </si>
+  <si>
+    <t>66f4bfb6</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.073225</t>
+  </si>
+  <si>
+    <t>3e1dbce3</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.073645</t>
+  </si>
+  <si>
+    <t>d71650b7</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.074121</t>
+  </si>
+  <si>
+    <t>f7633295</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.074559</t>
+  </si>
+  <si>
+    <t>f0b3dae8</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.075051</t>
+  </si>
+  <si>
+    <t>d3bd7387</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.075446</t>
+  </si>
+  <si>
+    <t>0f9da4c4</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.075793</t>
+  </si>
+  <si>
+    <t>fb2e497d</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.076217</t>
+  </si>
+  <si>
+    <t>89ffdd40</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.076724</t>
+  </si>
+  <si>
+    <t>6b0befbd</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.077302</t>
+  </si>
+  <si>
+    <t>1ae68bd2</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.077771</t>
+  </si>
+  <si>
+    <t>cee896be</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.078637</t>
+  </si>
+  <si>
+    <t>27b6a411</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.079321</t>
+  </si>
+  <si>
+    <t>09ec0833</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.079854</t>
+  </si>
+  <si>
+    <t>107a2d98</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.080636</t>
+  </si>
+  <si>
+    <t>4e3f9867</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.081406</t>
+  </si>
+  <si>
+    <t>55994dcb</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.081902</t>
+  </si>
+  <si>
+    <t>c2b277e6</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.082317</t>
+  </si>
+  <si>
+    <t>3216af22</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.082943</t>
+  </si>
+  <si>
+    <t>3a29a5ff</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.083474</t>
+  </si>
+  <si>
+    <t>58441630</t>
+  </si>
+  <si>
+    <t>ComplianceScanner</t>
+  </si>
+  <si>
+    <t>CERT-In Risk: Missing Audit Logging</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:56.966997</t>
   </si>
   <si>
     <t>Package / Library</t>
@@ -780,384 +792,336 @@
     <t>Location / Source</t>
   </si>
   <si>
-    <t>50b7f811</t>
+    <t>AI Model / Agent / Runtime</t>
+  </si>
+  <si>
+    <t>Type (Category)</t>
+  </si>
+  <si>
+    <t>Location / Endpoint</t>
+  </si>
+  <si>
+    <t>645d55d7</t>
+  </si>
+  <si>
+    <t>Copilot Agent — Registry Configuration Detected</t>
+  </si>
+  <si>
+    <t>AI Agent</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.744979</t>
+  </si>
+  <si>
+    <t>f8e1a1fa</t>
+  </si>
+  <si>
+    <t>Codex Agent — Registry Configuration Detected</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.744998</t>
+  </si>
+  <si>
+    <t>b0b5feda</t>
+  </si>
+  <si>
+    <t>ProcessScanner</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 436)</t>
+  </si>
+  <si>
+    <t>LLM Runtime</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:44:00.118899</t>
+  </si>
+  <si>
+    <t>44c0389a</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 920)</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:44:02.117750</t>
+  </si>
+  <si>
+    <t>b8810dac</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 6748)</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:44:04.225640</t>
+  </si>
+  <si>
+    <t>db3f8582</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 8736)</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:44:06.214905</t>
+  </si>
+  <si>
+    <t>e67a8ca0</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 9580)</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:44:08.278164</t>
+  </si>
+  <si>
+    <t>62941bc2</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 11288)</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:44:10.386825</t>
+  </si>
+  <si>
+    <t>9d5ef0db</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 11720)</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:44:12.556626</t>
+  </si>
+  <si>
+    <t>79597875</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 11864)</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:44:14.578917</t>
+  </si>
+  <si>
+    <t>9517ad99</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 12048)</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:44:18.038250</t>
+  </si>
+  <si>
+    <t>1133af59</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 12352)</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:44:20.105962</t>
+  </si>
+  <si>
+    <t>2b485a46</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 12424)</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:44:22.249932</t>
+  </si>
+  <si>
+    <t>24de1313</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 13968)</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:44:24.306385</t>
+  </si>
+  <si>
+    <t>5737e644</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 16196)</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:44:26.334242</t>
+  </si>
+  <si>
+    <t>68af1759</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 19344)</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:44:28.658980</t>
+  </si>
+  <si>
+    <t>5ab72fb3</t>
+  </si>
+  <si>
+    <t>AgentScanner</t>
+  </si>
+  <si>
+    <t>Agent Usage: LangChain Import</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.349048</t>
+  </si>
+  <si>
+    <t>66c85038</t>
+  </si>
+  <si>
+    <t>Agent Usage: CrewAI Import</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.360912</t>
+  </si>
+  <si>
+    <t>17c2c996</t>
+  </si>
+  <si>
+    <t>Agent Usage: Agent Instantiation</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.375262</t>
+  </si>
+  <si>
+    <t>05642fe6</t>
+  </si>
+  <si>
+    <t>Agent Usage: Crew Instantiation</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.398268</t>
+  </si>
+  <si>
+    <t>91d36f98</t>
+  </si>
+  <si>
+    <t>Agent Usage: AssistantAgent Instantiation</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.417311</t>
+  </si>
+  <si>
+    <t>d2fd97e8</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.430489</t>
+  </si>
+  <si>
+    <t>a4716f35</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.444848</t>
+  </si>
+  <si>
+    <t>12b55ced</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.478426</t>
+  </si>
+  <si>
+    <t>f2c1ca46</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.488411</t>
+  </si>
+  <si>
+    <t>7dcc32ad</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:57.538060</t>
+  </si>
+  <si>
+    <t>7c19a9d6</t>
+  </si>
+  <si>
+    <t>RuntimeScanner</t>
+  </si>
+  <si>
+    <t>Active LLM Service Port: 8080</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:58.978888</t>
+  </si>
+  <si>
+    <t>AI Discovery Scanner — Scan Summary Report (v1.4.0)</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Scan ID</t>
+  </si>
+  <si>
+    <t>0d29287b-45d</t>
+  </si>
+  <si>
+    <t>Scan Timestamp</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:43:56.907646</t>
+  </si>
+  <si>
+    <t>Hostname</t>
+  </si>
+  <si>
+    <t>AJINKYA-PATIL</t>
+  </si>
+  <si>
+    <t>Operating System</t>
+  </si>
+  <si>
+    <t>Windows 11 (x64)</t>
+  </si>
+  <si>
+    <t>Scan Duration (s)</t>
+  </si>
+  <si>
+    <t>Summary Statistics</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Total Findings</t>
+  </si>
+  <si>
+    <t>Overall Risk Score (0-100)</t>
+  </si>
+  <si>
+    <t>Modules Run</t>
+  </si>
+  <si>
+    <t>Modules Succeeded</t>
+  </si>
+  <si>
+    <t>Modules Failed</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Duration (s)</t>
+  </si>
+  <si>
+    <t>Findings</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>FileScanner</t>
   </si>
   <si>
     <t>PackageScanner</t>
   </si>
   <si>
-    <t>[UNVERIFIED] Package: google-generativeai (0.8.6)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.282197</t>
-  </si>
-  <si>
-    <t>61969347</t>
-  </si>
-  <si>
-    <t>[UNVERIFIED] Package: huggingface_hub (1.14.0)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.287109</t>
-  </si>
-  <si>
-    <t>a35e29b1</t>
-  </si>
-  <si>
-    <t>[UNVERIFIED] Package: openai (2.36.0)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.292259</t>
-  </si>
-  <si>
-    <t>685e9158</t>
-  </si>
-  <si>
-    <t>[UNVERIFIED] Package: torch (2.11.0)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.299024</t>
-  </si>
-  <si>
-    <t>2c288cbe</t>
-  </si>
-  <si>
-    <t>[UNVERIFIED] Package: transformers (5.8.0)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.304537</t>
-  </si>
-  <si>
-    <t>AI Model / Agent / Runtime</t>
-  </si>
-  <si>
-    <t>Type (Category)</t>
-  </si>
-  <si>
-    <t>Location / Endpoint</t>
-  </si>
-  <si>
-    <t>f0146d9c</t>
-  </si>
-  <si>
-    <t>Copilot Agent — Registry Configuration Detected</t>
-  </si>
-  <si>
-    <t>AI Agent</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.050731</t>
-  </si>
-  <si>
-    <t>2fd56bad</t>
-  </si>
-  <si>
-    <t>Codex Agent — Registry Configuration Detected</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:22.050747</t>
-  </si>
-  <si>
-    <t>6bb85034</t>
-  </si>
-  <si>
-    <t>ProcessScanner</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 3816)</t>
-  </si>
-  <si>
-    <t>LLM Runtime</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:28.859001</t>
-  </si>
-  <si>
-    <t>a572c229</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 5080)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:32.270723</t>
-  </si>
-  <si>
-    <t>446197da</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 12880)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:34.335937</t>
-  </si>
-  <si>
-    <t>909b26d1</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 14808)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:36.350058</t>
-  </si>
-  <si>
-    <t>e9ad8a04</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 16908)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:38.224089</t>
-  </si>
-  <si>
-    <t>7c06708d</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 17460)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:40.186993</t>
-  </si>
-  <si>
-    <t>9d63d040</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 17620)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:42.146717</t>
-  </si>
-  <si>
-    <t>29cb2fee</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 17640)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:43.866428</t>
-  </si>
-  <si>
-    <t>8ffbbd46</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 17704)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:45.668886</t>
-  </si>
-  <si>
-    <t>991cfd15</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 17896)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:47.398422</t>
-  </si>
-  <si>
-    <t>98e943ba</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 18372)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:49.145330</t>
-  </si>
-  <si>
-    <t>d751a7d0</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 18684)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:50.902622</t>
-  </si>
-  <si>
-    <t>eabcdcd1</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 19180)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:52.750325</t>
-  </si>
-  <si>
-    <t>4ff95aa2</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 19948)</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:54.492027</t>
-  </si>
-  <si>
-    <t>421c0dab</t>
-  </si>
-  <si>
-    <t>AgentScanner</t>
-  </si>
-  <si>
-    <t>Agent Usage: LangChain Import</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.595983</t>
-  </si>
-  <si>
-    <t>9e25b330</t>
-  </si>
-  <si>
-    <t>Agent Usage: CrewAI Import</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.605384</t>
-  </si>
-  <si>
-    <t>de7080c8</t>
-  </si>
-  <si>
-    <t>Agent Usage: Agent Instantiation</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.607564</t>
-  </si>
-  <si>
-    <t>0863caec</t>
-  </si>
-  <si>
-    <t>Agent Usage: Crew Instantiation</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.628028</t>
-  </si>
-  <si>
-    <t>c3df3405</t>
-  </si>
-  <si>
-    <t>Agent Usage: AssistantAgent Instantiation</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.657849</t>
-  </si>
-  <si>
-    <t>dd744037</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.706700</t>
-  </si>
-  <si>
-    <t>6599711b</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.728480</t>
-  </si>
-  <si>
-    <t>7f1d6a84</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.748454</t>
-  </si>
-  <si>
-    <t>ecf97914</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.762482</t>
-  </si>
-  <si>
-    <t>01b48c3e</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.791817</t>
-  </si>
-  <si>
-    <t>04554913</t>
-  </si>
-  <si>
-    <t>RuntimeScanner</t>
-  </si>
-  <si>
-    <t>Active LLM Service Port: 8080</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:23.381117</t>
-  </si>
-  <si>
-    <t>AI Discovery Scanner — Scan Summary Report (v1.4.0)</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Scan ID</t>
-  </si>
-  <si>
-    <t>4c1c9b41-a4b</t>
-  </si>
-  <si>
-    <t>Scan Timestamp</t>
-  </si>
-  <si>
-    <t>2026-06-22T17:44:21.190492</t>
-  </si>
-  <si>
-    <t>Hostname</t>
-  </si>
-  <si>
-    <t>AJINKYA-PATIL</t>
-  </si>
-  <si>
-    <t>Operating System</t>
-  </si>
-  <si>
-    <t>Windows 11 (x64)</t>
-  </si>
-  <si>
-    <t>Scan Duration (s)</t>
-  </si>
-  <si>
-    <t>Summary Statistics</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Total Findings</t>
-  </si>
-  <si>
-    <t>Overall Risk Score (0-100)</t>
-  </si>
-  <si>
-    <t>Modules Run</t>
-  </si>
-  <si>
-    <t>Modules Succeeded</t>
-  </si>
-  <si>
-    <t>Modules Failed</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Duration (s)</t>
-  </si>
-  <si>
-    <t>Findings</t>
-  </si>
-  <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>FileScanner</t>
-  </si>
-  <si>
     <t>MCPScanner</t>
   </si>
   <si>
-    <t>ComplianceScanner</t>
-  </si>
-  <si>
     <t>Diagnostic Check</t>
   </si>
   <si>
@@ -1170,7 +1134,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-06-22T17:44:54.711631</t>
+    <t>2026-06-23T12:44:28.872570</t>
   </si>
   <si>
     <t>Python Version</t>
@@ -1194,13 +1158,13 @@
     <t>Installed Packages</t>
   </si>
   <si>
-    <t>128 packages detected</t>
+    <t>51 packages detected</t>
   </si>
   <si>
     <t>System Memory Availability</t>
   </si>
   <si>
-    <t>Total: 7.6 GB (Available: 1.0 GB)</t>
+    <t>Total: 7.6 GB (Available: 0.5 GB)</t>
   </si>
   <si>
     <t>WARNING</t>
@@ -1209,13 +1173,13 @@
     <t>Process Memory Usage</t>
   </si>
   <si>
-    <t>47.5 MB used by scanner</t>
+    <t>60.3 MB used by scanner</t>
   </si>
   <si>
     <t>CPU Utilization Check</t>
   </si>
   <si>
-    <t>0.0% utilization</t>
+    <t>8.3% utilization</t>
   </si>
   <si>
     <t>Workspace Write Permissions</t>
@@ -1245,7 +1209,7 @@
     <t>Scan Execution Duration</t>
   </si>
   <si>
-    <t>33.585 seconds total run time</t>
+    <t>32.004 seconds total run time</t>
   </si>
   <si>
     <t>Active Modules Executed</t>
@@ -1276,9 +1240,6 @@
   </si>
   <si>
     <t>System Info</t>
-  </si>
-  <si>
-    <t>ML Framework</t>
   </si>
   <si>
     <t>Configuration</t>
@@ -4904,6 +4865,36 @@
         <v>251</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="s" s="10">
+        <v>252</v>
+      </c>
+      <c r="B114" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="C114" t="s" s="0">
+        <v>254</v>
+      </c>
+      <c r="D114" t="inlineStr" s="14">
+        <is>
+          <t>The primary audit log (ai_scanner.log) is missing. CERT-In mandates active logging for incident readiness and forensic timelines.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr" s="14">
+        <is>
+          <t>ai_scanner.log</t>
+        </is>
+      </c>
+      <c r="F114" t="s" s="6">
+        <v>19</v>
+      </c>
+      <c r="G114" s="10">
+        <v>90.0</v>
+      </c>
+      <c r="H114" t="s" s="10">
+        <v>255</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -4929,13 +4920,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>3</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="F1" t="s" s="1">
         <v>5</v>
@@ -4945,156 +4936,6 @@
       </c>
       <c r="H1" t="s" s="1">
         <v>7</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="10">
-        <v>254</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>255</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>256</v>
-      </c>
-      <c r="D2" t="inlineStr" s="14">
-        <is>
-          <t>Detected installed AI package: google-generativeai (version 0.8.6) Note: This package has not been verified against the baseline database.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr" s="14">
-        <is>
-          <t>C:/Users/Ajinkya Patil/AppData/Roaming/Python/Python314/site-packages</t>
-        </is>
-      </c>
-      <c r="F2" t="s" s="8">
-        <v>11</v>
-      </c>
-      <c r="G2" s="10">
-        <v>90.0</v>
-      </c>
-      <c r="H2" t="s" s="10">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="11">
-        <v>258</v>
-      </c>
-      <c r="B3" t="s" s="4">
-        <v>255</v>
-      </c>
-      <c r="C3" t="s" s="4">
-        <v>259</v>
-      </c>
-      <c r="D3" t="inlineStr" s="15">
-        <is>
-          <t>Detected installed AI package: huggingface_hub (version 1.14.0) Note: This package has not been verified against the baseline database.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr" s="15">
-        <is>
-          <t>C:/Users/Ajinkya Patil/AppData/Roaming/Python/Python314/site-packages</t>
-        </is>
-      </c>
-      <c r="F3" t="s" s="8">
-        <v>11</v>
-      </c>
-      <c r="G3" s="11">
-        <v>90.0</v>
-      </c>
-      <c r="H3" t="s" s="11">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="10">
-        <v>261</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>255</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>262</v>
-      </c>
-      <c r="D4" t="inlineStr" s="14">
-        <is>
-          <t>Detected installed AI package: openai (version 2.36.0) Note: This package has not been verified against the baseline database.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr" s="14">
-        <is>
-          <t>C:/Users/Ajinkya Patil/AppData/Roaming/Python/Python314/site-packages</t>
-        </is>
-      </c>
-      <c r="F4" t="s" s="8">
-        <v>11</v>
-      </c>
-      <c r="G4" s="10">
-        <v>90.0</v>
-      </c>
-      <c r="H4" t="s" s="10">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="11">
-        <v>264</v>
-      </c>
-      <c r="B5" t="s" s="4">
-        <v>255</v>
-      </c>
-      <c r="C5" t="s" s="4">
-        <v>265</v>
-      </c>
-      <c r="D5" t="inlineStr" s="15">
-        <is>
-          <t>Detected installed AI package: torch (version 2.11.0) Note: This package has not been verified against the baseline database.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr" s="15">
-        <is>
-          <t>C:/Users/Ajinkya Patil/AppData/Roaming/Python/Python314/site-packages</t>
-        </is>
-      </c>
-      <c r="F5" t="s" s="8">
-        <v>11</v>
-      </c>
-      <c r="G5" s="11">
-        <v>90.0</v>
-      </c>
-      <c r="H5" t="s" s="11">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="10">
-        <v>267</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>255</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>268</v>
-      </c>
-      <c r="D6" t="inlineStr" s="14">
-        <is>
-          <t>Detected installed AI package: transformers (version 5.8.0) Note: This package has not been verified against the baseline database.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr" s="14">
-        <is>
-          <t>C:/Users/Ajinkya Patil/AppData/Roaming/Python/Python314/site-packages</t>
-        </is>
-      </c>
-      <c r="F6" t="s" s="8">
-        <v>11</v>
-      </c>
-      <c r="G6" s="10">
-        <v>90.0</v>
-      </c>
-      <c r="H6" t="s" s="10">
-        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -5123,16 +4964,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>3</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="G1" t="s" s="1">
         <v>5</v>
@@ -5146,13 +4987,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="10">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>9</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="D2" t="inlineStr" s="14">
         <is>
@@ -5160,7 +5001,7 @@
         </is>
       </c>
       <c r="E2" t="s" s="10">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F2" t="inlineStr" s="14">
         <is>
@@ -5174,18 +5015,18 @@
         <v>85.0</v>
       </c>
       <c r="I2" t="s" s="10">
-        <v>276</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="11">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="B3" t="s" s="4">
         <v>9</v>
       </c>
       <c r="C3" t="s" s="4">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="D3" t="inlineStr" s="15">
         <is>
@@ -5193,7 +5034,7 @@
         </is>
       </c>
       <c r="E3" t="s" s="11">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F3" t="inlineStr" s="15">
         <is>
@@ -5207,26 +5048,26 @@
         <v>85.0</v>
       </c>
       <c r="I3" t="s" s="11">
-        <v>279</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="10">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="D4" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 3816) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 436) is running as a background process.</t>
         </is>
       </c>
       <c r="E4" t="s" s="10">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F4" t="inlineStr" s="14">
         <is>
@@ -5240,26 +5081,26 @@
         <v>90.0</v>
       </c>
       <c r="I4" t="s" s="10">
-        <v>284</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="11">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="B5" t="s" s="4">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C5" t="s" s="4">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="D5" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 5080) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 920) is running as a background process.</t>
         </is>
       </c>
       <c r="E5" t="s" s="11">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F5" t="inlineStr" s="15">
         <is>
@@ -5273,26 +5114,26 @@
         <v>90.0</v>
       </c>
       <c r="I5" t="s" s="11">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="10">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="D6" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 12880) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 6748) is running as a background process.</t>
         </is>
       </c>
       <c r="E6" t="s" s="10">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F6" t="inlineStr" s="14">
         <is>
@@ -5306,26 +5147,26 @@
         <v>90.0</v>
       </c>
       <c r="I6" t="s" s="10">
-        <v>290</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="11">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B7" t="s" s="4">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C7" t="s" s="4">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="D7" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 14808) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 8736) is running as a background process.</t>
         </is>
       </c>
       <c r="E7" t="s" s="11">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F7" t="inlineStr" s="15">
         <is>
@@ -5339,26 +5180,26 @@
         <v>90.0</v>
       </c>
       <c r="I7" t="s" s="11">
-        <v>293</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="10">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="D8" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 16908) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 9580) is running as a background process.</t>
         </is>
       </c>
       <c r="E8" t="s" s="10">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F8" t="inlineStr" s="14">
         <is>
@@ -5372,26 +5213,26 @@
         <v>90.0</v>
       </c>
       <c r="I8" t="s" s="10">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="11">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="B9" t="s" s="4">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C9" t="s" s="4">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D9" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 17460) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 11288) is running as a background process.</t>
         </is>
       </c>
       <c r="E9" t="s" s="11">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F9" t="inlineStr" s="15">
         <is>
@@ -5405,26 +5246,26 @@
         <v>90.0</v>
       </c>
       <c r="I9" t="s" s="11">
-        <v>299</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="10">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="D10" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 17620) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 11720) is running as a background process.</t>
         </is>
       </c>
       <c r="E10" t="s" s="10">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F10" t="inlineStr" s="14">
         <is>
@@ -5438,26 +5279,26 @@
         <v>90.0</v>
       </c>
       <c r="I10" t="s" s="10">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="11">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="B11" t="s" s="4">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C11" t="s" s="4">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="D11" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 17640) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 11864) is running as a background process.</t>
         </is>
       </c>
       <c r="E11" t="s" s="11">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F11" t="inlineStr" s="15">
         <is>
@@ -5471,26 +5312,26 @@
         <v>90.0</v>
       </c>
       <c r="I11" t="s" s="11">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="10">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="D12" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 17704) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 12048) is running as a background process.</t>
         </is>
       </c>
       <c r="E12" t="s" s="10">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F12" t="inlineStr" s="14">
         <is>
@@ -5504,26 +5345,26 @@
         <v>90.0</v>
       </c>
       <c r="I12" t="s" s="10">
-        <v>308</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="11">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="B13" t="s" s="4">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C13" t="s" s="4">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="D13" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 17896) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 12352) is running as a background process.</t>
         </is>
       </c>
       <c r="E13" t="s" s="11">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F13" t="inlineStr" s="15">
         <is>
@@ -5537,26 +5378,26 @@
         <v>90.0</v>
       </c>
       <c r="I13" t="s" s="11">
-        <v>311</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="10">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="D14" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 18372) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 12424) is running as a background process.</t>
         </is>
       </c>
       <c r="E14" t="s" s="10">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F14" t="inlineStr" s="14">
         <is>
@@ -5570,26 +5411,26 @@
         <v>90.0</v>
       </c>
       <c r="I14" t="s" s="10">
-        <v>314</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="11">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="B15" t="s" s="4">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C15" t="s" s="4">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="D15" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 18684) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 13968) is running as a background process.</t>
         </is>
       </c>
       <c r="E15" t="s" s="11">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F15" t="inlineStr" s="15">
         <is>
@@ -5603,26 +5444,26 @@
         <v>90.0</v>
       </c>
       <c r="I15" t="s" s="11">
-        <v>317</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="10">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="D16" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 19180) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 16196) is running as a background process.</t>
         </is>
       </c>
       <c r="E16" t="s" s="10">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F16" t="inlineStr" s="14">
         <is>
@@ -5636,26 +5477,26 @@
         <v>90.0</v>
       </c>
       <c r="I16" t="s" s="10">
-        <v>320</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="11">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="B17" t="s" s="4">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C17" t="s" s="4">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="D17" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 19948) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 19344) is running as a background process.</t>
         </is>
       </c>
       <c r="E17" t="s" s="11">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F17" t="inlineStr" s="15">
         <is>
@@ -5669,18 +5510,18 @@
         <v>90.0</v>
       </c>
       <c r="I17" t="s" s="11">
-        <v>323</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="10">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="D18" t="inlineStr" s="14">
         <is>
@@ -5688,7 +5529,7 @@
         </is>
       </c>
       <c r="E18" t="s" s="10">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F18" t="inlineStr" s="14">
         <is>
@@ -5702,18 +5543,18 @@
         <v>85.0</v>
       </c>
       <c r="I18" t="s" s="10">
-        <v>327</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="11">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="B19" t="s" s="4">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C19" t="s" s="4">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="D19" t="inlineStr" s="15">
         <is>
@@ -5721,7 +5562,7 @@
         </is>
       </c>
       <c r="E19" t="s" s="11">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F19" t="inlineStr" s="15">
         <is>
@@ -5735,18 +5576,18 @@
         <v>85.0</v>
       </c>
       <c r="I19" t="s" s="11">
-        <v>330</v>
+        <v>318</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="10">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="D20" t="inlineStr" s="14">
         <is>
@@ -5754,7 +5595,7 @@
         </is>
       </c>
       <c r="E20" t="s" s="10">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F20" t="inlineStr" s="14">
         <is>
@@ -5768,18 +5609,18 @@
         <v>85.0</v>
       </c>
       <c r="I20" t="s" s="10">
-        <v>333</v>
+        <v>321</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="11">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="B21" t="s" s="4">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C21" t="s" s="4">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="D21" t="inlineStr" s="15">
         <is>
@@ -5787,7 +5628,7 @@
         </is>
       </c>
       <c r="E21" t="s" s="11">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F21" t="inlineStr" s="15">
         <is>
@@ -5801,18 +5642,18 @@
         <v>85.0</v>
       </c>
       <c r="I21" t="s" s="11">
-        <v>336</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="10">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="D22" t="inlineStr" s="14">
         <is>
@@ -5820,7 +5661,7 @@
         </is>
       </c>
       <c r="E22" t="s" s="10">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F22" t="inlineStr" s="14">
         <is>
@@ -5834,51 +5675,51 @@
         <v>85.0</v>
       </c>
       <c r="I22" t="s" s="10">
-        <v>339</v>
+        <v>327</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="11">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="B23" t="s" s="4">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C23" t="s" s="4">
+        <v>317</v>
+      </c>
+      <c r="D23" t="inlineStr" s="15">
+        <is>
+          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 81 (CrewAI Import).</t>
+        </is>
+      </c>
+      <c r="E23" t="s" s="11">
+        <v>263</v>
+      </c>
+      <c r="F23" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:81</t>
+        </is>
+      </c>
+      <c r="G23" t="s" s="7">
+        <v>43</v>
+      </c>
+      <c r="H23" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I23" t="s" s="11">
         <v>329</v>
-      </c>
-      <c r="D23" t="inlineStr" s="15">
-        <is>
-          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 81 (CrewAI Import).</t>
-        </is>
-      </c>
-      <c r="E23" t="s" s="11">
-        <v>275</v>
-      </c>
-      <c r="F23" t="inlineStr" s="15">
-        <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:81</t>
-        </is>
-      </c>
-      <c r="G23" t="s" s="7">
-        <v>43</v>
-      </c>
-      <c r="H23" s="11">
-        <v>85.0</v>
-      </c>
-      <c r="I23" t="s" s="11">
-        <v>341</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="10">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="D24" t="inlineStr" s="14">
         <is>
@@ -5886,7 +5727,7 @@
         </is>
       </c>
       <c r="E24" t="s" s="10">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F24" t="inlineStr" s="14">
         <is>
@@ -5900,18 +5741,18 @@
         <v>85.0</v>
       </c>
       <c r="I24" t="s" s="10">
-        <v>343</v>
+        <v>331</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="11">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="B25" t="s" s="4">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C25" t="s" s="4">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="D25" t="inlineStr" s="15">
         <is>
@@ -5919,7 +5760,7 @@
         </is>
       </c>
       <c r="E25" t="s" s="11">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F25" t="inlineStr" s="15">
         <is>
@@ -5933,18 +5774,18 @@
         <v>85.0</v>
       </c>
       <c r="I25" t="s" s="11">
-        <v>345</v>
+        <v>333</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="10">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="D26" t="inlineStr" s="14">
         <is>
@@ -5952,7 +5793,7 @@
         </is>
       </c>
       <c r="E26" t="s" s="10">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F26" t="inlineStr" s="14">
         <is>
@@ -5966,18 +5807,18 @@
         <v>85.0</v>
       </c>
       <c r="I26" t="s" s="10">
-        <v>347</v>
+        <v>335</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="11">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="B27" t="s" s="4">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C27" t="s" s="4">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="D27" t="inlineStr" s="15">
         <is>
@@ -5985,7 +5826,7 @@
         </is>
       </c>
       <c r="E27" t="s" s="11">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F27" t="inlineStr" s="15">
         <is>
@@ -5999,18 +5840,18 @@
         <v>85.0</v>
       </c>
       <c r="I27" t="s" s="11">
-        <v>349</v>
+        <v>337</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="10">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="D28" t="inlineStr" s="14">
         <is>
@@ -6018,7 +5859,7 @@
         </is>
       </c>
       <c r="E28" t="s" s="10">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F28" t="inlineStr" s="14">
         <is>
@@ -6032,7 +5873,7 @@
         <v>90.0</v>
       </c>
       <c r="I28" t="s" s="10">
-        <v>353</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -6050,86 +5891,86 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>354</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" t="s" s="1">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>356</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="9">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>358</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="9">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>360</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="9">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>362</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="9">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>364</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="9">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="B8" s="10">
-        <v>33.585</v>
+        <v>32.004</v>
       </c>
     </row>
     <row r="9"/>
     <row r="10">
       <c r="A10" t="s" s="3">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="B10" t="s" s="3">
-        <v>367</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="9">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="B11" s="10">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="9">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="B12" s="10">
-        <v>64.9</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="9">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="B13" s="10">
         <v>10</v>
@@ -6137,7 +5978,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="9">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="B14" s="10">
         <v>10</v>
@@ -6145,7 +5986,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="9">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="B15" s="10">
         <v>0</v>
@@ -6157,13 +5998,13 @@
         <v>1</v>
       </c>
       <c r="B17" t="s" s="1">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="C17" t="s" s="1">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="D17" t="s" s="1">
-        <v>375</v>
+        <v>363</v>
       </c>
     </row>
     <row r="18">
@@ -6171,10 +6012,10 @@
         <v>9</v>
       </c>
       <c r="B18" t="s" s="10">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C18" s="10">
-        <v>0.825</v>
+        <v>0.831</v>
       </c>
       <c r="D18" s="10">
         <v>4</v>
@@ -6182,13 +6023,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="4">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="B19" t="s" s="11">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C19" s="11">
-        <v>0.096</v>
+        <v>0.069</v>
       </c>
       <c r="D19" s="11">
         <v>0</v>
@@ -6196,13 +6037,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="B20" t="s" s="10">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C20" s="10">
-        <v>33.267</v>
+        <v>31.746</v>
       </c>
       <c r="D20" s="10">
         <v>14</v>
@@ -6210,27 +6051,27 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="4">
-        <v>255</v>
+        <v>366</v>
       </c>
       <c r="B21" t="s" s="11">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C21" s="11">
-        <v>10.629</v>
+        <v>0.824</v>
       </c>
       <c r="D21" s="11">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="B22" t="s" s="10">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C22" s="10">
-        <v>0.788</v>
+        <v>0.826</v>
       </c>
       <c r="D22" s="10">
         <v>10</v>
@@ -6238,13 +6079,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="4">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="B23" t="s" s="11">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C23" s="11">
-        <v>2.137</v>
+        <v>2.059</v>
       </c>
       <c r="D23" s="11">
         <v>1</v>
@@ -6255,10 +6096,10 @@
         <v>17</v>
       </c>
       <c r="B24" t="s" s="10">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C24" s="10">
-        <v>0.802</v>
+        <v>0.814</v>
       </c>
       <c r="D24" s="10">
         <v>7</v>
@@ -6266,13 +6107,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="4">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="B25" t="s" s="11">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C25" s="11">
-        <v>1.998</v>
+        <v>1.141</v>
       </c>
       <c r="D25" s="11">
         <v>0</v>
@@ -6283,10 +6124,10 @@
         <v>38</v>
       </c>
       <c r="B26" t="s" s="10">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C26" s="10">
-        <v>2.52</v>
+        <v>1.251</v>
       </c>
       <c r="D26" s="10">
         <v>103</v>
@@ -6294,16 +6135,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="4">
-        <v>379</v>
+        <v>253</v>
       </c>
       <c r="B27" t="s" s="11">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C27" s="11">
-        <v>0.036</v>
+        <v>0.044</v>
       </c>
       <c r="D27" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6321,13 +6162,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>7</v>
@@ -6335,226 +6176,226 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="C2" t="s" s="8">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D2" t="s" s="10">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="4">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="B3" t="s" s="4">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="C3" t="s" s="8">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D3" t="s" s="11">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="C4" t="s" s="8">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D4" t="s" s="10">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="4">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="B5" t="s" s="4">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="C5" t="s" s="8">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D5" t="s" s="11">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="C6" t="s" s="8">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D6" t="s" s="10">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="4">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="B7" t="s" s="4">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C7" t="s" s="6">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="D7" t="s" s="11">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="C8" t="s" s="8">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D8" t="s" s="10">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="4">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="B9" t="s" s="4">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="C9" t="s" s="8">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D9" t="s" s="11">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="C10" t="s" s="8">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D10" t="s" s="10">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="4">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="B11" t="s" s="4">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="C11" t="s" s="8">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D11" t="s" s="11">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="C12" t="s" s="8">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D12" t="s" s="10">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="4">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="B13" t="s" s="4">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="C13" t="s" s="6">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="D13" t="s" s="11">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="C14" t="s" s="8">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D14" t="s" s="10">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="4">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="B15" t="s" s="4">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="C15" t="s" s="8">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D15" t="s" s="11">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="C16" t="s" s="8">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D16" t="s" s="10">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="4">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="B17" t="s" s="4">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="C17" t="s" s="8">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D17" t="s" s="11">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -6583,19 +6424,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>3</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="F1" t="s" s="1">
         <v>5</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="H1" t="s" s="1">
         <v>6</v>
@@ -6620,7 +6461,7 @@
         </is>
       </c>
       <c r="E2" t="s" s="10">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="F2" t="s" s="8">
         <v>11</v>
@@ -6653,7 +6494,7 @@
         </is>
       </c>
       <c r="E3" t="s" s="11">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="F3" t="s" s="8">
         <v>11</v>
@@ -6672,13 +6513,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="10">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>9</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="D4" t="inlineStr" s="14">
         <is>
@@ -6686,7 +6527,7 @@
         </is>
       </c>
       <c r="E4" t="s" s="10">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F4" t="s" s="7">
         <v>43</v>
@@ -6700,18 +6541,18 @@
         <v>85.0</v>
       </c>
       <c r="I4" t="s" s="10">
-        <v>276</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="11">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="B5" t="s" s="4">
         <v>9</v>
       </c>
       <c r="C5" t="s" s="4">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="D5" t="inlineStr" s="15">
         <is>
@@ -6719,7 +6560,7 @@
         </is>
       </c>
       <c r="E5" t="s" s="11">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F5" t="s" s="7">
         <v>43</v>
@@ -6733,26 +6574,26 @@
         <v>85.0</v>
       </c>
       <c r="I5" t="s" s="11">
-        <v>279</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="10">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="D6" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 3816) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 436) is running as a background process.</t>
         </is>
       </c>
       <c r="E6" t="s" s="10">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F6" t="s" s="7">
         <v>43</v>
@@ -6766,26 +6607,26 @@
         <v>90.0</v>
       </c>
       <c r="I6" t="s" s="10">
-        <v>284</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="11">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="B7" t="s" s="4">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C7" t="s" s="4">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="D7" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 5080) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 920) is running as a background process.</t>
         </is>
       </c>
       <c r="E7" t="s" s="11">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F7" t="s" s="7">
         <v>43</v>
@@ -6799,26 +6640,26 @@
         <v>90.0</v>
       </c>
       <c r="I7" t="s" s="11">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="10">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="D8" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 12880) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 6748) is running as a background process.</t>
         </is>
       </c>
       <c r="E8" t="s" s="10">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F8" t="s" s="7">
         <v>43</v>
@@ -6832,26 +6673,26 @@
         <v>90.0</v>
       </c>
       <c r="I8" t="s" s="10">
-        <v>290</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="11">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B9" t="s" s="4">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C9" t="s" s="4">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="D9" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 14808) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 8736) is running as a background process.</t>
         </is>
       </c>
       <c r="E9" t="s" s="11">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F9" t="s" s="7">
         <v>43</v>
@@ -6865,26 +6706,26 @@
         <v>90.0</v>
       </c>
       <c r="I9" t="s" s="11">
-        <v>293</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="10">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="D10" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 16908) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 9580) is running as a background process.</t>
         </is>
       </c>
       <c r="E10" t="s" s="10">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F10" t="s" s="7">
         <v>43</v>
@@ -6898,26 +6739,26 @@
         <v>90.0</v>
       </c>
       <c r="I10" t="s" s="10">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="11">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="B11" t="s" s="4">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C11" t="s" s="4">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D11" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 17460) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 11288) is running as a background process.</t>
         </is>
       </c>
       <c r="E11" t="s" s="11">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F11" t="s" s="7">
         <v>43</v>
@@ -6931,26 +6772,26 @@
         <v>90.0</v>
       </c>
       <c r="I11" t="s" s="11">
-        <v>299</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="10">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="D12" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 17620) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 11720) is running as a background process.</t>
         </is>
       </c>
       <c r="E12" t="s" s="10">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F12" t="s" s="7">
         <v>43</v>
@@ -6964,26 +6805,26 @@
         <v>90.0</v>
       </c>
       <c r="I12" t="s" s="10">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="11">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="B13" t="s" s="4">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C13" t="s" s="4">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="D13" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 17640) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 11864) is running as a background process.</t>
         </is>
       </c>
       <c r="E13" t="s" s="11">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F13" t="s" s="7">
         <v>43</v>
@@ -6997,26 +6838,26 @@
         <v>90.0</v>
       </c>
       <c r="I13" t="s" s="11">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="10">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="D14" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 17704) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 12048) is running as a background process.</t>
         </is>
       </c>
       <c r="E14" t="s" s="10">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F14" t="s" s="7">
         <v>43</v>
@@ -7030,26 +6871,26 @@
         <v>90.0</v>
       </c>
       <c r="I14" t="s" s="10">
-        <v>308</v>
+        <v>296</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="11">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="B15" t="s" s="4">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C15" t="s" s="4">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="D15" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 17896) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 12352) is running as a background process.</t>
         </is>
       </c>
       <c r="E15" t="s" s="11">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F15" t="s" s="7">
         <v>43</v>
@@ -7063,26 +6904,26 @@
         <v>90.0</v>
       </c>
       <c r="I15" t="s" s="11">
-        <v>311</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="10">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="D16" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 18372) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 12424) is running as a background process.</t>
         </is>
       </c>
       <c r="E16" t="s" s="10">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F16" t="s" s="7">
         <v>43</v>
@@ -7096,26 +6937,26 @@
         <v>90.0</v>
       </c>
       <c r="I16" t="s" s="10">
-        <v>314</v>
+        <v>302</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="11">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="B17" t="s" s="4">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C17" t="s" s="4">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="D17" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 18684) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 13968) is running as a background process.</t>
         </is>
       </c>
       <c r="E17" t="s" s="11">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F17" t="s" s="7">
         <v>43</v>
@@ -7129,26 +6970,26 @@
         <v>90.0</v>
       </c>
       <c r="I17" t="s" s="11">
-        <v>317</v>
+        <v>305</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="10">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="D18" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 19180) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 16196) is running as a background process.</t>
         </is>
       </c>
       <c r="E18" t="s" s="10">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F18" t="s" s="7">
         <v>43</v>
@@ -7162,26 +7003,26 @@
         <v>90.0</v>
       </c>
       <c r="I18" t="s" s="10">
-        <v>320</v>
+        <v>308</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="11">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="B19" t="s" s="4">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C19" t="s" s="4">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="D19" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 19948) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 19344) is running as a background process.</t>
         </is>
       </c>
       <c r="E19" t="s" s="11">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F19" t="s" s="7">
         <v>43</v>
@@ -7195,264 +7036,264 @@
         <v>90.0</v>
       </c>
       <c r="I19" t="s" s="11">
-        <v>323</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="10">
-        <v>254</v>
+        <v>312</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>255</v>
+        <v>313</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>256</v>
+        <v>314</v>
       </c>
       <c r="D20" t="inlineStr" s="14">
         <is>
-          <t>Detected installed AI package: google-generativeai (version 0.8.6) Note: This package has not been verified against the baseline database.</t>
+          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 25 (LangChain Import).</t>
         </is>
       </c>
       <c r="E20" t="s" s="10">
-        <v>420</v>
-      </c>
-      <c r="F20" t="s" s="8">
-        <v>11</v>
+        <v>263</v>
+      </c>
+      <c r="F20" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G20" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/Ajinkya Patil/AppData/Roaming/Python/Python314/site-packages</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:25</t>
         </is>
       </c>
       <c r="H20" s="10">
-        <v>90.0</v>
+        <v>85.0</v>
       </c>
       <c r="I20" t="s" s="10">
-        <v>257</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="11">
-        <v>258</v>
+        <v>316</v>
       </c>
       <c r="B21" t="s" s="4">
-        <v>255</v>
+        <v>313</v>
       </c>
       <c r="C21" t="s" s="4">
-        <v>259</v>
+        <v>317</v>
       </c>
       <c r="D21" t="inlineStr" s="15">
         <is>
-          <t>Detected installed AI package: huggingface_hub (version 1.14.0) Note: This package has not been verified against the baseline database.</t>
+          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 26 (CrewAI Import).</t>
         </is>
       </c>
       <c r="E21" t="s" s="11">
-        <v>420</v>
-      </c>
-      <c r="F21" t="s" s="8">
-        <v>11</v>
+        <v>263</v>
+      </c>
+      <c r="F21" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G21" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/Ajinkya Patil/AppData/Roaming/Python/Python314/site-packages</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:26</t>
         </is>
       </c>
       <c r="H21" s="11">
-        <v>90.0</v>
+        <v>85.0</v>
       </c>
       <c r="I21" t="s" s="11">
-        <v>260</v>
+        <v>318</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="10">
-        <v>261</v>
+        <v>319</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>255</v>
+        <v>313</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>262</v>
+        <v>320</v>
       </c>
       <c r="D22" t="inlineStr" s="14">
         <is>
-          <t>Detected installed AI package: openai (version 2.36.0) Note: This package has not been verified against the baseline database.</t>
+          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 30 (Agent Instantiation).</t>
         </is>
       </c>
       <c r="E22" t="s" s="10">
-        <v>420</v>
-      </c>
-      <c r="F22" t="s" s="8">
-        <v>11</v>
+        <v>263</v>
+      </c>
+      <c r="F22" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G22" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/Ajinkya Patil/AppData/Roaming/Python/Python314/site-packages</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:30</t>
         </is>
       </c>
       <c r="H22" s="10">
-        <v>90.0</v>
+        <v>85.0</v>
       </c>
       <c r="I22" t="s" s="10">
-        <v>263</v>
+        <v>321</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="11">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="B23" t="s" s="4">
-        <v>255</v>
+        <v>313</v>
       </c>
       <c r="C23" t="s" s="4">
-        <v>265</v>
+        <v>323</v>
       </c>
       <c r="D23" t="inlineStr" s="15">
         <is>
-          <t>Detected installed AI package: torch (version 2.11.0) Note: This package has not been verified against the baseline database.</t>
+          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 31 (Crew Instantiation).</t>
         </is>
       </c>
       <c r="E23" t="s" s="11">
-        <v>420</v>
-      </c>
-      <c r="F23" t="s" s="8">
-        <v>11</v>
+        <v>263</v>
+      </c>
+      <c r="F23" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G23" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/Ajinkya Patil/AppData/Roaming/Python/Python314/site-packages</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:31</t>
         </is>
       </c>
       <c r="H23" s="11">
-        <v>90.0</v>
+        <v>85.0</v>
       </c>
       <c r="I23" t="s" s="11">
-        <v>266</v>
+        <v>324</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="10">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>255</v>
+        <v>313</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="D24" t="inlineStr" s="14">
         <is>
-          <t>Detected installed AI package: transformers (version 5.8.0) Note: This package has not been verified against the baseline database.</t>
+          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 32 (AssistantAgent Instantiation).</t>
         </is>
       </c>
       <c r="E24" t="s" s="10">
-        <v>420</v>
-      </c>
-      <c r="F24" t="s" s="8">
-        <v>11</v>
+        <v>263</v>
+      </c>
+      <c r="F24" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G24" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/Ajinkya Patil/AppData/Roaming/Python/Python314/site-packages</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:32</t>
         </is>
       </c>
       <c r="H24" s="10">
-        <v>90.0</v>
+        <v>85.0</v>
       </c>
       <c r="I24" t="s" s="10">
-        <v>269</v>
+        <v>327</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="11">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B25" t="s" s="4">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C25" t="s" s="4">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D25" t="inlineStr" s="15">
         <is>
-          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 25 (LangChain Import).</t>
+          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 81 (CrewAI Import).</t>
         </is>
       </c>
       <c r="E25" t="s" s="11">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F25" t="s" s="7">
         <v>43</v>
       </c>
       <c r="G25" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:25</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:81</t>
         </is>
       </c>
       <c r="H25" s="11">
         <v>85.0</v>
       </c>
       <c r="I25" t="s" s="11">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="10">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="D26" t="inlineStr" s="14">
         <is>
-          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 26 (CrewAI Import).</t>
+          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 82 (LangChain Import).</t>
         </is>
       </c>
       <c r="E26" t="s" s="10">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F26" t="s" s="7">
         <v>43</v>
       </c>
       <c r="G26" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:26</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:82</t>
         </is>
       </c>
       <c r="H26" s="10">
         <v>85.0</v>
       </c>
       <c r="I26" t="s" s="10">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="11">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B27" t="s" s="4">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C27" t="s" s="4">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="D27" t="inlineStr" s="15">
         <is>
-          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 30 (Agent Instantiation).</t>
+          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 87 (LangChain Import).</t>
         </is>
       </c>
       <c r="E27" t="s" s="11">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F27" t="s" s="7">
         <v>43</v>
       </c>
       <c r="G27" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:30</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:87</t>
         </is>
       </c>
       <c r="H27" s="11">
@@ -7467,95 +7308,95 @@
         <v>334</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C28" t="s" s="0">
+        <v>317</v>
+      </c>
+      <c r="D28" t="inlineStr" s="14">
+        <is>
+          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 92 (CrewAI Import).</t>
+        </is>
+      </c>
+      <c r="E28" t="s" s="10">
+        <v>263</v>
+      </c>
+      <c r="F28" t="s" s="7">
+        <v>43</v>
+      </c>
+      <c r="G28" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:92</t>
+        </is>
+      </c>
+      <c r="H28" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="I28" t="s" s="10">
         <v>335</v>
-      </c>
-      <c r="D28" t="inlineStr" s="14">
-        <is>
-          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 31 (Crew Instantiation).</t>
-        </is>
-      </c>
-      <c r="E28" t="s" s="10">
-        <v>275</v>
-      </c>
-      <c r="F28" t="s" s="7">
-        <v>43</v>
-      </c>
-      <c r="G28" t="inlineStr" s="14">
-        <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:31</t>
-        </is>
-      </c>
-      <c r="H28" s="10">
-        <v>85.0</v>
-      </c>
-      <c r="I28" t="s" s="10">
-        <v>336</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="11">
+        <v>336</v>
+      </c>
+      <c r="B29" t="s" s="4">
+        <v>313</v>
+      </c>
+      <c r="C29" t="s" s="4">
+        <v>320</v>
+      </c>
+      <c r="D29" t="inlineStr" s="15">
+        <is>
+          <t>Potential AI Agent signature detected in script 'test_classifier.py' at line 103 (Agent Instantiation).</t>
+        </is>
+      </c>
+      <c r="E29" t="s" s="11">
+        <v>263</v>
+      </c>
+      <c r="F29" t="s" s="7">
+        <v>43</v>
+      </c>
+      <c r="G29" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_classifier.py:103</t>
+        </is>
+      </c>
+      <c r="H29" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="I29" t="s" s="11">
         <v>337</v>
-      </c>
-      <c r="B29" t="s" s="4">
-        <v>325</v>
-      </c>
-      <c r="C29" t="s" s="4">
-        <v>338</v>
-      </c>
-      <c r="D29" t="inlineStr" s="15">
-        <is>
-          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 32 (AssistantAgent Instantiation).</t>
-        </is>
-      </c>
-      <c r="E29" t="s" s="11">
-        <v>275</v>
-      </c>
-      <c r="F29" t="s" s="7">
-        <v>43</v>
-      </c>
-      <c r="G29" t="inlineStr" s="15">
-        <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:32</t>
-        </is>
-      </c>
-      <c r="H29" s="11">
-        <v>85.0</v>
-      </c>
-      <c r="I29" t="s" s="11">
-        <v>339</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="10">
+        <v>338</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>339</v>
+      </c>
+      <c r="C30" t="s" s="0">
         <v>340</v>
       </c>
-      <c r="B30" t="s" s="0">
-        <v>325</v>
-      </c>
-      <c r="C30" t="s" s="0">
-        <v>329</v>
-      </c>
       <c r="D30" t="inlineStr" s="14">
         <is>
-          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 81 (CrewAI Import).</t>
+          <t>An active service was detected listening on port 8080 (llama.cpp / LocalAI Server). This port is commonly used by local LLM APIs, services, or model servers.</t>
         </is>
       </c>
       <c r="E30" t="s" s="10">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F30" t="s" s="7">
         <v>43</v>
       </c>
       <c r="G30" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:81</t>
+          <t>127.0.0.1:8080</t>
         </is>
       </c>
       <c r="H30" s="10">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="I30" t="s" s="10">
         <v>341</v>
@@ -7563,535 +7404,535 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="11">
-        <v>342</v>
+        <v>16</v>
       </c>
       <c r="B31" t="s" s="4">
-        <v>325</v>
+        <v>17</v>
       </c>
       <c r="C31" t="s" s="4">
-        <v>326</v>
+        <v>18</v>
       </c>
       <c r="D31" t="inlineStr" s="15">
         <is>
-          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 82 (LangChain Import).</t>
+          <t>A matching pattern for a OpenAI API Key was discovered in config file 'D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py' at line 21.</t>
         </is>
       </c>
       <c r="E31" t="s" s="11">
-        <v>275</v>
-      </c>
-      <c r="F31" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F31" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G31" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:82</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py:21</t>
         </is>
       </c>
       <c r="H31" s="11">
-        <v>85.0</v>
+        <v>95.0</v>
       </c>
       <c r="I31" t="s" s="11">
-        <v>343</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="10">
-        <v>344</v>
+        <v>21</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>325</v>
+        <v>17</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>326</v>
+        <v>18</v>
       </c>
       <c r="D32" t="inlineStr" s="14">
         <is>
-          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 87 (LangChain Import).</t>
+          <t>A matching pattern for a OpenAI API Key was discovered in config file 'D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py' at line 30.</t>
         </is>
       </c>
       <c r="E32" t="s" s="10">
-        <v>275</v>
-      </c>
-      <c r="F32" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F32" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G32" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:87</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py:30</t>
         </is>
       </c>
       <c r="H32" s="10">
-        <v>85.0</v>
+        <v>95.0</v>
       </c>
       <c r="I32" t="s" s="10">
-        <v>345</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="11">
-        <v>346</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s" s="4">
-        <v>325</v>
+        <v>17</v>
       </c>
       <c r="C33" t="s" s="4">
-        <v>329</v>
+        <v>24</v>
       </c>
       <c r="D33" t="inlineStr" s="15">
         <is>
-          <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 92 (CrewAI Import).</t>
+          <t>A matching pattern for a Generic API Key/Token was discovered in config file 'D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py' at line 47.</t>
         </is>
       </c>
       <c r="E33" t="s" s="11">
-        <v>275</v>
-      </c>
-      <c r="F33" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F33" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G33" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:92</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py:47</t>
         </is>
       </c>
       <c r="H33" s="11">
-        <v>85.0</v>
+        <v>95.0</v>
       </c>
       <c r="I33" t="s" s="11">
-        <v>347</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="10">
-        <v>348</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>325</v>
+        <v>17</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>332</v>
+        <v>27</v>
       </c>
       <c r="D34" t="inlineStr" s="14">
         <is>
-          <t>Potential AI Agent signature detected in script 'test_classifier.py' at line 103 (Agent Instantiation).</t>
+          <t>A matching pattern for a AWS Access Key ID was discovered in config file 'D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py' at line 48.</t>
         </is>
       </c>
       <c r="E34" t="s" s="10">
-        <v>275</v>
-      </c>
-      <c r="F34" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F34" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G34" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_classifier.py:103</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py:48</t>
         </is>
       </c>
       <c r="H34" s="10">
-        <v>85.0</v>
+        <v>95.0</v>
       </c>
       <c r="I34" t="s" s="10">
-        <v>349</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="11">
-        <v>350</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s" s="4">
-        <v>351</v>
+        <v>17</v>
       </c>
       <c r="C35" t="s" s="4">
-        <v>352</v>
+        <v>18</v>
       </c>
       <c r="D35" t="inlineStr" s="15">
         <is>
-          <t>An active service was detected listening on port 8080 (llama.cpp / LocalAI Server). This port is commonly used by local LLM APIs, services, or model servers.</t>
+          <t>A matching pattern for a OpenAI API Key was discovered in config file 'D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py' at line 69.</t>
         </is>
       </c>
       <c r="E35" t="s" s="11">
-        <v>283</v>
-      </c>
-      <c r="F35" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F35" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G35" t="inlineStr" s="15">
         <is>
-          <t>127.0.0.1:8080</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py:69</t>
         </is>
       </c>
       <c r="H35" s="11">
-        <v>90.0</v>
+        <v>95.0</v>
       </c>
       <c r="I35" t="s" s="11">
-        <v>353</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="10">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>17</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D36" t="inlineStr" s="14">
         <is>
-          <t>A matching pattern for a OpenAI API Key was discovered in config file 'D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py' at line 21.</t>
+          <t>Active environment variable 'ANTIGRAVITY_CSRF_TOKEN' contains a potential Unknown credential.</t>
         </is>
       </c>
       <c r="E36" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F36" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G36" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py:21</t>
+          <t>env://ANTIGRAVITY_CSRF_TOKEN</t>
         </is>
       </c>
       <c r="H36" s="10">
         <v>95.0</v>
       </c>
       <c r="I36" t="s" s="10">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="11">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s" s="4">
         <v>17</v>
       </c>
       <c r="C37" t="s" s="4">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D37" t="inlineStr" s="15">
         <is>
-          <t>A matching pattern for a OpenAI API Key was discovered in config file 'D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py' at line 30.</t>
+          <t>Active environment variable 'GEMINI_API_KEY' contains a potential Google/Gemini credential.</t>
         </is>
       </c>
       <c r="E37" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F37" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G37" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py:30</t>
+          <t>env://GEMINI_API_KEY</t>
         </is>
       </c>
       <c r="H37" s="11">
         <v>95.0</v>
       </c>
       <c r="I37" t="s" s="11">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="10">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D38" t="inlineStr" s="14">
         <is>
-          <t>A matching pattern for a Generic API Key/Token was discovered in config file 'D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py' at line 47.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'debug_test.py' at line 10. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E38" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F38" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G38" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py:47</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/debug_test.py:10</t>
         </is>
       </c>
       <c r="H38" s="10">
-        <v>95.0</v>
+        <v>85.0</v>
       </c>
       <c r="I38" t="s" s="10">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="11">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B39" t="s" s="4">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C39" t="s" s="4">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D39" t="inlineStr" s="15">
         <is>
-          <t>A matching pattern for a AWS Access Key ID was discovered in config file 'D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py' at line 48.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'update_licenses.py' at line 20. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E39" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F39" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F39" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G39" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py:48</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:20</t>
         </is>
       </c>
       <c r="H39" s="11">
-        <v>95.0</v>
+        <v>85.0</v>
       </c>
       <c r="I39" t="s" s="11">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="10">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D40" t="inlineStr" s="14">
         <is>
-          <t>A matching pattern for a OpenAI API Key was discovered in config file 'D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py' at line 69.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 24. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E40" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F40" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G40" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py:69</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:24</t>
         </is>
       </c>
       <c r="H40" s="10">
-        <v>95.0</v>
+        <v>85.0</v>
       </c>
       <c r="I40" t="s" s="10">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="11">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="B41" t="s" s="4">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C41" t="s" s="4">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D41" t="inlineStr" s="15">
         <is>
-          <t>Active environment variable 'ANTIGRAVITY_CSRF_TOKEN' contains a potential Unknown credential.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 26. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E41" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F41" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G41" t="inlineStr" s="15">
         <is>
-          <t>env://ANTIGRAVITY_CSRF_TOKEN</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:26</t>
         </is>
       </c>
       <c r="H41" s="11">
-        <v>95.0</v>
+        <v>85.0</v>
       </c>
       <c r="I41" t="s" s="11">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="10">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D42" t="inlineStr" s="14">
         <is>
-          <t>Active environment variable 'GEMINI_API_KEY' contains a potential Google/Gemini credential.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 29. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E42" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F42" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F42" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G42" t="inlineStr" s="14">
         <is>
-          <t>env://GEMINI_API_KEY</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:29</t>
         </is>
       </c>
       <c r="H42" s="10">
-        <v>95.0</v>
+        <v>85.0</v>
       </c>
       <c r="I42" t="s" s="10">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="11">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B43" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C43" t="s" s="4">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D43" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'debug_test.py' at line 10. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'update_licenses.py' at line 32. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E43" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F43" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F43" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G43" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/debug_test.py:10</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:32</t>
         </is>
       </c>
       <c r="H43" s="11">
         <v>85.0</v>
       </c>
       <c r="I43" t="s" s="11">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="10">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B44" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D44" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'update_licenses.py' at line 20. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E44" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F44" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F44" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G44" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:20</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:35</t>
         </is>
       </c>
       <c r="H44" s="10">
         <v>85.0</v>
       </c>
       <c r="I44" t="s" s="10">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="11">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B45" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C45" t="s" s="4">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D45" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 24. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'update_licenses.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E45" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F45" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F45" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G45" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:24</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:35</t>
         </is>
       </c>
       <c r="H45" s="11">
         <v>85.0</v>
       </c>
       <c r="I45" t="s" s="11">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="10">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D46" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 26. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'update_licenses.py' at line 38. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E46" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F46" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G46" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:26</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:38</t>
         </is>
       </c>
       <c r="H46" s="10">
         <v>85.0</v>
       </c>
       <c r="I46" t="s" s="10">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="11">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B47" t="s" s="4">
         <v>38</v>
@@ -8101,162 +7942,162 @@
       </c>
       <c r="D47" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 29. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 44. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E47" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F47" t="s" s="7">
         <v>43</v>
       </c>
       <c r="G47" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:29</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:44</t>
         </is>
       </c>
       <c r="H47" s="11">
         <v>85.0</v>
       </c>
       <c r="I47" t="s" s="11">
-        <v>51</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="10">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B48" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C48" t="s" s="0">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D48" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'update_licenses.py' at line 32. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E48" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F48" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F48" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G48" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:32</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:47</t>
         </is>
       </c>
       <c r="H48" s="10">
         <v>85.0</v>
       </c>
       <c r="I48" t="s" s="10">
-        <v>55</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="11">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B49" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C49" t="s" s="4">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D49" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'update_licenses.py' at line 67. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E49" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F49" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F49" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G49" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:35</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:67</t>
         </is>
       </c>
       <c r="H49" s="11">
         <v>85.0</v>
       </c>
       <c r="I49" t="s" s="11">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="10">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B50" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C50" t="s" s="0">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D50" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'update_licenses.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 72. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E50" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F50" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F50" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G50" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:35</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:72</t>
         </is>
       </c>
       <c r="H50" s="10">
         <v>85.0</v>
       </c>
       <c r="I50" t="s" s="10">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="11">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B51" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C51" t="s" s="4">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D51" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'update_licenses.py' at line 38. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 74. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E51" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F51" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G51" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:38</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:74</t>
         </is>
       </c>
       <c r="H51" s="11">
         <v>85.0</v>
       </c>
       <c r="I51" t="s" s="11">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="10">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B52" t="s" s="0">
         <v>38</v>
@@ -8266,393 +8107,393 @@
       </c>
       <c r="D52" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 44. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 78. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E52" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F52" t="s" s="7">
         <v>43</v>
       </c>
       <c r="G52" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:44</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:78</t>
         </is>
       </c>
       <c r="H52" s="10">
         <v>85.0</v>
       </c>
       <c r="I52" t="s" s="10">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="11">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B53" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C53" t="s" s="4">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D53" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'update_licenses.py' at line 81. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E53" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F53" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F53" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G53" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:47</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:81</t>
         </is>
       </c>
       <c r="H53" s="11">
         <v>85.0</v>
       </c>
       <c r="I53" t="s" s="11">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="10">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B54" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C54" t="s" s="0">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D54" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'update_licenses.py' at line 67. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 85. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E54" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F54" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F54" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G54" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:67</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:85</t>
         </is>
       </c>
       <c r="H54" s="10">
         <v>85.0</v>
       </c>
       <c r="I54" t="s" s="10">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="11">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B55" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C55" t="s" s="4">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D55" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 72. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'update_licenses.py' at line 85. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E55" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F55" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F55" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G55" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:72</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:85</t>
         </is>
       </c>
       <c r="H55" s="11">
         <v>85.0</v>
       </c>
       <c r="I55" t="s" s="11">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="10">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B56" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C56" t="s" s="0">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D56" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 74. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'update_licenses.py' at line 88. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E56" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F56" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G56" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:74</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:88</t>
         </is>
       </c>
       <c r="H56" s="10">
         <v>85.0</v>
       </c>
       <c r="I56" t="s" s="10">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="11">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B57" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C57" t="s" s="4">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D57" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 78. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'update_licenses.py' at line 89. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E57" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F57" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F57" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G57" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:78</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:89</t>
         </is>
       </c>
       <c r="H57" s="11">
         <v>85.0</v>
       </c>
       <c r="I57" t="s" s="11">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="10">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B58" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C58" t="s" s="0">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D58" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'update_licenses.py' at line 81. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 95. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E58" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F58" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F58" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G58" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:81</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:95</t>
         </is>
       </c>
       <c r="H58" s="10">
         <v>85.0</v>
       </c>
       <c r="I58" t="s" s="10">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="11">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B59" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C59" t="s" s="4">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D59" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 85. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 99. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E59" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F59" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F59" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G59" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:85</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:99</t>
         </is>
       </c>
       <c r="H59" s="11">
         <v>85.0</v>
       </c>
       <c r="I59" t="s" s="11">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="10">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B60" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C60" t="s" s="0">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D60" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'update_licenses.py' at line 85. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E60" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F60" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F60" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G60" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:85</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
         </is>
       </c>
       <c r="H60" s="10">
         <v>85.0</v>
       </c>
       <c r="I60" t="s" s="10">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="11">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B61" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C61" t="s" s="4">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D61" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'update_licenses.py' at line 88. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E61" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F61" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G61" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:88</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
         </is>
       </c>
       <c r="H61" s="11">
         <v>85.0</v>
       </c>
       <c r="I61" t="s" s="11">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="10">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B62" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C62" t="s" s="0">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D62" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'update_licenses.py' at line 89. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E62" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F62" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F62" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G62" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:89</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
         </is>
       </c>
       <c r="H62" s="10">
         <v>85.0</v>
       </c>
       <c r="I62" t="s" s="10">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="11">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B63" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C63" t="s" s="4">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D63" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 95. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E63" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F63" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F63" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G63" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:95</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
         </is>
       </c>
       <c r="H63" s="11">
         <v>85.0</v>
       </c>
       <c r="I63" t="s" s="11">
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="10">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B64" t="s" s="0">
         <v>38</v>
@@ -8662,30 +8503,30 @@
       </c>
       <c r="D64" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 99. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E64" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F64" t="s" s="7">
         <v>43</v>
       </c>
       <c r="G64" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:99</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
         </is>
       </c>
       <c r="H64" s="10">
         <v>85.0</v>
       </c>
       <c r="I64" t="s" s="10">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="11">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B65" t="s" s="4">
         <v>38</v>
@@ -8695,30 +8536,30 @@
       </c>
       <c r="D65" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E65" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F65" t="s" s="7">
         <v>43</v>
       </c>
       <c r="G65" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:35</t>
         </is>
       </c>
       <c r="H65" s="11">
         <v>85.0</v>
       </c>
       <c r="I65" t="s" s="11">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="10">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B66" t="s" s="0">
         <v>38</v>
@@ -8728,30 +8569,30 @@
       </c>
       <c r="D66" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 36. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E66" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F66" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G66" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:36</t>
         </is>
       </c>
       <c r="H66" s="10">
         <v>85.0</v>
       </c>
       <c r="I66" t="s" s="10">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="11">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B67" t="s" s="4">
         <v>38</v>
@@ -8761,30 +8602,30 @@
       </c>
       <c r="D67" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 37. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E67" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F67" t="s" s="5">
         <v>54</v>
       </c>
       <c r="G67" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:37</t>
         </is>
       </c>
       <c r="H67" s="11">
         <v>85.0</v>
       </c>
       <c r="I67" t="s" s="11">
-        <v>94</v>
+        <v>104</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="10">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B68" t="s" s="0">
         <v>38</v>
@@ -8794,30 +8635,30 @@
       </c>
       <c r="D68" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'verify_implementation.py' at line 38. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E68" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F68" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G68" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:38</t>
         </is>
       </c>
       <c r="H68" s="10">
         <v>85.0</v>
       </c>
       <c r="I68" t="s" s="10">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="11">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B69" t="s" s="4">
         <v>38</v>
@@ -8827,30 +8668,30 @@
       </c>
       <c r="D69" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'verify_implementation.py' at line 39. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E69" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F69" t="s" s="7">
         <v>43</v>
       </c>
       <c r="G69" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:21</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:39</t>
         </is>
       </c>
       <c r="H69" s="11">
         <v>85.0</v>
       </c>
       <c r="I69" t="s" s="11">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="10">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B70" t="s" s="0">
         <v>38</v>
@@ -8860,30 +8701,30 @@
       </c>
       <c r="D70" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 53. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E70" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F70" t="s" s="7">
         <v>43</v>
       </c>
       <c r="G70" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:35</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:53</t>
         </is>
       </c>
       <c r="H70" s="10">
         <v>85.0</v>
       </c>
       <c r="I70" t="s" s="10">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="11">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B71" t="s" s="4">
         <v>38</v>
@@ -8893,30 +8734,30 @@
       </c>
       <c r="D71" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 36. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 54. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E71" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F71" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G71" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:36</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:54</t>
         </is>
       </c>
       <c r="H71" s="11">
         <v>85.0</v>
       </c>
       <c r="I71" t="s" s="11">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="10">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B72" t="s" s="0">
         <v>38</v>
@@ -8926,426 +8767,426 @@
       </c>
       <c r="D72" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 37. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 55. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E72" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F72" t="s" s="5">
         <v>54</v>
       </c>
       <c r="G72" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:37</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:55</t>
         </is>
       </c>
       <c r="H72" s="10">
         <v>85.0</v>
       </c>
       <c r="I72" t="s" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="11">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B73" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C73" t="s" s="4">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="D73" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'verify_implementation.py' at line 38. This may indicate an inadvertently copied AI snippet.</t>
+          <t>License signature 'MIT' detected in file docstring header of 'license_scanner.py'. Taxonomy classification: Approved. Permissive license. Allowed for enterprise usage.</t>
         </is>
       </c>
       <c r="E73" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F73" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F73" t="s" s="8">
+        <v>11</v>
       </c>
       <c r="G73" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:38</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:1</t>
         </is>
       </c>
       <c r="H73" s="11">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="I73" t="s" s="11">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="10">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B74" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C74" t="s" s="0">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D74" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'verify_implementation.py' at line 39. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E74" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F74" t="s" s="7">
         <v>43</v>
       </c>
       <c r="G74" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:39</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
         </is>
       </c>
       <c r="H74" s="10">
         <v>85.0</v>
       </c>
       <c r="I74" t="s" s="10">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="11">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="B75" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C75" t="s" s="4">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D75" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 53. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E75" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F75" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F75" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G75" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:53</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
         </is>
       </c>
       <c r="H75" s="11">
         <v>85.0</v>
       </c>
       <c r="I75" t="s" s="11">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="10">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B76" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C76" t="s" s="0">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D76" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 54. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E76" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F76" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F76" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G76" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:54</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
         </is>
       </c>
       <c r="H76" s="10">
         <v>85.0</v>
       </c>
       <c r="I76" t="s" s="10">
-        <v>112</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="11">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B77" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C77" t="s" s="4">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D77" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 55. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E77" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F77" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F77" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G77" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:55</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
         </is>
       </c>
       <c r="H77" s="11">
         <v>85.0</v>
       </c>
       <c r="I77" t="s" s="11">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="10">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B78" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C78" t="s" s="0">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="D78" t="inlineStr" s="14">
         <is>
-          <t>License signature 'MIT' detected in file docstring header of 'license_scanner.py'. Taxonomy classification: Approved. Permissive license. Allowed for enterprise usage.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E78" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F78" t="s" s="8">
-        <v>11</v>
+        <v>408</v>
+      </c>
+      <c r="F78" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G78" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:1</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
         </is>
       </c>
       <c r="H78" s="10">
-        <v>90.0</v>
+        <v>85.0</v>
       </c>
       <c r="I78" t="s" s="10">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="11">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B79" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C79" t="s" s="4">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D79" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 7. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E79" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F79" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F79" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G79" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:7</t>
         </is>
       </c>
       <c r="H79" s="11">
         <v>85.0</v>
       </c>
       <c r="I79" t="s" s="11">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="10">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B80" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C80" t="s" s="0">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D80" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 7. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E80" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F80" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F80" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G80" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:7</t>
         </is>
       </c>
       <c r="H80" s="10">
         <v>85.0</v>
       </c>
       <c r="I80" t="s" s="10">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="11">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B81" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C81" t="s" s="4">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D81" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 43. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E81" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F81" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F81" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G81" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:43</t>
         </is>
       </c>
       <c r="H81" s="11">
         <v>85.0</v>
       </c>
       <c r="I81" t="s" s="11">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="10">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B82" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C82" t="s" s="0">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D82" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 48. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E82" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F82" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G82" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:48</t>
         </is>
       </c>
       <c r="H82" s="10">
         <v>85.0</v>
       </c>
       <c r="I82" t="s" s="10">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="11">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B83" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C83" t="s" s="4">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D83" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 50. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E83" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F83" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F83" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G83" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:50</t>
         </is>
       </c>
       <c r="H83" s="11">
         <v>85.0</v>
       </c>
       <c r="I83" t="s" s="11">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="10">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B84" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C84" t="s" s="0">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D84" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 7. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 54. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E84" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F84" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F84" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G84" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:7</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:54</t>
         </is>
       </c>
       <c r="H84" s="10">
         <v>85.0</v>
       </c>
       <c r="I84" t="s" s="10">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="11">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B85" t="s" s="4">
         <v>38</v>
@@ -9355,690 +9196,690 @@
       </c>
       <c r="D85" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 7. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 57. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E85" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F85" t="s" s="5">
         <v>54</v>
       </c>
       <c r="G85" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:7</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:57</t>
         </is>
       </c>
       <c r="H85" s="11">
         <v>85.0</v>
       </c>
       <c r="I85" t="s" s="11">
-        <v>131</v>
+        <v>141</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="10">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B86" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C86" t="s" s="0">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D86" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 43. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E86" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F86" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F86" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G86" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:43</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:61</t>
         </is>
       </c>
       <c r="H86" s="10">
         <v>85.0</v>
       </c>
       <c r="I86" t="s" s="10">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="11">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B87" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C87" t="s" s="4">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D87" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 48. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E87" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F87" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F87" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G87" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:48</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:61</t>
         </is>
       </c>
       <c r="H87" s="11">
         <v>85.0</v>
       </c>
       <c r="I87" t="s" s="11">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="10">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B88" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C88" t="s" s="0">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D88" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 50. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'license_scanner.py' at line 64. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E88" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F88" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G88" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:50</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:64</t>
         </is>
       </c>
       <c r="H88" s="10">
         <v>85.0</v>
       </c>
       <c r="I88" t="s" s="10">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="11">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B89" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C89" t="s" s="4">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D89" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 54. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'license_scanner.py' at line 65. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E89" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F89" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F89" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G89" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:54</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:65</t>
         </is>
       </c>
       <c r="H89" s="11">
         <v>85.0</v>
       </c>
       <c r="I89" t="s" s="11">
-        <v>139</v>
+        <v>149</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="10">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B90" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C90" t="s" s="0">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D90" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 57. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 71. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E90" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F90" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F90" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G90" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:57</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:71</t>
         </is>
       </c>
       <c r="H90" s="10">
         <v>85.0</v>
       </c>
       <c r="I90" t="s" s="10">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="11">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="B91" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C91" t="s" s="4">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D91" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 75. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E91" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F91" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F91" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G91" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:61</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:75</t>
         </is>
       </c>
       <c r="H91" s="11">
         <v>85.0</v>
       </c>
       <c r="I91" t="s" s="11">
-        <v>143</v>
+        <v>153</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="10">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B92" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C92" t="s" s="0">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D92" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 82. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E92" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F92" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F92" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G92" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:61</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:82</t>
         </is>
       </c>
       <c r="H92" s="10">
         <v>85.0</v>
       </c>
       <c r="I92" t="s" s="10">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="11">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B93" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C93" t="s" s="4">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D93" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'license_scanner.py' at line 64. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 83. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E93" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F93" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G93" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:64</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:83</t>
         </is>
       </c>
       <c r="H93" s="11">
         <v>85.0</v>
       </c>
       <c r="I93" t="s" s="11">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="10">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B94" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C94" t="s" s="0">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D94" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'license_scanner.py' at line 65. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 84. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E94" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F94" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G94" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:65</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:84</t>
         </is>
       </c>
       <c r="H94" s="10">
         <v>85.0</v>
       </c>
       <c r="I94" t="s" s="10">
-        <v>149</v>
+        <v>159</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="11">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="B95" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C95" t="s" s="4">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D95" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 71. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 85. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E95" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F95" t="s" s="7">
         <v>43</v>
       </c>
       <c r="G95" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:71</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:85</t>
         </is>
       </c>
       <c r="H95" s="11">
         <v>85.0</v>
       </c>
       <c r="I95" t="s" s="11">
-        <v>151</v>
+        <v>161</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="10">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="B96" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C96" t="s" s="0">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D96" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 75. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 86. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E96" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F96" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F96" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G96" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:75</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:86</t>
         </is>
       </c>
       <c r="H96" s="10">
         <v>85.0</v>
       </c>
       <c r="I96" t="s" s="10">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="11">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B97" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C97" t="s" s="4">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D97" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 82. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E97" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F97" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F97" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G97" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:82</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:21</t>
         </is>
       </c>
       <c r="H97" s="11">
         <v>85.0</v>
       </c>
       <c r="I97" t="s" s="11">
-        <v>155</v>
+        <v>165</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="10">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B98" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C98" t="s" s="0">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D98" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 83. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 23. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E98" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F98" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F98" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G98" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:83</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:23</t>
         </is>
       </c>
       <c r="H98" s="10">
         <v>85.0</v>
       </c>
       <c r="I98" t="s" s="10">
-        <v>157</v>
+        <v>167</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="11">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B99" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C99" t="s" s="4">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D99" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 84. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 34. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E99" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F99" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F99" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G99" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:84</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:34</t>
         </is>
       </c>
       <c r="H99" s="11">
         <v>85.0</v>
       </c>
       <c r="I99" t="s" s="11">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="10">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B100" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C100" t="s" s="0">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D100" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 85. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 39. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E100" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F100" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F100" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G100" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:85</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:39</t>
         </is>
       </c>
       <c r="H100" s="10">
         <v>85.0</v>
       </c>
       <c r="I100" t="s" s="10">
-        <v>161</v>
+        <v>171</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="11">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="B101" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C101" t="s" s="4">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D101" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 86. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 40. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E101" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F101" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F101" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G101" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:86</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:40</t>
         </is>
       </c>
       <c r="H101" s="11">
         <v>85.0</v>
       </c>
       <c r="I101" t="s" s="11">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="10">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B102" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C102" t="s" s="0">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D102" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E102" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F102" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F102" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G102" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:21</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:47</t>
         </is>
       </c>
       <c r="H102" s="10">
         <v>85.0</v>
       </c>
       <c r="I102" t="s" s="10">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="11">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B103" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C103" t="s" s="4">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D103" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 23. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E103" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F103" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F103" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G103" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:23</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:61</t>
         </is>
       </c>
       <c r="H103" s="11">
         <v>85.0</v>
       </c>
       <c r="I103" t="s" s="11">
-        <v>167</v>
+        <v>177</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="10">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="B104" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C104" t="s" s="0">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D104" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 34. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 62. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E104" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F104" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F104" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G104" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:34</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:62</t>
         </is>
       </c>
       <c r="H104" s="10">
         <v>85.0</v>
       </c>
       <c r="I104" t="s" s="10">
-        <v>169</v>
+        <v>179</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="11">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="B105" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C105" t="s" s="4">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D105" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 39. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 70. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E105" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F105" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F105" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G105" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:39</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:70</t>
         </is>
       </c>
       <c r="H105" s="11">
         <v>85.0</v>
       </c>
       <c r="I105" t="s" s="11">
-        <v>171</v>
+        <v>181</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="10">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="B106" t="s" s="0">
         <v>38</v>
@@ -10048,129 +9889,129 @@
       </c>
       <c r="D106" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 40. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 100. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E106" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F106" t="s" s="5">
         <v>54</v>
       </c>
       <c r="G106" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:40</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:100</t>
         </is>
       </c>
       <c r="H106" s="10">
         <v>85.0</v>
       </c>
       <c r="I106" t="s" s="10">
-        <v>173</v>
+        <v>183</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="11">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B107" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C107" t="s" s="4">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D107" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 112. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E107" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F107" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F107" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G107" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:47</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:112</t>
         </is>
       </c>
       <c r="H107" s="11">
         <v>85.0</v>
       </c>
       <c r="I107" t="s" s="11">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="10">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="B108" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C108" t="s" s="0">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D108" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 113. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E108" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F108" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F108" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G108" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:61</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:113</t>
         </is>
       </c>
       <c r="H108" s="10">
         <v>85.0</v>
       </c>
       <c r="I108" t="s" s="10">
-        <v>177</v>
+        <v>187</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="11">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="B109" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C109" t="s" s="4">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D109" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 62. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E109" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F109" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F109" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G109" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:62</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
         </is>
       </c>
       <c r="H109" s="11">
         <v>85.0</v>
       </c>
       <c r="I109" t="s" s="11">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="10">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="B110" t="s" s="0">
         <v>38</v>
@@ -10180,30 +10021,30 @@
       </c>
       <c r="D110" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 70. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E110" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F110" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G110" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:70</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
         </is>
       </c>
       <c r="H110" s="10">
         <v>85.0</v>
       </c>
       <c r="I110" t="s" s="10">
-        <v>181</v>
+        <v>191</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="11">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B111" t="s" s="4">
         <v>38</v>
@@ -10213,96 +10054,96 @@
       </c>
       <c r="D111" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 100. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E111" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F111" t="s" s="5">
         <v>54</v>
       </c>
       <c r="G111" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:100</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
         </is>
       </c>
       <c r="H111" s="11">
         <v>85.0</v>
       </c>
       <c r="I111" t="s" s="11">
-        <v>183</v>
+        <v>193</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="10">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="B112" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C112" t="s" s="0">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D112" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 112. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E112" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F112" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F112" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G112" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:112</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
         </is>
       </c>
       <c r="H112" s="10">
         <v>85.0</v>
       </c>
       <c r="I112" t="s" s="10">
-        <v>185</v>
+        <v>195</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="11">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="B113" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C113" t="s" s="4">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D113" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 113. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E113" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F113" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F113" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G113" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:113</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
         </is>
       </c>
       <c r="H113" s="11">
         <v>85.0</v>
       </c>
       <c r="I113" t="s" s="11">
-        <v>187</v>
+        <v>197</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="10">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B114" t="s" s="0">
         <v>38</v>
@@ -10312,558 +10153,558 @@
       </c>
       <c r="D114" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 30. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E114" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F114" t="s" s="7">
         <v>43</v>
       </c>
       <c r="G114" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:30</t>
         </is>
       </c>
       <c r="H114" s="10">
         <v>85.0</v>
       </c>
       <c r="I114" t="s" s="10">
-        <v>189</v>
+        <v>199</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="11">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="B115" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C115" t="s" s="4">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D115" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 31. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E115" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F115" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F115" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G115" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:31</t>
         </is>
       </c>
       <c r="H115" s="11">
         <v>85.0</v>
       </c>
       <c r="I115" t="s" s="11">
-        <v>191</v>
+        <v>201</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="10">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="B116" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C116" t="s" s="0">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D116" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 32. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E116" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F116" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F116" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G116" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:32</t>
         </is>
       </c>
       <c r="H116" s="10">
         <v>85.0</v>
       </c>
       <c r="I116" t="s" s="10">
-        <v>193</v>
+        <v>203</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="11">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B117" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C117" t="s" s="4">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D117" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 34. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E117" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F117" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G117" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:34</t>
         </is>
       </c>
       <c r="H117" s="11">
         <v>85.0</v>
       </c>
       <c r="I117" t="s" s="11">
-        <v>195</v>
+        <v>205</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="10">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="B118" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C118" t="s" s="0">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D118" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E118" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F118" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F118" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G118" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:35</t>
         </is>
       </c>
       <c r="H118" s="10">
         <v>85.0</v>
       </c>
       <c r="I118" t="s" s="10">
-        <v>197</v>
+        <v>207</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="11">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="B119" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C119" t="s" s="4">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D119" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 30. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 36. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E119" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F119" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F119" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G119" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:30</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:36</t>
         </is>
       </c>
       <c r="H119" s="11">
         <v>85.0</v>
       </c>
       <c r="I119" t="s" s="11">
-        <v>199</v>
+        <v>209</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="10">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B120" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C120" t="s" s="0">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D120" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 31. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 38. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E120" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F120" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F120" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G120" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:31</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:38</t>
         </is>
       </c>
       <c r="H120" s="10">
         <v>85.0</v>
       </c>
       <c r="I120" t="s" s="10">
-        <v>201</v>
+        <v>211</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="11">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B121" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C121" t="s" s="4">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D121" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 32. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 39. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E121" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F121" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F121" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G121" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:32</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:39</t>
         </is>
       </c>
       <c r="H121" s="11">
         <v>85.0</v>
       </c>
       <c r="I121" t="s" s="11">
-        <v>203</v>
+        <v>213</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="10">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="B122" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C122" t="s" s="0">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D122" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 34. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 40. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E122" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F122" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F122" t="s" s="5">
+        <v>54</v>
       </c>
       <c r="G122" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:34</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:40</t>
         </is>
       </c>
       <c r="H122" s="10">
         <v>85.0</v>
       </c>
       <c r="I122" t="s" s="10">
-        <v>205</v>
+        <v>215</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="11">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="B123" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C123" t="s" s="4">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D123" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 42. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E123" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F123" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G123" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:35</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:42</t>
         </is>
       </c>
       <c r="H123" s="11">
         <v>85.0</v>
       </c>
       <c r="I123" t="s" s="11">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="10">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="B124" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C124" t="s" s="0">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D124" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 36. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 43. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E124" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F124" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G124" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:36</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:43</t>
         </is>
       </c>
       <c r="H124" s="10">
         <v>85.0</v>
       </c>
       <c r="I124" t="s" s="10">
-        <v>209</v>
+        <v>219</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="11">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B125" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C125" t="s" s="4">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D125" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 38. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 44. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E125" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F125" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F125" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G125" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:38</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:44</t>
         </is>
       </c>
       <c r="H125" s="11">
         <v>85.0</v>
       </c>
       <c r="I125" t="s" s="11">
-        <v>211</v>
+        <v>221</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="10">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B126" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C126" t="s" s="0">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D126" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 39. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 46. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E126" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F126" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F126" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G126" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:39</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:46</t>
         </is>
       </c>
       <c r="H126" s="10">
         <v>85.0</v>
       </c>
       <c r="I126" t="s" s="10">
-        <v>213</v>
+        <v>223</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="11">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="B127" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C127" t="s" s="4">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D127" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 40. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E127" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F127" t="s" s="5">
-        <v>54</v>
+        <v>408</v>
+      </c>
+      <c r="F127" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G127" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:40</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:47</t>
         </is>
       </c>
       <c r="H127" s="11">
         <v>85.0</v>
       </c>
       <c r="I127" t="s" s="11">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="10">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B128" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C128" t="s" s="0">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D128" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 42. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 48. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E128" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F128" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F128" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G128" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:42</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:48</t>
         </is>
       </c>
       <c r="H128" s="10">
         <v>85.0</v>
       </c>
       <c r="I128" t="s" s="10">
-        <v>217</v>
+        <v>227</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="11">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B129" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C129" t="s" s="4">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D129" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 43. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 57. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E129" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F129" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G129" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:43</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:57</t>
         </is>
       </c>
       <c r="H129" s="11">
         <v>85.0</v>
       </c>
       <c r="I129" t="s" s="11">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="10">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B130" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C130" t="s" s="0">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D130" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 44. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 60. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E130" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F130" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G130" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:44</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:60</t>
         </is>
       </c>
       <c r="H130" s="10">
         <v>85.0</v>
       </c>
       <c r="I130" t="s" s="10">
-        <v>221</v>
+        <v>231</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="11">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B131" t="s" s="4">
         <v>38</v>
@@ -10873,96 +10714,96 @@
       </c>
       <c r="D131" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 46. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E131" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F131" t="s" s="7">
         <v>43</v>
       </c>
       <c r="G131" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:46</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:61</t>
         </is>
       </c>
       <c r="H131" s="11">
         <v>85.0</v>
       </c>
       <c r="I131" t="s" s="11">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="10">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="B132" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C132" t="s" s="0">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D132" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 71. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E132" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F132" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F132" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G132" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:47</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:71</t>
         </is>
       </c>
       <c r="H132" s="10">
         <v>85.0</v>
       </c>
       <c r="I132" t="s" s="10">
-        <v>225</v>
+        <v>235</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="11">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B133" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C133" t="s" s="4">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D133" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 48. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 72. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E133" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F133" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F133" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G133" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:48</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:72</t>
         </is>
       </c>
       <c r="H133" s="11">
         <v>85.0</v>
       </c>
       <c r="I133" t="s" s="11">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="10">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B134" t="s" s="0">
         <v>38</v>
@@ -10972,30 +10813,30 @@
       </c>
       <c r="D134" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 57. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 73. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E134" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F134" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G134" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:57</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:73</t>
         </is>
       </c>
       <c r="H134" s="10">
         <v>85.0</v>
       </c>
       <c r="I134" t="s" s="10">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="11">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B135" t="s" s="4">
         <v>38</v>
@@ -11005,63 +10846,63 @@
       </c>
       <c r="D135" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 60. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 79. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E135" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F135" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G135" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:60</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:79</t>
         </is>
       </c>
       <c r="H135" s="11">
         <v>85.0</v>
       </c>
       <c r="I135" t="s" s="11">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="10">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B136" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C136" t="s" s="0">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D136" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 101. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E136" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F136" t="s" s="7">
-        <v>43</v>
+        <v>408</v>
+      </c>
+      <c r="F136" t="s" s="6">
+        <v>19</v>
       </c>
       <c r="G136" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:61</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:101</t>
         </is>
       </c>
       <c r="H136" s="10">
         <v>85.0</v>
       </c>
       <c r="I136" t="s" s="10">
-        <v>233</v>
+        <v>243</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="11">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B137" t="s" s="4">
         <v>38</v>
@@ -11071,30 +10912,30 @@
       </c>
       <c r="D137" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 71. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 105. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E137" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F137" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G137" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:71</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:105</t>
         </is>
       </c>
       <c r="H137" s="11">
         <v>85.0</v>
       </c>
       <c r="I137" t="s" s="11">
-        <v>235</v>
+        <v>245</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="10">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B138" t="s" s="0">
         <v>38</v>
@@ -11104,63 +10945,63 @@
       </c>
       <c r="D138" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 72. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 109. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E138" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F138" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G138" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:72</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:109</t>
         </is>
       </c>
       <c r="H138" s="10">
         <v>85.0</v>
       </c>
       <c r="I138" t="s" s="10">
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="11">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B139" t="s" s="4">
         <v>38</v>
       </c>
       <c r="C139" t="s" s="4">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D139" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 73. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 113. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E139" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F139" t="s" s="6">
-        <v>19</v>
+        <v>408</v>
+      </c>
+      <c r="F139" t="s" s="7">
+        <v>43</v>
       </c>
       <c r="G139" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:73</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:113</t>
         </is>
       </c>
       <c r="H139" s="11">
         <v>85.0</v>
       </c>
       <c r="I139" t="s" s="11">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="10">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B140" t="s" s="0">
         <v>38</v>
@@ -11170,190 +11011,58 @@
       </c>
       <c r="D140" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 79. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 117. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E140" t="s" s="10">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F140" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G140" t="inlineStr" s="14">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:79</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:117</t>
         </is>
       </c>
       <c r="H140" s="10">
         <v>85.0</v>
       </c>
       <c r="I140" t="s" s="10">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="11">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B141" t="s" s="4">
-        <v>38</v>
+        <v>253</v>
       </c>
       <c r="C141" t="s" s="4">
-        <v>39</v>
+        <v>254</v>
       </c>
       <c r="D141" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 101. This may indicate an inadvertently copied AI snippet.</t>
+          <t>The primary audit log (ai_scanner.log) is missing. CERT-In mandates active logging for incident readiness and forensic timelines.</t>
         </is>
       </c>
       <c r="E141" t="s" s="11">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="F141" t="s" s="6">
         <v>19</v>
       </c>
       <c r="G141" t="inlineStr" s="15">
         <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:101</t>
+          <t>ai_scanner.log</t>
         </is>
       </c>
       <c r="H141" s="11">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="I141" t="s" s="11">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s" s="10">
-        <v>244</v>
-      </c>
-      <c r="B142" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="C142" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="D142" t="inlineStr" s="14">
-        <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 105. This may indicate an inadvertently copied AI snippet.</t>
-        </is>
-      </c>
-      <c r="E142" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F142" t="s" s="6">
-        <v>19</v>
-      </c>
-      <c r="G142" t="inlineStr" s="14">
-        <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:105</t>
-        </is>
-      </c>
-      <c r="H142" s="10">
-        <v>85.0</v>
-      </c>
-      <c r="I142" t="s" s="10">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s" s="11">
-        <v>246</v>
-      </c>
-      <c r="B143" t="s" s="4">
-        <v>38</v>
-      </c>
-      <c r="C143" t="s" s="4">
-        <v>39</v>
-      </c>
-      <c r="D143" t="inlineStr" s="15">
-        <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 109. This may indicate an inadvertently copied AI snippet.</t>
-        </is>
-      </c>
-      <c r="E143" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F143" t="s" s="6">
-        <v>19</v>
-      </c>
-      <c r="G143" t="inlineStr" s="15">
-        <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:109</t>
-        </is>
-      </c>
-      <c r="H143" s="11">
-        <v>85.0</v>
-      </c>
-      <c r="I143" t="s" s="11">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s" s="10">
-        <v>248</v>
-      </c>
-      <c r="B144" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="C144" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="D144" t="inlineStr" s="14">
-        <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 113. This may indicate an inadvertently copied AI snippet.</t>
-        </is>
-      </c>
-      <c r="E144" t="s" s="10">
-        <v>421</v>
-      </c>
-      <c r="F144" t="s" s="7">
-        <v>43</v>
-      </c>
-      <c r="G144" t="inlineStr" s="14">
-        <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:113</t>
-        </is>
-      </c>
-      <c r="H144" s="10">
-        <v>85.0</v>
-      </c>
-      <c r="I144" t="s" s="10">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s" s="11">
-        <v>250</v>
-      </c>
-      <c r="B145" t="s" s="4">
-        <v>38</v>
-      </c>
-      <c r="C145" t="s" s="4">
-        <v>39</v>
-      </c>
-      <c r="D145" t="inlineStr" s="15">
-        <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 117. This may indicate an inadvertently copied AI snippet.</t>
-        </is>
-      </c>
-      <c r="E145" t="s" s="11">
-        <v>421</v>
-      </c>
-      <c r="F145" t="s" s="6">
-        <v>19</v>
-      </c>
-      <c r="G145" t="inlineStr" s="15">
-        <is>
-          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:117</t>
-        </is>
-      </c>
-      <c r="H145" s="11">
-        <v>85.0</v>
-      </c>
-      <c r="I145" t="s" s="11">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -11371,33 +11080,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>422</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" t="s" s="1">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="C3" t="s" s="1">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="D3" t="s" s="1">
-        <v>426</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="B4" t="s" s="10">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="C4" s="10">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s" s="7">
         <v>43</v>
@@ -11405,13 +11114,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="4">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="B5" t="s" s="11">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="C5" s="11">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s" s="6">
         <v>19</v>
@@ -11419,13 +11128,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="B6" t="s" s="10">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="C6" s="10">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s" s="6">
         <v>19</v>
@@ -11433,45 +11142,45 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="4">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="B7" t="s" s="11">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="C7" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="s" s="8">
-        <v>433</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="B8" t="s" s="10">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="C8" s="10">
         <v>15</v>
       </c>
       <c r="D8" t="s" s="8">
-        <v>433</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9"/>
     <row r="10">
       <c r="A10" t="s" s="9">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="B10" s="10">
-        <v>64.9</v>
+        <v>67.3</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>367</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -11487,23 +11196,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>437</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="B2" s="10">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="4">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="B3" s="11">
         <v>15</v>
@@ -11511,7 +11220,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="B4" s="10">
         <v>12</v>
@@ -11519,17 +11228,9 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="4">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="B5" s="11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>419</v>
-      </c>
-      <c r="B6" s="10">
         <v>2</v>
       </c>
     </row>
@@ -11549,7 +11250,7 @@
         <v>5</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>437</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2">
@@ -11565,7 +11266,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="11">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
@@ -11581,7 +11282,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="10">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/System Scanner/test_report.xlsx
+++ b/System Scanner/test_report.xlsx
@@ -10,7 +10,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="342">
   <si>
     <t>Finding ID</t>
   </si>
@@ -36,85 +36,37 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>3f87adec</t>
-  </si>
-  <si>
-    <t>PackageScanner</t>
-  </si>
-  <si>
-    <t>[UNVERIFIED] Package: google-generativeai (0.8.6)</t>
+    <t>Setting Name</t>
+  </si>
+  <si>
+    <t>Value / Source</t>
+  </si>
+  <si>
+    <t>21b57b46</t>
+  </si>
+  <si>
+    <t>SystemScanner</t>
+  </si>
+  <si>
+    <t>Host Machine: AJINKYA-PATIL</t>
   </si>
   <si>
     <t>INFO</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:42.270695</t>
-  </si>
-  <si>
-    <t>6578aa56</t>
-  </si>
-  <si>
-    <t>[UNVERIFIED] Package: huggingface_hub (1.18.0)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.271667</t>
-  </si>
-  <si>
-    <t>2eebdb72</t>
-  </si>
-  <si>
-    <t>[UNVERIFIED] Package: torch (2.12.0)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.279702</t>
-  </si>
-  <si>
-    <t>7deea02c</t>
-  </si>
-  <si>
-    <t>[UNVERIFIED] Package: transformers (5.10.2)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.292673</t>
-  </si>
-  <si>
-    <t>131857a3</t>
-  </si>
-  <si>
-    <t>[UNVERIFIED] NPM Global: @github/copilot (1.0.36)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.347126</t>
-  </si>
-  <si>
-    <t>cc182253</t>
-  </si>
-  <si>
-    <t>[UNVERIFIED] NPM Global: @openai/codex (0.125.0)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.348889</t>
-  </si>
-  <si>
-    <t>Setting Name</t>
-  </si>
-  <si>
-    <t>Value / Source</t>
-  </si>
-  <si>
-    <t>44d88412</t>
-  </si>
-  <si>
-    <t>SystemScanner</t>
-  </si>
-  <si>
-    <t>Host Machine: YADNESH</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.139259</t>
-  </si>
-  <si>
-    <t>a209d487</t>
+    <t>2026-06-24T11:57:59.671698</t>
+  </si>
+  <si>
+    <t>9d1e1291</t>
+  </si>
+  <si>
+    <t>GPU Detected: NVIDIA GeForce GTX 1650</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:00.807239</t>
+  </si>
+  <si>
+    <t>626d8fef</t>
   </si>
   <si>
     <t>APIScanner</t>
@@ -126,49 +78,58 @@
     <t>HIGH</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:41.754180</t>
-  </si>
-  <si>
-    <t>3c8f6587</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.754618</t>
-  </si>
-  <si>
-    <t>fe86e1d0</t>
+    <t>2026-06-24T11:58:02.974876</t>
+  </si>
+  <si>
+    <t>aa7e9efe</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:02.975159</t>
+  </si>
+  <si>
+    <t>9b649a98</t>
   </si>
   <si>
     <t>Exposed Generic API Key/Token</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:41.755466</t>
-  </si>
-  <si>
-    <t>638d5250</t>
+    <t>2026-06-24T11:58:02.975424</t>
+  </si>
+  <si>
+    <t>4afec278</t>
   </si>
   <si>
     <t>Exposed AWS Access Key ID</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:41.755535</t>
-  </si>
-  <si>
-    <t>f0cf4b5a</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.756486</t>
-  </si>
-  <si>
-    <t>e74fd142</t>
+    <t>2026-06-24T11:58:02.975458</t>
+  </si>
+  <si>
+    <t>3f066f60</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:02.975733</t>
+  </si>
+  <si>
+    <t>62054a10</t>
   </si>
   <si>
     <t>Environment Variable: ANTIGRAVITY_CSRF_TOKEN</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:41.945269</t>
-  </si>
-  <si>
-    <t>2d616212</t>
+    <t>2026-06-24T11:58:03.041639</t>
+  </si>
+  <si>
+    <t>f4d7d135</t>
+  </si>
+  <si>
+    <t>Environment Variable: GEMINI_API_KEY</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:03.041738</t>
+  </si>
+  <si>
+    <t>56755203</t>
   </si>
   <si>
     <t>LicenseScanner</t>
@@ -177,10 +138,10 @@
     <t>Code Snippet: GPL Mention</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:40.748520</t>
-  </si>
-  <si>
-    <t>a8249f3a</t>
+    <t>2026-06-24T11:58:04.158402</t>
+  </si>
+  <si>
+    <t>5459023e</t>
   </si>
   <si>
     <t>Code Snippet: LGPL Mention</t>
@@ -189,31 +150,31 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:40.877894</t>
-  </si>
-  <si>
-    <t>4f2f0605</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:40.881087</t>
-  </si>
-  <si>
-    <t>8c0f1937</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:40.882403</t>
-  </si>
-  <si>
-    <t>bd6da335</t>
+    <t>2026-06-24T11:58:04.453813</t>
+  </si>
+  <si>
+    <t>f770e7c7</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.454375</t>
+  </si>
+  <si>
+    <t>9b57cac8</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.454702</t>
+  </si>
+  <si>
+    <t>ffb59131</t>
   </si>
   <si>
     <t>Code Snippet: Proprietary Mention</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:40.886468</t>
-  </si>
-  <si>
-    <t>6811b580</t>
+    <t>2026-06-24T11:58:04.455128</t>
+  </si>
+  <si>
+    <t>6e51210f</t>
   </si>
   <si>
     <t>Code Snippet: AGPL Mention</t>
@@ -222,598 +183,598 @@
     <t>CRITICAL</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:40.890047</t>
-  </si>
-  <si>
-    <t>ca075f5a</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:40.892578</t>
-  </si>
-  <si>
-    <t>23857f99</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:40.900129</t>
-  </si>
-  <si>
-    <t>09a7564b</t>
+    <t>2026-06-24T11:58:04.455457</t>
+  </si>
+  <si>
+    <t>e07c0383</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.455888</t>
+  </si>
+  <si>
+    <t>4bac397e</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.456245</t>
+  </si>
+  <si>
+    <t>d384e63a</t>
   </si>
   <si>
     <t>Code Snippet: Polyform Shield Mention</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:40.905640</t>
-  </si>
-  <si>
-    <t>6b5b3f58</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:40.909803</t>
-  </si>
-  <si>
-    <t>8771aff1</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:40.911670</t>
-  </si>
-  <si>
-    <t>77a127fc</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:40.914395</t>
-  </si>
-  <si>
-    <t>d6e8abdb</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:40.917361</t>
-  </si>
-  <si>
-    <t>fb3fdbf9</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:40.921938</t>
-  </si>
-  <si>
-    <t>bc2b0fd6</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:40.927330</t>
-  </si>
-  <si>
-    <t>5dabba7d</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:40.931202</t>
-  </si>
-  <si>
-    <t>9f2bf62c</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:40.940209</t>
-  </si>
-  <si>
-    <t>4bd5a491</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:40.946705</t>
-  </si>
-  <si>
-    <t>2f984057</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:40.956422</t>
-  </si>
-  <si>
-    <t>383c91fa</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:40.969943</t>
-  </si>
-  <si>
-    <t>1da6f08a</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:40.975630</t>
-  </si>
-  <si>
-    <t>b6ef2372</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:40.978387</t>
-  </si>
-  <si>
-    <t>8076f204</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.006469</t>
-  </si>
-  <si>
-    <t>87e2eb22</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.009108</t>
-  </si>
-  <si>
-    <t>494b2081</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.012943</t>
-  </si>
-  <si>
-    <t>6a4a42c6</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.021320</t>
-  </si>
-  <si>
-    <t>54594aa4</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.038274</t>
-  </si>
-  <si>
-    <t>d79c2e08</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.046516</t>
-  </si>
-  <si>
-    <t>40d0922f</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.061008</t>
-  </si>
-  <si>
-    <t>f6503980</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.076540</t>
-  </si>
-  <si>
-    <t>230c7b90</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.080154</t>
-  </si>
-  <si>
-    <t>9da4a599</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.082943</t>
-  </si>
-  <si>
-    <t>46dc0093</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.090709</t>
-  </si>
-  <si>
-    <t>802968b5</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.096858</t>
-  </si>
-  <si>
-    <t>23bebbf2</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.099293</t>
-  </si>
-  <si>
-    <t>76f68e68</t>
+    <t>2026-06-24T11:58:04.456671</t>
+  </si>
+  <si>
+    <t>23cd85c5</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.457409</t>
+  </si>
+  <si>
+    <t>3d39bc3e</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.457867</t>
+  </si>
+  <si>
+    <t>b6d44b8d</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.458806</t>
+  </si>
+  <si>
+    <t>3177e347</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.459286</t>
+  </si>
+  <si>
+    <t>043ba1a5</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.459566</t>
+  </si>
+  <si>
+    <t>320070ac</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.459902</t>
+  </si>
+  <si>
+    <t>9cc92aae</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.460536</t>
+  </si>
+  <si>
+    <t>3f1b8ad9</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.461020</t>
+  </si>
+  <si>
+    <t>c960d199</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.461406</t>
+  </si>
+  <si>
+    <t>9b7ddf61</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.461879</t>
+  </si>
+  <si>
+    <t>a2ba6775</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.462363</t>
+  </si>
+  <si>
+    <t>39bef3e7</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.462815</t>
+  </si>
+  <si>
+    <t>e26134e1</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.463179</t>
+  </si>
+  <si>
+    <t>ce9823c8</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.470307</t>
+  </si>
+  <si>
+    <t>7c9053bf</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.470587</t>
+  </si>
+  <si>
+    <t>9d7b6cad</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.470924</t>
+  </si>
+  <si>
+    <t>ac59caf6</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.471220</t>
+  </si>
+  <si>
+    <t>3b440b96</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.471488</t>
+  </si>
+  <si>
+    <t>3449d6cf</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.472047</t>
+  </si>
+  <si>
+    <t>7c6e2ef8</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.472418</t>
+  </si>
+  <si>
+    <t>0e32fadc</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.472759</t>
+  </si>
+  <si>
+    <t>eca02783</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.473220</t>
+  </si>
+  <si>
+    <t>a42d7bd8</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.473590</t>
+  </si>
+  <si>
+    <t>47c39d33</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.474294</t>
+  </si>
+  <si>
+    <t>daff2f5e</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.474750</t>
+  </si>
+  <si>
+    <t>e607f197</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.475490</t>
+  </si>
+  <si>
+    <t>6230f287</t>
   </si>
   <si>
     <t>Code License: MIT Header</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:41.872092</t>
-  </si>
-  <si>
-    <t>2f415d13</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.898699</t>
-  </si>
-  <si>
-    <t>39df49fa</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.916390</t>
-  </si>
-  <si>
-    <t>0bd76aad</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.929769</t>
-  </si>
-  <si>
-    <t>741f33f6</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.941950</t>
-  </si>
-  <si>
-    <t>4a34b0f3</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.947516</t>
-  </si>
-  <si>
-    <t>581d0db2</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.949160</t>
-  </si>
-  <si>
-    <t>a4d49d63</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.949986</t>
-  </si>
-  <si>
-    <t>66b1a34d</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.951802</t>
-  </si>
-  <si>
-    <t>fa0048a6</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.952742</t>
-  </si>
-  <si>
-    <t>c6e228f5</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.953693</t>
-  </si>
-  <si>
-    <t>c88579f1</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.954911</t>
-  </si>
-  <si>
-    <t>9820560f</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.955899</t>
-  </si>
-  <si>
-    <t>8310bc5d</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.957051</t>
-  </si>
-  <si>
-    <t>35090e7d</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.957824</t>
-  </si>
-  <si>
-    <t>48ade3f4</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.958792</t>
-  </si>
-  <si>
-    <t>cefa6d52</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.959591</t>
-  </si>
-  <si>
-    <t>393700c4</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.960583</t>
-  </si>
-  <si>
-    <t>445329a6</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.961530</t>
-  </si>
-  <si>
-    <t>86e03f64</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.962460</t>
-  </si>
-  <si>
-    <t>cb358ed5</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.963217</t>
-  </si>
-  <si>
-    <t>cd35150a</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.964039</t>
-  </si>
-  <si>
-    <t>e40a1f5b</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.965063</t>
-  </si>
-  <si>
-    <t>4a3316c3</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.966305</t>
-  </si>
-  <si>
-    <t>278ae0e2</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.344605</t>
-  </si>
-  <si>
-    <t>ed47d8ac</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.345314</t>
-  </si>
-  <si>
-    <t>086c4a1d</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.346586</t>
-  </si>
-  <si>
-    <t>088397c1</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.347502</t>
-  </si>
-  <si>
-    <t>10be08da</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.348362</t>
-  </si>
-  <si>
-    <t>6f29f00f</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.349184</t>
-  </si>
-  <si>
-    <t>1b9d38ec</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.350378</t>
-  </si>
-  <si>
-    <t>a12ef15d</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.351302</t>
-  </si>
-  <si>
-    <t>3017faf8</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.352158</t>
-  </si>
-  <si>
-    <t>739a2ca9</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.354034</t>
-  </si>
-  <si>
-    <t>a2c68493</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.355186</t>
-  </si>
-  <si>
-    <t>0bdb03d8</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.355824</t>
-  </si>
-  <si>
-    <t>b1c0c8af</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.360783</t>
-  </si>
-  <si>
-    <t>6b6ca1f3</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.361442</t>
-  </si>
-  <si>
-    <t>2831ea4a</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.362256</t>
-  </si>
-  <si>
-    <t>12e694e3</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.362630</t>
-  </si>
-  <si>
-    <t>107cfa84</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.363148</t>
-  </si>
-  <si>
-    <t>ce662857</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.363749</t>
-  </si>
-  <si>
-    <t>f331b1c1</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.365287</t>
-  </si>
-  <si>
-    <t>40b8ddda</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.366467</t>
-  </si>
-  <si>
-    <t>8d031d3e</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.368074</t>
-  </si>
-  <si>
-    <t>1a0d793f</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.369669</t>
-  </si>
-  <si>
-    <t>9737a9d4</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.370869</t>
-  </si>
-  <si>
-    <t>77641ccc</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.372107</t>
-  </si>
-  <si>
-    <t>dbd9c590</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.373595</t>
-  </si>
-  <si>
-    <t>134ea8fc</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.374565</t>
-  </si>
-  <si>
-    <t>4a2f90f7</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.375309</t>
-  </si>
-  <si>
-    <t>86ea0d48</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.375931</t>
-  </si>
-  <si>
-    <t>3d330b12</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.376545</t>
-  </si>
-  <si>
-    <t>fb990307</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.377103</t>
-  </si>
-  <si>
-    <t>03dce855</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.377628</t>
-  </si>
-  <si>
-    <t>fc4e423f</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.378217</t>
-  </si>
-  <si>
-    <t>7b66fc9b</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.378943</t>
-  </si>
-  <si>
-    <t>3ab668e5</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.379472</t>
-  </si>
-  <si>
-    <t>e694414c</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.380050</t>
-  </si>
-  <si>
-    <t>00246510</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.380741</t>
-  </si>
-  <si>
-    <t>9a49b5c2</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.381470</t>
-  </si>
-  <si>
-    <t>a010b939</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.382369</t>
-  </si>
-  <si>
-    <t>1b926a2e</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.382964</t>
-  </si>
-  <si>
-    <t>4814bd13</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.383986</t>
-  </si>
-  <si>
-    <t>bb73721c</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.384564</t>
-  </si>
-  <si>
-    <t>8b8c5127</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.385152</t>
-  </si>
-  <si>
-    <t>c4a2b34f</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.385739</t>
-  </si>
-  <si>
-    <t>a28abd69</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.386241</t>
-  </si>
-  <si>
-    <t>95b145c9</t>
+    <t>2026-06-24T11:58:04.681205</t>
+  </si>
+  <si>
+    <t>d606205a</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.684868</t>
+  </si>
+  <si>
+    <t>48ae6d42</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.685153</t>
+  </si>
+  <si>
+    <t>d0ac9bd7</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.685437</t>
+  </si>
+  <si>
+    <t>064fa7f6</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.685879</t>
+  </si>
+  <si>
+    <t>5dfd37de</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.686433</t>
+  </si>
+  <si>
+    <t>b76125ef</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.687048</t>
+  </si>
+  <si>
+    <t>fc28fd58</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.687530</t>
+  </si>
+  <si>
+    <t>b55e2233</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.688526</t>
+  </si>
+  <si>
+    <t>56671c48</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.689192</t>
+  </si>
+  <si>
+    <t>70867fad</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.689561</t>
+  </si>
+  <si>
+    <t>8eb079ae</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.690276</t>
+  </si>
+  <si>
+    <t>9019d3a9</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.690736</t>
+  </si>
+  <si>
+    <t>bcee3943</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.691363</t>
+  </si>
+  <si>
+    <t>a3fbbb4a</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.691716</t>
+  </si>
+  <si>
+    <t>84dfea16</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.692095</t>
+  </si>
+  <si>
+    <t>ab30f69d</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.692386</t>
+  </si>
+  <si>
+    <t>53c261e6</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.692865</t>
+  </si>
+  <si>
+    <t>a10142c5</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.693234</t>
+  </si>
+  <si>
+    <t>82aab010</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.693693</t>
+  </si>
+  <si>
+    <t>f0392a69</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.694300</t>
+  </si>
+  <si>
+    <t>8fd70a94</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.694839</t>
+  </si>
+  <si>
+    <t>2f50f784</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.695193</t>
+  </si>
+  <si>
+    <t>095b768d</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:04.695653</t>
+  </si>
+  <si>
+    <t>1a4f56f3</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.332506</t>
+  </si>
+  <si>
+    <t>550876f7</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.333204</t>
+  </si>
+  <si>
+    <t>5d17d9f3</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.334001</t>
+  </si>
+  <si>
+    <t>5c287312</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.334692</t>
+  </si>
+  <si>
+    <t>cc1c83d9</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.335537</t>
+  </si>
+  <si>
+    <t>cb3063e8</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.384102</t>
+  </si>
+  <si>
+    <t>d9d25290</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.385067</t>
+  </si>
+  <si>
+    <t>90f6edbb</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.385503</t>
+  </si>
+  <si>
+    <t>86f8eb29</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.386012</t>
+  </si>
+  <si>
+    <t>2e89fce4</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.387102</t>
+  </si>
+  <si>
+    <t>603a032a</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.387871</t>
+  </si>
+  <si>
+    <t>af7c71d9</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.388334</t>
+  </si>
+  <si>
+    <t>384d8db1</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.393707</t>
+  </si>
+  <si>
+    <t>cfe006d4</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.394207</t>
+  </si>
+  <si>
+    <t>2e1dca68</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.394635</t>
+  </si>
+  <si>
+    <t>2385d383</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.395058</t>
+  </si>
+  <si>
+    <t>86bedb29</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.395468</t>
+  </si>
+  <si>
+    <t>7f061e21</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.396076</t>
+  </si>
+  <si>
+    <t>54671924</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.396484</t>
+  </si>
+  <si>
+    <t>939288e8</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.396897</t>
+  </si>
+  <si>
+    <t>d61d09f3</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.397248</t>
+  </si>
+  <si>
+    <t>88fdd9dc</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.397556</t>
+  </si>
+  <si>
+    <t>5e5cd8ea</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.398009</t>
+  </si>
+  <si>
+    <t>39718757</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.398341</t>
+  </si>
+  <si>
+    <t>c14819f8</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.399129</t>
+  </si>
+  <si>
+    <t>9ae0759e</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.399642</t>
+  </si>
+  <si>
+    <t>130e727a</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.400172</t>
+  </si>
+  <si>
+    <t>006e1a08</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.400503</t>
+  </si>
+  <si>
+    <t>3f3513a8</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.400963</t>
+  </si>
+  <si>
+    <t>ac254109</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.401420</t>
+  </si>
+  <si>
+    <t>a626d77c</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.401876</t>
+  </si>
+  <si>
+    <t>cb9e10da</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.402289</t>
+  </si>
+  <si>
+    <t>15bb6c85</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.402706</t>
+  </si>
+  <si>
+    <t>d0158a2b</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.403023</t>
+  </si>
+  <si>
+    <t>849b35ec</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.403330</t>
+  </si>
+  <si>
+    <t>3feab52b</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.403740</t>
+  </si>
+  <si>
+    <t>9e7fb5f5</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.404019</t>
+  </si>
+  <si>
+    <t>232d826f</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.404379</t>
+  </si>
+  <si>
+    <t>1d0845c0</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.404845</t>
+  </si>
+  <si>
+    <t>2dcb3b91</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.405815</t>
+  </si>
+  <si>
+    <t>c5950976</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.406219</t>
+  </si>
+  <si>
+    <t>2b57df91</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.406757</t>
+  </si>
+  <si>
+    <t>322197e7</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.407408</t>
+  </si>
+  <si>
+    <t>0a18ec08</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:06.407836</t>
+  </si>
+  <si>
+    <t>11b4e9d7</t>
   </si>
   <si>
     <t>ComplianceScanner</t>
@@ -822,7 +783,7 @@
     <t>CERT-In Risk: Missing Audit Logging</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:40.633633</t>
+    <t>2026-06-24T11:58:06.383906</t>
   </si>
   <si>
     <t>AI Model / Agent / Runtime</t>
@@ -834,7 +795,7 @@
     <t>Location / Endpoint</t>
   </si>
   <si>
-    <t>4bfca630</t>
+    <t>b2944791</t>
   </si>
   <si>
     <t>Copilot Agent — Registry Configuration Detected</t>
@@ -843,151 +804,151 @@
     <t>AI Agent</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:41.912363</t>
-  </si>
-  <si>
-    <t>1dde31d3</t>
+    <t>2026-06-24T11:58:00.810270</t>
+  </si>
+  <si>
+    <t>877196ff</t>
+  </si>
+  <si>
+    <t>Codex Agent — Registry Configuration Detected</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:00.810311</t>
+  </si>
+  <si>
+    <t>1997eef2</t>
   </si>
   <si>
     <t>ProcessScanner</t>
   </si>
   <si>
-    <t>Antigravity (PID: 1280)</t>
+    <t>Antigravity (PID: 3016)</t>
   </si>
   <si>
     <t>LLM Runtime</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:44.755471</t>
-  </si>
-  <si>
-    <t>7dbc2a87</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 2184)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:47.433042</t>
-  </si>
-  <si>
-    <t>1b7ae0e0</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 2624)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:50.030357</t>
-  </si>
-  <si>
-    <t>e941a5e5</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 7692)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:52.268807</t>
-  </si>
-  <si>
-    <t>fcac4106</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 8564)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:54.450457</t>
-  </si>
-  <si>
-    <t>453898a2</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 11944)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:56.408331</t>
-  </si>
-  <si>
-    <t>a6a01637</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 12452)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:58.344232</t>
-  </si>
-  <si>
-    <t>16d29519</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 14524)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:54:00.229889</t>
-  </si>
-  <si>
-    <t>20baca8f</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 15920)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:54:02.081506</t>
-  </si>
-  <si>
-    <t>f6a8656f</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 17208)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:54:04.005623</t>
-  </si>
-  <si>
-    <t>a5830001</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 18680)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:54:06.084761</t>
-  </si>
-  <si>
-    <t>9249c121</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 18776)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:54:08.659447</t>
-  </si>
-  <si>
-    <t>37ef801a</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 19064)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:54:10.734222</t>
-  </si>
-  <si>
-    <t>649d2c97</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 19248)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:54:12.744815</t>
-  </si>
-  <si>
-    <t>278e4894</t>
-  </si>
-  <si>
-    <t>Antigravity (PID: 21464)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:54:16.118361</t>
-  </si>
-  <si>
-    <t>f0aed76d</t>
+    <t>2026-06-24T11:58:08.316412</t>
+  </si>
+  <si>
+    <t>cb83e0c6</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 7676)</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:11.717748</t>
+  </si>
+  <si>
+    <t>4066e531</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 10244)</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:15.114446</t>
+  </si>
+  <si>
+    <t>9e28f086</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 10364)</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:18.524595</t>
+  </si>
+  <si>
+    <t>39c65843</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 10436)</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:21.898508</t>
+  </si>
+  <si>
+    <t>7ae256af</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 12500)</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:23.884209</t>
+  </si>
+  <si>
+    <t>555cf786</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 13260)</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:25.881733</t>
+  </si>
+  <si>
+    <t>561cdb27</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 15588)</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:27.954177</t>
+  </si>
+  <si>
+    <t>48d764bd</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 15772)</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:30.118712</t>
+  </si>
+  <si>
+    <t>0d851dab</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 16456)</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:32.141676</t>
+  </si>
+  <si>
+    <t>7dd9f606</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 17760)</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:35.402746</t>
+  </si>
+  <si>
+    <t>c43d63d0</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 18604)</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:38.698982</t>
+  </si>
+  <si>
+    <t>4360badb</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 19448)</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:40.725544</t>
+  </si>
+  <si>
+    <t>e54b22fe</t>
+  </si>
+  <si>
+    <t>Antigravity (PID: 20424)</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:42.776897</t>
+  </si>
+  <si>
+    <t>4d4538c1</t>
   </si>
   <si>
     <t>AgentScanner</t>
@@ -996,94 +957,85 @@
     <t>Agent Usage: LangChain Import</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:41.080930</t>
-  </si>
-  <si>
-    <t>222c034b</t>
+    <t>2026-06-24T11:58:00.996921</t>
+  </si>
+  <si>
+    <t>aab4e1ab</t>
   </si>
   <si>
     <t>Agent Usage: CrewAI Import</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:41.087058</t>
-  </si>
-  <si>
-    <t>6d90dbaa</t>
+    <t>2026-06-24T11:58:00.997414</t>
+  </si>
+  <si>
+    <t>6aa76fff</t>
   </si>
   <si>
     <t>Agent Usage: Agent Instantiation</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:41.095511</t>
-  </si>
-  <si>
-    <t>d008a8e6</t>
+    <t>2026-06-24T11:58:00.998004</t>
+  </si>
+  <si>
+    <t>be0c4dbb</t>
   </si>
   <si>
     <t>Agent Usage: Crew Instantiation</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:41.097995</t>
-  </si>
-  <si>
-    <t>21bf9193</t>
+    <t>2026-06-24T11:58:00.998338</t>
+  </si>
+  <si>
+    <t>78ba220d</t>
   </si>
   <si>
     <t>Agent Usage: AssistantAgent Instantiation</t>
   </si>
   <si>
-    <t>2026-06-23T10:53:41.118483</t>
-  </si>
-  <si>
-    <t>68da5f17</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.181688</t>
-  </si>
-  <si>
-    <t>b867c82a</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.226132</t>
-  </si>
-  <si>
-    <t>b89bae4c</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.244335</t>
-  </si>
-  <si>
-    <t>1ac07b05</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.278882</t>
-  </si>
-  <si>
-    <t>bb4544a0</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:41.433555</t>
-  </si>
-  <si>
-    <t>1eea99d1</t>
+    <t>2026-06-24T11:58:00.998633</t>
+  </si>
+  <si>
+    <t>f5e78db0</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:00.999117</t>
+  </si>
+  <si>
+    <t>e8054d25</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:00.999541</t>
+  </si>
+  <si>
+    <t>b6f350cd</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:00.999989</t>
+  </si>
+  <si>
+    <t>bb3dbdf2</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:01.000328</t>
+  </si>
+  <si>
+    <t>2bd86bcf</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:01.004213</t>
+  </si>
+  <si>
+    <t>0c5ed716</t>
   </si>
   <si>
     <t>RuntimeScanner</t>
   </si>
   <si>
-    <t>Ollama Local Directory (Installed)</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.681894</t>
-  </si>
-  <si>
-    <t>b3bc9c01</t>
-  </si>
-  <si>
-    <t>Active LLM Service Port: 8000</t>
-  </si>
-  <si>
-    <t>2026-06-23T10:53:42.683755</t>
+    <t>Active LLM Service Port: 8080</t>
+  </si>
+  <si>
+    <t>2026-06-24T11:58:03.146604</t>
   </si>
 </sst>
 </file>
@@ -1298,186 +1250,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="10">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="D2" t="inlineStr" s="14">
-        <is>
-          <t>Detected installed AI package: google-generativeai (version 0.8.6) Note: This package has not been verified against the baseline database.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr" s="14">
-        <is>
-          <t>C:/Users/ADMIN/AppData/Roaming/Python/Python314/site-packages</t>
-        </is>
-      </c>
-      <c r="F2" t="s" s="8">
-        <v>11</v>
-      </c>
-      <c r="G2" s="10">
-        <v>90.0</v>
-      </c>
-      <c r="H2" t="s" s="10">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="11">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s" s="4">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s" s="4">
-        <v>14</v>
-      </c>
-      <c r="D3" t="inlineStr" s="15">
-        <is>
-          <t>Detected installed AI package: huggingface_hub (version 1.18.0) Note: This package has not been verified against the baseline database.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr" s="15">
-        <is>
-          <t>C:/Users/ADMIN/AppData/Roaming/Python/Python314/site-packages</t>
-        </is>
-      </c>
-      <c r="F3" t="s" s="8">
-        <v>11</v>
-      </c>
-      <c r="G3" s="11">
-        <v>90.0</v>
-      </c>
-      <c r="H3" t="s" s="11">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="10">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="D4" t="inlineStr" s="14">
-        <is>
-          <t>Detected installed AI package: torch (version 2.12.0) Note: This package has not been verified against the baseline database.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr" s="14">
-        <is>
-          <t>C:/Users/ADMIN/AppData/Roaming/Python/Python314/site-packages</t>
-        </is>
-      </c>
-      <c r="F4" t="s" s="8">
-        <v>11</v>
-      </c>
-      <c r="G4" s="10">
-        <v>90.0</v>
-      </c>
-      <c r="H4" t="s" s="10">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="11">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s" s="4">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s" s="4">
-        <v>20</v>
-      </c>
-      <c r="D5" t="inlineStr" s="15">
-        <is>
-          <t>Detected installed AI package: transformers (version 5.10.2) Note: This package has not been verified against the baseline database.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr" s="15">
-        <is>
-          <t>C:/Users/ADMIN/AppData/Roaming/Python/Python314/site-packages</t>
-        </is>
-      </c>
-      <c r="F5" t="s" s="8">
-        <v>11</v>
-      </c>
-      <c r="G5" s="11">
-        <v>90.0</v>
-      </c>
-      <c r="H5" t="s" s="11">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="10">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="D6" t="inlineStr" s="14">
-        <is>
-          <t>Global NPM AI package detected: @github/copilot — GitHub Copilot CLI brings the power of Copilot coding agent directly to your terminal. Note: This package has not been verified against the baseline database.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr" s="14">
-        <is>
-          <t>C:/Users/ADMIN/AppData/Roaming/npm/node_modules/@github/copilot</t>
-        </is>
-      </c>
-      <c r="F6" t="s" s="8">
-        <v>11</v>
-      </c>
-      <c r="G6" s="10">
-        <v>90.0</v>
-      </c>
-      <c r="H6" t="s" s="10">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="11">
-        <v>25</v>
-      </c>
-      <c r="B7" t="s" s="4">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s" s="4">
-        <v>26</v>
-      </c>
-      <c r="D7" t="inlineStr" s="15">
-        <is>
-          <t>Global NPM AI package detected: OpenAI Codex CLI Note: This package has not been verified against the baseline database.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr" s="15">
-        <is>
-          <t>C:/Users/ADMIN/AppData/Roaming/npm/node_modules/@openai/codex</t>
-        </is>
-      </c>
-      <c r="F7" t="s" s="8">
-        <v>11</v>
-      </c>
-      <c r="G7" s="11">
-        <v>90.0</v>
-      </c>
-      <c r="H7" t="s" s="11">
-        <v>27</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1503,13 +1275,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>3</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F1" t="s" s="1">
         <v>5</v>
@@ -1523,3332 +1295,3392 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="10">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D2" t="inlineStr" s="14">
         <is>
-          <t>System scan target identified: YADNESH running Windows 11 (x64)</t>
+          <t>System scan target identified: AJINKYA-PATIL running Windows 11 (x64)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="14">
         <is>
-          <t>hostname=YADNESH</t>
+          <t>hostname=AJINKYA-PATIL</t>
         </is>
       </c>
       <c r="F2" t="s" s="8">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2" s="10">
         <v>100.0</v>
       </c>
       <c r="H2" t="s" s="10">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="11">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s" s="4">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s" s="4">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D3" t="inlineStr" s="15">
         <is>
-          <t>A matching pattern for a OpenAI API Key was discovered in config file 'C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_api_scanner.py' at line 21.</t>
+          <t>A GPU was detected on this machine. GPUs are commonly used to accelerate AI/ML model inference and training.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_api_scanner.py:21</t>
-        </is>
-      </c>
-      <c r="F3" t="s" s="6">
-        <v>37</v>
+          <t>system_gpu_detection</t>
+        </is>
+      </c>
+      <c r="F3" t="s" s="8">
+        <v>13</v>
       </c>
       <c r="G3" s="11">
-        <v>95.0</v>
+        <v>100.0</v>
       </c>
       <c r="H3" t="s" s="11">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="10">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D4" t="inlineStr" s="14">
         <is>
-          <t>A matching pattern for a OpenAI API Key was discovered in config file 'C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_api_scanner.py' at line 30.</t>
+          <t>A matching pattern for a OpenAI API Key was discovered in config file 'D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py' at line 21.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_api_scanner.py:30</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py:21</t>
         </is>
       </c>
       <c r="F4" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G4" s="10">
         <v>95.0</v>
       </c>
       <c r="H4" t="s" s="10">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="11">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s" s="4">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s" s="4">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D5" t="inlineStr" s="15">
         <is>
-          <t>A matching pattern for a Generic API Key/Token was discovered in config file 'C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_api_scanner.py' at line 47.</t>
+          <t>A matching pattern for a OpenAI API Key was discovered in config file 'D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py' at line 30.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_api_scanner.py:47</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py:30</t>
         </is>
       </c>
       <c r="F5" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G5" s="11">
         <v>95.0</v>
       </c>
       <c r="H5" t="s" s="11">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="10">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D6" t="inlineStr" s="14">
         <is>
-          <t>A matching pattern for a AWS Access Key ID was discovered in config file 'C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_api_scanner.py' at line 48.</t>
+          <t>A matching pattern for a Generic API Key/Token was discovered in config file 'D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py' at line 47.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_api_scanner.py:48</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py:47</t>
         </is>
       </c>
       <c r="F6" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G6" s="10">
         <v>95.0</v>
       </c>
       <c r="H6" t="s" s="10">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="11">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s" s="4">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s" s="4">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D7" t="inlineStr" s="15">
         <is>
-          <t>A matching pattern for a OpenAI API Key was discovered in config file 'C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_api_scanner.py' at line 69.</t>
+          <t>A matching pattern for a AWS Access Key ID was discovered in config file 'D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py' at line 48.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_api_scanner.py:69</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py:48</t>
         </is>
       </c>
       <c r="F7" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G7" s="11">
         <v>95.0</v>
       </c>
       <c r="H7" t="s" s="11">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="10">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D8" t="inlineStr" s="14">
         <is>
-          <t>Active environment variable 'ANTIGRAVITY_CSRF_TOKEN' contains a potential Unknown credential.</t>
+          <t>A matching pattern for a OpenAI API Key was discovered in config file 'D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py' at line 69.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="14">
         <is>
-          <t>env://ANTIGRAVITY_CSRF_TOKEN</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_api_scanner.py:69</t>
         </is>
       </c>
       <c r="F8" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G8" s="10">
         <v>95.0</v>
       </c>
       <c r="H8" t="s" s="10">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="11">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s" s="4">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s" s="4">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D9" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'debug_test.py' at line 10. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Active environment variable 'ANTIGRAVITY_CSRF_TOKEN' contains a potential Unknown credential.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/debug_test.py:10</t>
+          <t>env://ANTIGRAVITY_CSRF_TOKEN</t>
         </is>
       </c>
       <c r="F9" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G9" s="11">
-        <v>85.0</v>
+        <v>95.0</v>
       </c>
       <c r="H9" t="s" s="11">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="10">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="D10" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'update_licenses.py' at line 20. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Active environment variable 'GEMINI_API_KEY' contains a potential Google/Gemini credential.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:20</t>
-        </is>
-      </c>
-      <c r="F10" t="s" s="7">
-        <v>58</v>
+          <t>env://GEMINI_API_KEY</t>
+        </is>
+      </c>
+      <c r="F10" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G10" s="10">
-        <v>85.0</v>
+        <v>95.0</v>
       </c>
       <c r="H10" t="s" s="10">
-        <v>59</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="11">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s" s="4">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D11" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 24. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'debug_test.py' at line 10. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:24</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/debug_test.py:10</t>
         </is>
       </c>
       <c r="F11" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G11" s="11">
         <v>85.0</v>
       </c>
       <c r="H11" t="s" s="11">
-        <v>61</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="10">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D12" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 26. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'update_licenses.py' at line 20. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:26</t>
-        </is>
-      </c>
-      <c r="F12" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:20</t>
+        </is>
+      </c>
+      <c r="F12" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G12" s="10">
         <v>85.0</v>
       </c>
       <c r="H12" t="s" s="10">
-        <v>63</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="11">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s" s="4">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="D13" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 29. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 24. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:29</t>
-        </is>
-      </c>
-      <c r="F13" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:24</t>
+        </is>
+      </c>
+      <c r="F13" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G13" s="11">
         <v>85.0</v>
       </c>
       <c r="H13" t="s" s="11">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="10">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="D14" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'update_licenses.py' at line 32. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 26. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:32</t>
-        </is>
-      </c>
-      <c r="F14" t="s" s="5">
-        <v>69</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:26</t>
+        </is>
+      </c>
+      <c r="F14" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G14" s="10">
         <v>85.0</v>
       </c>
       <c r="H14" t="s" s="10">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="11">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s" s="4">
+        <v>52</v>
+      </c>
+      <c r="D15" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 29. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:29</t>
+        </is>
+      </c>
+      <c r="F15" t="s" s="7">
+        <v>45</v>
+      </c>
+      <c r="G15" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H15" t="s" s="11">
         <v>53</v>
-      </c>
-      <c r="C15" t="s" s="4">
-        <v>54</v>
-      </c>
-      <c r="D15" t="inlineStr" s="15">
-        <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr" s="15">
-        <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:35</t>
-        </is>
-      </c>
-      <c r="F15" t="s" s="6">
-        <v>37</v>
-      </c>
-      <c r="G15" s="11">
-        <v>85.0</v>
-      </c>
-      <c r="H15" t="s" s="11">
-        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="10">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D16" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'update_licenses.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'update_licenses.py' at line 32. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:35</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:32</t>
         </is>
       </c>
       <c r="F16" t="s" s="5">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G16" s="10">
         <v>85.0</v>
       </c>
       <c r="H16" t="s" s="10">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="11">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s" s="4">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="D17" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'update_licenses.py' at line 38. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:38</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:35</t>
         </is>
       </c>
       <c r="F17" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G17" s="11">
         <v>85.0</v>
       </c>
       <c r="H17" t="s" s="11">
-        <v>77</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="10">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D18" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 44. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'update_licenses.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:44</t>
-        </is>
-      </c>
-      <c r="F18" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:35</t>
+        </is>
+      </c>
+      <c r="F18" t="s" s="5">
+        <v>56</v>
       </c>
       <c r="G18" s="10">
         <v>85.0</v>
       </c>
       <c r="H18" t="s" s="10">
-        <v>79</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="11">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s" s="4">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D19" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'update_licenses.py' at line 38. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:47</t>
-        </is>
-      </c>
-      <c r="F19" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:38</t>
+        </is>
+      </c>
+      <c r="F19" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G19" s="11">
         <v>85.0</v>
       </c>
       <c r="H19" t="s" s="11">
-        <v>81</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="10">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D20" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'update_licenses.py' at line 67. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 44. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:67</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:44</t>
         </is>
       </c>
       <c r="F20" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G20" s="10">
         <v>85.0</v>
       </c>
       <c r="H20" t="s" s="10">
-        <v>83</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="11">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B21" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s" s="4">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D21" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 72. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:72</t>
-        </is>
-      </c>
-      <c r="F21" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:47</t>
+        </is>
+      </c>
+      <c r="F21" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G21" s="11">
         <v>85.0</v>
       </c>
       <c r="H21" t="s" s="11">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="10">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D22" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 74. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'update_licenses.py' at line 67. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:74</t>
-        </is>
-      </c>
-      <c r="F22" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:67</t>
+        </is>
+      </c>
+      <c r="F22" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G22" s="10">
         <v>85.0</v>
       </c>
       <c r="H22" t="s" s="10">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="11">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s" s="4">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="D23" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 78. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 72. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:78</t>
-        </is>
-      </c>
-      <c r="F23" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:72</t>
+        </is>
+      </c>
+      <c r="F23" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G23" s="11">
         <v>85.0</v>
       </c>
       <c r="H23" t="s" s="11">
-        <v>89</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="10">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="D24" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'update_licenses.py' at line 81. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 74. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:81</t>
-        </is>
-      </c>
-      <c r="F24" t="s" s="5">
-        <v>69</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:74</t>
+        </is>
+      </c>
+      <c r="F24" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G24" s="10">
         <v>85.0</v>
       </c>
       <c r="H24" t="s" s="10">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="11">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s" s="4">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D25" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 85. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 78. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:85</t>
-        </is>
-      </c>
-      <c r="F25" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:78</t>
+        </is>
+      </c>
+      <c r="F25" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G25" s="11">
         <v>85.0</v>
       </c>
       <c r="H25" t="s" s="11">
-        <v>93</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="10">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D26" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'update_licenses.py' at line 85. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'update_licenses.py' at line 81. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:85</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:81</t>
         </is>
       </c>
       <c r="F26" t="s" s="5">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G26" s="10">
         <v>85.0</v>
       </c>
       <c r="H26" t="s" s="10">
-        <v>95</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="11">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s" s="4">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="D27" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'update_licenses.py' at line 88. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'update_licenses.py' at line 85. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:88</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:85</t>
         </is>
       </c>
       <c r="F27" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G27" s="11">
         <v>85.0</v>
       </c>
       <c r="H27" t="s" s="11">
-        <v>97</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="10">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D28" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'update_licenses.py' at line 89. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'update_licenses.py' at line 85. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:89</t>
-        </is>
-      </c>
-      <c r="F28" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:85</t>
+        </is>
+      </c>
+      <c r="F28" t="s" s="5">
+        <v>56</v>
       </c>
       <c r="G28" s="10">
         <v>85.0</v>
       </c>
       <c r="H28" t="s" s="10">
-        <v>99</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="11">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="B29" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s" s="4">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D29" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 95. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'update_licenses.py' at line 88. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:95</t>
-        </is>
-      </c>
-      <c r="F29" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:88</t>
+        </is>
+      </c>
+      <c r="F29" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G29" s="11">
         <v>85.0</v>
       </c>
       <c r="H29" t="s" s="11">
-        <v>101</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="10">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D30" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 99. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'update_licenses.py' at line 89. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/update_licenses.py:99</t>
-        </is>
-      </c>
-      <c r="F30" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:89</t>
+        </is>
+      </c>
+      <c r="F30" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G30" s="10">
         <v>85.0</v>
       </c>
       <c r="H30" t="s" s="10">
-        <v>103</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="11">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C31" t="s" s="4">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D31" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 95. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/verify_implementation.py:21</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:95</t>
         </is>
       </c>
       <c r="F31" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G31" s="11">
         <v>85.0</v>
       </c>
       <c r="H31" t="s" s="11">
-        <v>105</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="10">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D32" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'update_licenses.py' at line 99. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/verify_implementation.py:21</t>
-        </is>
-      </c>
-      <c r="F32" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/update_licenses.py:99</t>
+        </is>
+      </c>
+      <c r="F32" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G32" s="10">
         <v>85.0</v>
       </c>
       <c r="H32" t="s" s="10">
-        <v>107</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="11">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="B33" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s" s="4">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="D33" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 27. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/verify_implementation.py:21</t>
-        </is>
-      </c>
-      <c r="F33" t="s" s="5">
-        <v>69</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:27</t>
+        </is>
+      </c>
+      <c r="F33" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G33" s="11">
         <v>85.0</v>
       </c>
       <c r="H33" t="s" s="11">
-        <v>109</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="10">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="D34" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 27. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/verify_implementation.py:21</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:27</t>
         </is>
       </c>
       <c r="F34" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G34" s="10">
         <v>85.0</v>
       </c>
       <c r="H34" t="s" s="10">
-        <v>111</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="11">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="B35" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C35" t="s" s="4">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D35" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'verify_implementation.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 27. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/verify_implementation.py:21</t>
-        </is>
-      </c>
-      <c r="F35" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:27</t>
+        </is>
+      </c>
+      <c r="F35" t="s" s="5">
+        <v>56</v>
       </c>
       <c r="G35" s="11">
         <v>85.0</v>
       </c>
       <c r="H35" t="s" s="11">
-        <v>113</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="10">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D36" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'verify_implementation.py' at line 27. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/verify_implementation.py:35</t>
-        </is>
-      </c>
-      <c r="F36" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:27</t>
+        </is>
+      </c>
+      <c r="F36" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G36" s="10">
         <v>85.0</v>
       </c>
       <c r="H36" t="s" s="10">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="11">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="B37" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C37" t="s" s="4">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D37" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 36. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'verify_implementation.py' at line 27. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/verify_implementation.py:36</t>
-        </is>
-      </c>
-      <c r="F37" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:27</t>
+        </is>
+      </c>
+      <c r="F37" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G37" s="11">
         <v>85.0</v>
       </c>
       <c r="H37" t="s" s="11">
-        <v>117</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="10">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="D38" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 37. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 41. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/verify_implementation.py:37</t>
-        </is>
-      </c>
-      <c r="F38" t="s" s="5">
-        <v>69</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:41</t>
+        </is>
+      </c>
+      <c r="F38" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G38" s="10">
         <v>85.0</v>
       </c>
       <c r="H38" t="s" s="10">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="11">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B39" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s" s="4">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="D39" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'verify_implementation.py' at line 38. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 42. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/verify_implementation.py:38</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:42</t>
         </is>
       </c>
       <c r="F39" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G39" s="11">
         <v>85.0</v>
       </c>
       <c r="H39" t="s" s="11">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="10">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D40" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'verify_implementation.py' at line 39. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 43. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/verify_implementation.py:39</t>
-        </is>
-      </c>
-      <c r="F40" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:43</t>
+        </is>
+      </c>
+      <c r="F40" t="s" s="5">
+        <v>56</v>
       </c>
       <c r="G40" s="10">
         <v>85.0</v>
       </c>
       <c r="H40" t="s" s="10">
-        <v>123</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="11">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="B41" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C41" t="s" s="4">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D41" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 53. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'verify_implementation.py' at line 44. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/verify_implementation.py:53</t>
-        </is>
-      </c>
-      <c r="F41" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:44</t>
+        </is>
+      </c>
+      <c r="F41" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G41" s="11">
         <v>85.0</v>
       </c>
       <c r="H41" t="s" s="11">
-        <v>125</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="10">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D42" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 54. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'verify_implementation.py' at line 45. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/verify_implementation.py:54</t>
-        </is>
-      </c>
-      <c r="F42" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:45</t>
+        </is>
+      </c>
+      <c r="F42" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G42" s="10">
         <v>85.0</v>
       </c>
       <c r="H42" t="s" s="10">
-        <v>127</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="11">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="B43" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C43" t="s" s="4">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="D43" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 55. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'verify_implementation.py' at line 59. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/verify_implementation.py:55</t>
-        </is>
-      </c>
-      <c r="F43" t="s" s="5">
-        <v>69</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:59</t>
+        </is>
+      </c>
+      <c r="F43" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G43" s="11">
         <v>85.0</v>
       </c>
       <c r="H43" t="s" s="11">
-        <v>129</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="10">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="D44" t="inlineStr" s="14">
         <is>
-          <t>License signature 'MIT' detected in file docstring header of 'license_scanner.py'. Taxonomy classification: Approved. Permissive license. Allowed for enterprise usage.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'verify_implementation.py' at line 60. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:1</t>
-        </is>
-      </c>
-      <c r="F44" t="s" s="8">
-        <v>11</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:60</t>
+        </is>
+      </c>
+      <c r="F44" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G44" s="10">
-        <v>90.0</v>
+        <v>85.0</v>
       </c>
       <c r="H44" t="s" s="10">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="11">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="B45" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C45" t="s" s="4">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D45" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'verify_implementation.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:5</t>
-        </is>
-      </c>
-      <c r="F45" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/verify_implementation.py:61</t>
+        </is>
+      </c>
+      <c r="F45" t="s" s="5">
+        <v>56</v>
       </c>
       <c r="G45" s="11">
         <v>85.0</v>
       </c>
       <c r="H45" t="s" s="11">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="10">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>54</v>
+        <v>118</v>
       </c>
       <c r="D46" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+          <t>License signature 'MIT' detected in file docstring header of 'license_scanner.py'. Taxonomy classification: Approved. Permissive license. Allowed for enterprise usage.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:5</t>
-        </is>
-      </c>
-      <c r="F46" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:1</t>
+        </is>
+      </c>
+      <c r="F46" t="s" s="8">
+        <v>13</v>
       </c>
       <c r="G46" s="10">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="H46" t="s" s="10">
-        <v>136</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="11">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="B47" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C47" t="s" s="4">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="D47" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:5</t>
-        </is>
-      </c>
-      <c r="F47" t="s" s="5">
-        <v>69</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+        </is>
+      </c>
+      <c r="F47" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G47" s="11">
         <v>85.0</v>
       </c>
       <c r="H47" t="s" s="11">
-        <v>138</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="10">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C48" t="s" s="0">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="D48" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:5</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
         </is>
       </c>
       <c r="F48" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G48" s="10">
         <v>85.0</v>
       </c>
       <c r="H48" t="s" s="10">
-        <v>140</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="11">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="B49" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C49" t="s" s="4">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D49" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:5</t>
-        </is>
-      </c>
-      <c r="F49" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+        </is>
+      </c>
+      <c r="F49" t="s" s="5">
+        <v>56</v>
       </c>
       <c r="G49" s="11">
         <v>85.0</v>
       </c>
       <c r="H49" t="s" s="11">
-        <v>142</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="10">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C50" t="s" s="0">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D50" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 7. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:7</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
         </is>
       </c>
       <c r="F50" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G50" s="10">
         <v>85.0</v>
       </c>
       <c r="H50" t="s" s="10">
-        <v>144</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="11">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="B51" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C51" t="s" s="4">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D51" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 7. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 5. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:7</t>
-        </is>
-      </c>
-      <c r="F51" t="s" s="5">
-        <v>69</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:5</t>
+        </is>
+      </c>
+      <c r="F51" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G51" s="11">
         <v>85.0</v>
       </c>
       <c r="H51" t="s" s="11">
-        <v>146</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="10">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C52" t="s" s="0">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D52" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 43. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 7. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:43</t>
-        </is>
-      </c>
-      <c r="F52" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:7</t>
+        </is>
+      </c>
+      <c r="F52" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G52" s="10">
         <v>85.0</v>
       </c>
       <c r="H52" t="s" s="10">
-        <v>148</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="11">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="B53" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C53" t="s" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D53" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 48. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 7. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:48</t>
-        </is>
-      </c>
-      <c r="F53" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:7</t>
+        </is>
+      </c>
+      <c r="F53" t="s" s="5">
+        <v>56</v>
       </c>
       <c r="G53" s="11">
         <v>85.0</v>
       </c>
       <c r="H53" t="s" s="11">
-        <v>150</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="10">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C54" t="s" s="0">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D54" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 50. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 43. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:50</t>
-        </is>
-      </c>
-      <c r="F54" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:43</t>
+        </is>
+      </c>
+      <c r="F54" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G54" s="10">
         <v>85.0</v>
       </c>
       <c r="H54" t="s" s="10">
-        <v>152</v>
+        <v>135</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="11">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="B55" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C55" t="s" s="4">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="D55" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 54. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 48. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:54</t>
-        </is>
-      </c>
-      <c r="F55" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:48</t>
+        </is>
+      </c>
+      <c r="F55" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G55" s="11">
         <v>85.0</v>
       </c>
       <c r="H55" t="s" s="11">
-        <v>154</v>
+        <v>137</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="10">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C56" t="s" s="0">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="D56" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 57. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 50. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:57</t>
-        </is>
-      </c>
-      <c r="F56" t="s" s="5">
-        <v>69</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:50</t>
+        </is>
+      </c>
+      <c r="F56" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G56" s="10">
         <v>85.0</v>
       </c>
       <c r="H56" t="s" s="10">
-        <v>156</v>
+        <v>139</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="11">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="B57" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C57" t="s" s="4">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D57" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 54. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:61</t>
-        </is>
-      </c>
-      <c r="F57" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:54</t>
+        </is>
+      </c>
+      <c r="F57" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G57" s="11">
         <v>85.0</v>
       </c>
       <c r="H57" t="s" s="11">
-        <v>158</v>
+        <v>141</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="10">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C58" t="s" s="0">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D58" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 57. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:61</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:57</t>
         </is>
       </c>
       <c r="F58" t="s" s="5">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G58" s="10">
         <v>85.0</v>
       </c>
       <c r="H58" t="s" s="10">
-        <v>160</v>
+        <v>143</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="11">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="B59" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C59" t="s" s="4">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="D59" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'license_scanner.py' at line 64. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:64</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:61</t>
         </is>
       </c>
       <c r="F59" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G59" s="11">
         <v>85.0</v>
       </c>
       <c r="H59" t="s" s="11">
-        <v>162</v>
+        <v>145</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="10">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C60" t="s" s="0">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D60" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'license_scanner.py' at line 65. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'license_scanner.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:65</t>
-        </is>
-      </c>
-      <c r="F60" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:61</t>
+        </is>
+      </c>
+      <c r="F60" t="s" s="5">
+        <v>56</v>
       </c>
       <c r="G60" s="10">
         <v>85.0</v>
       </c>
       <c r="H60" t="s" s="10">
-        <v>164</v>
+        <v>147</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="11">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="B61" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C61" t="s" s="4">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D61" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 71. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'license_scanner.py' at line 64. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:71</t>
-        </is>
-      </c>
-      <c r="F61" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:64</t>
+        </is>
+      </c>
+      <c r="F61" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G61" s="11">
         <v>85.0</v>
       </c>
       <c r="H61" t="s" s="11">
-        <v>166</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="10">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C62" t="s" s="0">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D62" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 75. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'license_scanner.py' at line 65. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:75</t>
-        </is>
-      </c>
-      <c r="F62" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:65</t>
+        </is>
+      </c>
+      <c r="F62" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G62" s="10">
         <v>85.0</v>
       </c>
       <c r="H62" t="s" s="10">
-        <v>168</v>
+        <v>151</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="11">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="B63" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C63" t="s" s="4">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D63" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 82. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 71. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:82</t>
-        </is>
-      </c>
-      <c r="F63" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:71</t>
+        </is>
+      </c>
+      <c r="F63" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G63" s="11">
         <v>85.0</v>
       </c>
       <c r="H63" t="s" s="11">
-        <v>170</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="10">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="B64" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C64" t="s" s="0">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D64" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 83. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'license_scanner.py' at line 75. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:83</t>
-        </is>
-      </c>
-      <c r="F64" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:75</t>
+        </is>
+      </c>
+      <c r="F64" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G64" s="10">
         <v>85.0</v>
       </c>
       <c r="H64" t="s" s="10">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="11">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="B65" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C65" t="s" s="4">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D65" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 84. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 82. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:84</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:82</t>
         </is>
       </c>
       <c r="F65" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G65" s="11">
         <v>85.0</v>
       </c>
       <c r="H65" t="s" s="11">
-        <v>174</v>
+        <v>157</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="10">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C66" t="s" s="0">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D66" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 85. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 83. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:85</t>
-        </is>
-      </c>
-      <c r="F66" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:83</t>
+        </is>
+      </c>
+      <c r="F66" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G66" s="10">
         <v>85.0</v>
       </c>
       <c r="H66" t="s" s="10">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="11">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="B67" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C67" t="s" s="4">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D67" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 86. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 84. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/scanner/modules/license_scanner.py:86</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:84</t>
         </is>
       </c>
       <c r="F67" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G67" s="11">
         <v>85.0</v>
       </c>
       <c r="H67" t="s" s="11">
-        <v>178</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="10">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C68" t="s" s="0">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="D68" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'license_scanner.py' at line 85. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner.py:21</t>
-        </is>
-      </c>
-      <c r="F68" t="s" s="5">
-        <v>69</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:85</t>
+        </is>
+      </c>
+      <c r="F68" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G68" s="10">
         <v>85.0</v>
       </c>
       <c r="H68" t="s" s="10">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="11">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="B69" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C69" t="s" s="4">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="D69" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 23. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'license_scanner.py' at line 86. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner.py:23</t>
-        </is>
-      </c>
-      <c r="F69" t="s" s="5">
-        <v>69</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/scanner/modules/license_scanner.py:86</t>
+        </is>
+      </c>
+      <c r="F69" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G69" s="11">
         <v>85.0</v>
       </c>
       <c r="H69" t="s" s="11">
-        <v>182</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="10">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="B70" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C70" t="s" s="0">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D70" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 34. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 21. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner.py:34</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:21</t>
         </is>
       </c>
       <c r="F70" t="s" s="5">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G70" s="10">
         <v>85.0</v>
       </c>
       <c r="H70" t="s" s="10">
-        <v>184</v>
+        <v>167</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="11">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="B71" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C71" t="s" s="4">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D71" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 39. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 23. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner.py:39</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:23</t>
         </is>
       </c>
       <c r="F71" t="s" s="5">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G71" s="11">
         <v>85.0</v>
       </c>
       <c r="H71" t="s" s="11">
-        <v>186</v>
+        <v>169</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="10">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C72" t="s" s="0">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D72" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 40. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 34. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner.py:40</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:34</t>
         </is>
       </c>
       <c r="F72" t="s" s="5">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G72" s="10">
         <v>85.0</v>
       </c>
       <c r="H72" t="s" s="10">
-        <v>188</v>
+        <v>171</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="11">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="B73" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C73" t="s" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D73" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 39. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner.py:47</t>
-        </is>
-      </c>
-      <c r="F73" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:39</t>
+        </is>
+      </c>
+      <c r="F73" t="s" s="5">
+        <v>56</v>
       </c>
       <c r="G73" s="11">
         <v>85.0</v>
       </c>
       <c r="H73" t="s" s="11">
-        <v>190</v>
+        <v>173</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="10">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="B74" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C74" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D74" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 40. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner.py:61</t>
-        </is>
-      </c>
-      <c r="F74" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:40</t>
+        </is>
+      </c>
+      <c r="F74" t="s" s="5">
+        <v>56</v>
       </c>
       <c r="G74" s="10">
         <v>85.0</v>
       </c>
       <c r="H74" t="s" s="10">
-        <v>192</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="11">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="B75" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C75" t="s" s="4">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D75" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 62. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner.py:62</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:47</t>
         </is>
       </c>
       <c r="F75" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G75" s="11">
         <v>85.0</v>
       </c>
       <c r="H75" t="s" s="11">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="10">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="B76" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C76" t="s" s="0">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D76" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 70. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner.py:70</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:61</t>
         </is>
       </c>
       <c r="F76" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G76" s="10">
         <v>85.0</v>
       </c>
       <c r="H76" t="s" s="10">
-        <v>196</v>
+        <v>179</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="11">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="B77" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C77" t="s" s="4">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="D77" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 100. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 62. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner.py:100</t>
-        </is>
-      </c>
-      <c r="F77" t="s" s="5">
-        <v>69</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:62</t>
+        </is>
+      </c>
+      <c r="F77" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G77" s="11">
         <v>85.0</v>
       </c>
       <c r="H77" t="s" s="11">
-        <v>198</v>
+        <v>181</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="10">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="B78" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C78" t="s" s="0">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="D78" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 112. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner.py' at line 70. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner.py:112</t>
-        </is>
-      </c>
-      <c r="F78" t="s" s="5">
-        <v>69</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:70</t>
+        </is>
+      </c>
+      <c r="F78" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G78" s="10">
         <v>85.0</v>
       </c>
       <c r="H78" t="s" s="10">
-        <v>200</v>
+        <v>183</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="11">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="B79" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C79" t="s" s="4">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D79" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 113. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 100. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner.py:113</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:100</t>
         </is>
       </c>
       <c r="F79" t="s" s="5">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G79" s="11">
         <v>85.0</v>
       </c>
       <c r="H79" t="s" s="11">
-        <v>202</v>
+        <v>185</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="10">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C80" t="s" s="0">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D80" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 112. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:19</t>
-        </is>
-      </c>
-      <c r="F80" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:112</t>
+        </is>
+      </c>
+      <c r="F80" t="s" s="5">
+        <v>56</v>
       </c>
       <c r="G80" s="10">
         <v>85.0</v>
       </c>
       <c r="H80" t="s" s="10">
-        <v>204</v>
+        <v>187</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="11">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="B81" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C81" t="s" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D81" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner.py' at line 113. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:19</t>
-        </is>
-      </c>
-      <c r="F81" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner.py:113</t>
+        </is>
+      </c>
+      <c r="F81" t="s" s="5">
+        <v>56</v>
       </c>
       <c r="G81" s="11">
         <v>85.0</v>
       </c>
       <c r="H81" t="s" s="11">
-        <v>206</v>
+        <v>189</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="10">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="B82" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C82" t="s" s="0">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="D82" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:19</t>
-        </is>
-      </c>
-      <c r="F82" t="s" s="5">
-        <v>69</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+        </is>
+      </c>
+      <c r="F82" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G82" s="10">
         <v>85.0</v>
       </c>
       <c r="H82" t="s" s="10">
-        <v>208</v>
+        <v>191</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="11">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="B83" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C83" t="s" s="4">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="D83" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
         </is>
       </c>
       <c r="F83" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G83" s="11">
         <v>85.0</v>
       </c>
       <c r="H83" t="s" s="11">
-        <v>210</v>
+        <v>193</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="10">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="B84" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C84" t="s" s="0">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D84" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:19</t>
-        </is>
-      </c>
-      <c r="F84" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+        </is>
+      </c>
+      <c r="F84" t="s" s="5">
+        <v>56</v>
       </c>
       <c r="G84" s="10">
         <v>85.0</v>
       </c>
       <c r="H84" t="s" s="10">
-        <v>212</v>
+        <v>195</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="11">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="B85" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C85" t="s" s="4">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D85" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 30. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:30</t>
-        </is>
-      </c>
-      <c r="F85" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
+        </is>
+      </c>
+      <c r="F85" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G85" s="11">
         <v>85.0</v>
       </c>
       <c r="H85" t="s" s="11">
-        <v>214</v>
+        <v>197</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="10">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="B86" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C86" t="s" s="0">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D86" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 31. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 19. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:31</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:19</t>
         </is>
       </c>
       <c r="F86" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G86" s="10">
         <v>85.0</v>
       </c>
       <c r="H86" t="s" s="10">
-        <v>216</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="11">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="B87" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C87" t="s" s="4">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D87" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 32. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 30. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:32</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:30</t>
         </is>
       </c>
       <c r="F87" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G87" s="11">
         <v>85.0</v>
       </c>
       <c r="H87" t="s" s="11">
-        <v>218</v>
+        <v>201</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="10">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="B88" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C88" t="s" s="0">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D88" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 34. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 31. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:34</t>
-        </is>
-      </c>
-      <c r="F88" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:31</t>
+        </is>
+      </c>
+      <c r="F88" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G88" s="10">
         <v>85.0</v>
       </c>
       <c r="H88" t="s" s="10">
-        <v>220</v>
+        <v>203</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="11">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="B89" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C89" t="s" s="4">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D89" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 32. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:35</t>
-        </is>
-      </c>
-      <c r="F89" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:32</t>
+        </is>
+      </c>
+      <c r="F89" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G89" s="11">
         <v>85.0</v>
       </c>
       <c r="H89" t="s" s="11">
-        <v>222</v>
+        <v>205</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="10">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="B90" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C90" t="s" s="0">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D90" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 36. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 34. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:36</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:34</t>
         </is>
       </c>
       <c r="F90" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G90" s="10">
         <v>85.0</v>
       </c>
       <c r="H90" t="s" s="10">
-        <v>224</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="11">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="B91" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C91" t="s" s="4">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="D91" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 38. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 35. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:38</t>
-        </is>
-      </c>
-      <c r="F91" t="s" s="5">
-        <v>69</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:35</t>
+        </is>
+      </c>
+      <c r="F91" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G91" s="11">
         <v>85.0</v>
       </c>
       <c r="H91" t="s" s="11">
-        <v>226</v>
+        <v>209</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="10">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="B92" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C92" t="s" s="0">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="D92" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 39. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 36. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:39</t>
-        </is>
-      </c>
-      <c r="F92" t="s" s="5">
-        <v>69</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:36</t>
+        </is>
+      </c>
+      <c r="F92" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G92" s="10">
         <v>85.0</v>
       </c>
       <c r="H92" t="s" s="10">
-        <v>228</v>
+        <v>211</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="11">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="B93" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C93" t="s" s="4">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D93" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 40. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 38. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:40</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:38</t>
         </is>
       </c>
       <c r="F93" t="s" s="5">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G93" s="11">
         <v>85.0</v>
       </c>
       <c r="H93" t="s" s="11">
-        <v>230</v>
+        <v>213</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="10">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="B94" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C94" t="s" s="0">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D94" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 42. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 39. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:42</t>
-        </is>
-      </c>
-      <c r="F94" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:39</t>
+        </is>
+      </c>
+      <c r="F94" t="s" s="5">
+        <v>56</v>
       </c>
       <c r="G94" s="10">
         <v>85.0</v>
       </c>
       <c r="H94" t="s" s="10">
-        <v>232</v>
+        <v>215</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="11">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="B95" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C95" t="s" s="4">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D95" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 43. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'AGPL' detected inline in 'test_license_scanner_tasks.py' at line 40. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:43</t>
-        </is>
-      </c>
-      <c r="F95" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:40</t>
+        </is>
+      </c>
+      <c r="F95" t="s" s="5">
+        <v>56</v>
       </c>
       <c r="G95" s="11">
         <v>85.0</v>
       </c>
       <c r="H95" t="s" s="11">
-        <v>234</v>
+        <v>217</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="10">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="B96" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C96" t="s" s="0">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D96" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 44. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 42. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:44</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:42</t>
         </is>
       </c>
       <c r="F96" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G96" s="10">
         <v>85.0</v>
       </c>
       <c r="H96" t="s" s="10">
-        <v>236</v>
+        <v>219</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="11">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="B97" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C97" t="s" s="4">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D97" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 46. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 43. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:46</t>
-        </is>
-      </c>
-      <c r="F97" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:43</t>
+        </is>
+      </c>
+      <c r="F97" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G97" s="11">
         <v>85.0</v>
       </c>
       <c r="H97" t="s" s="11">
-        <v>238</v>
+        <v>221</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="10">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="B98" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C98" t="s" s="0">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D98" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Polyform Shield' detected inline in 'test_license_scanner_tasks.py' at line 44. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:47</t>
-        </is>
-      </c>
-      <c r="F98" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:44</t>
+        </is>
+      </c>
+      <c r="F98" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G98" s="10">
         <v>85.0</v>
       </c>
       <c r="H98" t="s" s="10">
-        <v>240</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="11">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="B99" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C99" t="s" s="4">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D99" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 48. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 46. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:48</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:46</t>
         </is>
       </c>
       <c r="F99" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G99" s="11">
         <v>85.0</v>
       </c>
       <c r="H99" t="s" s="11">
-        <v>242</v>
+        <v>225</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="10">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="B100" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C100" t="s" s="0">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D100" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 57. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 47. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:57</t>
-        </is>
-      </c>
-      <c r="F100" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:47</t>
+        </is>
+      </c>
+      <c r="F100" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G100" s="10">
         <v>85.0</v>
       </c>
       <c r="H100" t="s" s="10">
-        <v>244</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="11">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="B101" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C101" t="s" s="4">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D101" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 60. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 48. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:60</t>
-        </is>
-      </c>
-      <c r="F101" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:48</t>
+        </is>
+      </c>
+      <c r="F101" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G101" s="11">
         <v>85.0</v>
       </c>
       <c r="H101" t="s" s="11">
-        <v>246</v>
+        <v>229</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="10">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="B102" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C102" t="s" s="0">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="D102" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 57. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:61</t>
-        </is>
-      </c>
-      <c r="F102" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:57</t>
+        </is>
+      </c>
+      <c r="F102" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G102" s="10">
         <v>85.0</v>
       </c>
       <c r="H102" t="s" s="10">
-        <v>248</v>
+        <v>231</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="11">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="B103" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C103" t="s" s="4">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D103" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 71. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 60. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:71</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:60</t>
         </is>
       </c>
       <c r="F103" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G103" s="11">
         <v>85.0</v>
       </c>
       <c r="H103" t="s" s="11">
-        <v>250</v>
+        <v>233</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="10">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="B104" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C104" t="s" s="0">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D104" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 72. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'Proprietary' detected inline in 'test_license_scanner_tasks.py' at line 61. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:72</t>
-        </is>
-      </c>
-      <c r="F104" t="s" s="6">
-        <v>37</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:61</t>
+        </is>
+      </c>
+      <c r="F104" t="s" s="7">
+        <v>45</v>
       </c>
       <c r="G104" s="10">
         <v>85.0</v>
       </c>
       <c r="H104" t="s" s="10">
-        <v>252</v>
+        <v>235</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="11">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="B105" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C105" t="s" s="4">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D105" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 73. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 71. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:73</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:71</t>
         </is>
       </c>
       <c r="F105" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G105" s="11">
         <v>85.0</v>
       </c>
       <c r="H105" t="s" s="11">
-        <v>254</v>
+        <v>237</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="10">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="B106" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C106" t="s" s="0">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D106" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 79. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 72. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:79</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:72</t>
         </is>
       </c>
       <c r="F106" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G106" s="10">
         <v>85.0</v>
       </c>
       <c r="H106" t="s" s="10">
-        <v>256</v>
+        <v>239</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="11">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="B107" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C107" t="s" s="4">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D107" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 101. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 73. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:101</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:73</t>
         </is>
       </c>
       <c r="F107" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G107" s="11">
         <v>85.0</v>
       </c>
       <c r="H107" t="s" s="11">
-        <v>258</v>
+        <v>241</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="10">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="B108" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C108" t="s" s="0">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D108" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 105. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 79. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:105</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:79</t>
         </is>
       </c>
       <c r="F108" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G108" s="10">
         <v>85.0</v>
       </c>
       <c r="H108" t="s" s="10">
-        <v>260</v>
+        <v>243</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="11">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="B109" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C109" t="s" s="4">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D109" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 109. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 101. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:109</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:101</t>
         </is>
       </c>
       <c r="F109" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G109" s="11">
         <v>85.0</v>
       </c>
       <c r="H109" t="s" s="11">
-        <v>262</v>
+        <v>245</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="10">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="B110" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C110" t="s" s="0">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D110" t="inlineStr" s="14">
         <is>
-          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 113. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 105. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:113</t>
-        </is>
-      </c>
-      <c r="F110" t="s" s="7">
-        <v>58</v>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:105</t>
+        </is>
+      </c>
+      <c r="F110" t="s" s="6">
+        <v>21</v>
       </c>
       <c r="G110" s="10">
         <v>85.0</v>
       </c>
       <c r="H110" t="s" s="10">
-        <v>264</v>
+        <v>247</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="11">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="B111" t="s" s="4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C111" t="s" s="4">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D111" t="inlineStr" s="15">
         <is>
-          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 117. This may indicate an inadvertently copied AI snippet.</t>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 109. This may indicate an inadvertently copied AI snippet.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_license_scanner_tasks.py:117</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:109</t>
         </is>
       </c>
       <c r="F111" t="s" s="6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G111" s="11">
         <v>85.0</v>
       </c>
       <c r="H111" t="s" s="11">
-        <v>266</v>
+        <v>249</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="10">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="B112" t="s" s="0">
-        <v>268</v>
+        <v>40</v>
       </c>
       <c r="C112" t="s" s="0">
-        <v>269</v>
+        <v>44</v>
       </c>
       <c r="D112" t="inlineStr" s="14">
         <is>
+          <t>Possible copyleft / restrictive license signature 'LGPL' detected inline in 'test_license_scanner_tasks.py' at line 113. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr" s="14">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:113</t>
+        </is>
+      </c>
+      <c r="F112" t="s" s="7">
+        <v>45</v>
+      </c>
+      <c r="G112" s="10">
+        <v>85.0</v>
+      </c>
+      <c r="H112" t="s" s="10">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="11">
+        <v>252</v>
+      </c>
+      <c r="B113" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="C113" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="D113" t="inlineStr" s="15">
+        <is>
+          <t>Possible copyleft / restrictive license signature 'GPL' detected inline in 'test_license_scanner_tasks.py' at line 117. This may indicate an inadvertently copied AI snippet.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr" s="15">
+        <is>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_license_scanner_tasks.py:117</t>
+        </is>
+      </c>
+      <c r="F113" t="s" s="6">
+        <v>21</v>
+      </c>
+      <c r="G113" s="11">
+        <v>85.0</v>
+      </c>
+      <c r="H113" t="s" s="11">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="10">
+        <v>254</v>
+      </c>
+      <c r="B114" t="s" s="0">
+        <v>255</v>
+      </c>
+      <c r="C114" t="s" s="0">
+        <v>256</v>
+      </c>
+      <c r="D114" t="inlineStr" s="14">
+        <is>
           <t>The primary audit log (ai_scanner.log) is missing. CERT-In mandates active logging for incident readiness and forensic timelines.</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr" s="14">
+      <c r="E114" t="inlineStr" s="14">
         <is>
           <t>ai_scanner.log</t>
         </is>
       </c>
-      <c r="F112" t="s" s="6">
-        <v>37</v>
-      </c>
-      <c r="G112" s="10">
+      <c r="F114" t="s" s="6">
+        <v>21</v>
+      </c>
+      <c r="G114" s="10">
         <v>90.0</v>
       </c>
-      <c r="H112" t="s" s="10">
-        <v>270</v>
+      <c r="H114" t="s" s="10">
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -4877,16 +4709,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>3</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="G1" t="s" s="1">
         <v>5</v>
@@ -4900,13 +4732,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="10">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="D2" t="inlineStr" s="14">
         <is>
@@ -4914,7 +4746,7 @@
         </is>
       </c>
       <c r="E2" t="s" s="10">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="F2" t="inlineStr" s="14">
         <is>
@@ -4922,65 +4754,65 @@
         </is>
       </c>
       <c r="G2" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H2" s="10">
         <v>85.0</v>
       </c>
       <c r="I2" t="s" s="10">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="11">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="B3" t="s" s="4">
-        <v>279</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s" s="4">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="D3" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 1280) is running as a background process.</t>
+          <t>Codex registry entries were found on this system. This indicates it is installed or its AppX package is registered.</t>
         </is>
       </c>
       <c r="E3" t="s" s="11">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="F3" t="inlineStr" s="15">
         <is>
-          <t>Antigravity IDE.exe</t>
+          <t>registry:AppXStore</t>
         </is>
       </c>
       <c r="G3" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H3" s="11">
-        <v>90.0</v>
+        <v>85.0</v>
       </c>
       <c r="I3" t="s" s="11">
-        <v>282</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="10">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="D4" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 2184) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 3016) is running as a background process.</t>
         </is>
       </c>
       <c r="E4" t="s" s="10">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F4" t="inlineStr" s="14">
         <is>
@@ -4988,32 +4820,32 @@
         </is>
       </c>
       <c r="G4" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H4" s="10">
         <v>90.0</v>
       </c>
       <c r="I4" t="s" s="10">
-        <v>285</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="11">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="B5" t="s" s="4">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C5" t="s" s="4">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D5" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 2624) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 7676) is running as a background process.</t>
         </is>
       </c>
       <c r="E5" t="s" s="11">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F5" t="inlineStr" s="15">
         <is>
@@ -5021,32 +4853,32 @@
         </is>
       </c>
       <c r="G5" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H5" s="11">
         <v>90.0</v>
       </c>
       <c r="I5" t="s" s="11">
-        <v>288</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="10">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="D6" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 7692) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 10244) is running as a background process.</t>
         </is>
       </c>
       <c r="E6" t="s" s="10">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F6" t="inlineStr" s="14">
         <is>
@@ -5054,32 +4886,32 @@
         </is>
       </c>
       <c r="G6" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H6" s="10">
         <v>90.0</v>
       </c>
       <c r="I6" t="s" s="10">
-        <v>291</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="11">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="B7" t="s" s="4">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C7" t="s" s="4">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="D7" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 8564) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 10364) is running as a background process.</t>
         </is>
       </c>
       <c r="E7" t="s" s="11">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F7" t="inlineStr" s="15">
         <is>
@@ -5087,32 +4919,32 @@
         </is>
       </c>
       <c r="G7" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H7" s="11">
         <v>90.0</v>
       </c>
       <c r="I7" t="s" s="11">
-        <v>294</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="10">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="D8" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 11944) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 10436) is running as a background process.</t>
         </is>
       </c>
       <c r="E8" t="s" s="10">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F8" t="inlineStr" s="14">
         <is>
@@ -5120,32 +4952,32 @@
         </is>
       </c>
       <c r="G8" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H8" s="10">
         <v>90.0</v>
       </c>
       <c r="I8" t="s" s="10">
-        <v>297</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="11">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="B9" t="s" s="4">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C9" t="s" s="4">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="D9" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 12452) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 12500) is running as a background process.</t>
         </is>
       </c>
       <c r="E9" t="s" s="11">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F9" t="inlineStr" s="15">
         <is>
@@ -5153,32 +4985,32 @@
         </is>
       </c>
       <c r="G9" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H9" s="11">
         <v>90.0</v>
       </c>
       <c r="I9" t="s" s="11">
-        <v>300</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="10">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="D10" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 14524) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 13260) is running as a background process.</t>
         </is>
       </c>
       <c r="E10" t="s" s="10">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F10" t="inlineStr" s="14">
         <is>
@@ -5186,32 +5018,32 @@
         </is>
       </c>
       <c r="G10" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H10" s="10">
         <v>90.0</v>
       </c>
       <c r="I10" t="s" s="10">
-        <v>303</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="11">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="B11" t="s" s="4">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C11" t="s" s="4">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="D11" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 15920) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 15588) is running as a background process.</t>
         </is>
       </c>
       <c r="E11" t="s" s="11">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F11" t="inlineStr" s="15">
         <is>
@@ -5219,32 +5051,32 @@
         </is>
       </c>
       <c r="G11" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H11" s="11">
         <v>90.0</v>
       </c>
       <c r="I11" t="s" s="11">
-        <v>306</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="10">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="D12" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 17208) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 15772) is running as a background process.</t>
         </is>
       </c>
       <c r="E12" t="s" s="10">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F12" t="inlineStr" s="14">
         <is>
@@ -5252,32 +5084,32 @@
         </is>
       </c>
       <c r="G12" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H12" s="10">
         <v>90.0</v>
       </c>
       <c r="I12" t="s" s="10">
-        <v>309</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="11">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="B13" t="s" s="4">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C13" t="s" s="4">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="D13" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 18680) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 16456) is running as a background process.</t>
         </is>
       </c>
       <c r="E13" t="s" s="11">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F13" t="inlineStr" s="15">
         <is>
@@ -5285,32 +5117,32 @@
         </is>
       </c>
       <c r="G13" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H13" s="11">
         <v>90.0</v>
       </c>
       <c r="I13" t="s" s="11">
-        <v>312</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="10">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="D14" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 18776) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 17760) is running as a background process.</t>
         </is>
       </c>
       <c r="E14" t="s" s="10">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F14" t="inlineStr" s="14">
         <is>
@@ -5318,32 +5150,32 @@
         </is>
       </c>
       <c r="G14" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H14" s="10">
         <v>90.0</v>
       </c>
       <c r="I14" t="s" s="10">
-        <v>315</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="11">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="B15" t="s" s="4">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C15" t="s" s="4">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="D15" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 19064) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 18604) is running as a background process.</t>
         </is>
       </c>
       <c r="E15" t="s" s="11">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F15" t="inlineStr" s="15">
         <is>
@@ -5351,32 +5183,32 @@
         </is>
       </c>
       <c r="G15" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H15" s="11">
         <v>90.0</v>
       </c>
       <c r="I15" t="s" s="11">
-        <v>318</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="10">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="D16" t="inlineStr" s="14">
         <is>
-          <t>AI daemon detected: Antigravity (PID 19248) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 19448) is running as a background process.</t>
         </is>
       </c>
       <c r="E16" t="s" s="10">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F16" t="inlineStr" s="14">
         <is>
@@ -5384,32 +5216,32 @@
         </is>
       </c>
       <c r="G16" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H16" s="10">
         <v>90.0</v>
       </c>
       <c r="I16" t="s" s="10">
-        <v>321</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="11">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="B17" t="s" s="4">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C17" t="s" s="4">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="D17" t="inlineStr" s="15">
         <is>
-          <t>AI daemon detected: Antigravity (PID 21464) is running as a background process.</t>
+          <t>AI daemon detected: Antigravity (PID 20424) is running as a background process.</t>
         </is>
       </c>
       <c r="E17" t="s" s="11">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F17" t="inlineStr" s="15">
         <is>
@@ -5417,24 +5249,24 @@
         </is>
       </c>
       <c r="G17" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H17" s="11">
         <v>90.0</v>
       </c>
       <c r="I17" t="s" s="11">
-        <v>324</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="10">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="D18" t="inlineStr" s="14">
         <is>
@@ -5442,32 +5274,32 @@
         </is>
       </c>
       <c r="E18" t="s" s="10">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="F18" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_agent_scanner.py:25</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:25</t>
         </is>
       </c>
       <c r="G18" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H18" s="10">
         <v>85.0</v>
       </c>
       <c r="I18" t="s" s="10">
-        <v>328</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="11">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="B19" t="s" s="4">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="C19" t="s" s="4">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="D19" t="inlineStr" s="15">
         <is>
@@ -5475,32 +5307,32 @@
         </is>
       </c>
       <c r="E19" t="s" s="11">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="F19" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_agent_scanner.py:26</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:26</t>
         </is>
       </c>
       <c r="G19" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H19" s="11">
         <v>85.0</v>
       </c>
       <c r="I19" t="s" s="11">
-        <v>331</v>
+        <v>318</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="10">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="D20" t="inlineStr" s="14">
         <is>
@@ -5508,32 +5340,32 @@
         </is>
       </c>
       <c r="E20" t="s" s="10">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="F20" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_agent_scanner.py:30</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:30</t>
         </is>
       </c>
       <c r="G20" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H20" s="10">
         <v>85.0</v>
       </c>
       <c r="I20" t="s" s="10">
-        <v>334</v>
+        <v>321</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="11">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="B21" t="s" s="4">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="C21" t="s" s="4">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="D21" t="inlineStr" s="15">
         <is>
@@ -5541,65 +5373,65 @@
         </is>
       </c>
       <c r="E21" t="s" s="11">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="F21" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_agent_scanner.py:31</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:31</t>
         </is>
       </c>
       <c r="G21" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H21" s="11">
         <v>85.0</v>
       </c>
       <c r="I21" t="s" s="11">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="10">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="B22" t="s" s="0">
+        <v>313</v>
+      </c>
+      <c r="C22" t="s" s="0">
         <v>326</v>
       </c>
-      <c r="C22" t="s" s="0">
-        <v>339</v>
-      </c>
       <c r="D22" t="inlineStr" s="14">
         <is>
           <t>Potential AI Agent signature detected in script 'test_agent_scanner.py' at line 32 (AssistantAgent Instantiation).</t>
         </is>
       </c>
       <c r="E22" t="s" s="10">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="F22" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_agent_scanner.py:32</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:32</t>
         </is>
       </c>
       <c r="G22" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H22" s="10">
         <v>85.0</v>
       </c>
       <c r="I22" t="s" s="10">
-        <v>340</v>
+        <v>327</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="11">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="B23" t="s" s="4">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="C23" t="s" s="4">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="D23" t="inlineStr" s="15">
         <is>
@@ -5607,32 +5439,32 @@
         </is>
       </c>
       <c r="E23" t="s" s="11">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="F23" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_agent_scanner.py:81</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:81</t>
         </is>
       </c>
       <c r="G23" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H23" s="11">
         <v>85.0</v>
       </c>
       <c r="I23" t="s" s="11">
-        <v>342</v>
+        <v>329</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="10">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="D24" t="inlineStr" s="14">
         <is>
@@ -5640,32 +5472,32 @@
         </is>
       </c>
       <c r="E24" t="s" s="10">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="F24" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_agent_scanner.py:82</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:82</t>
         </is>
       </c>
       <c r="G24" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H24" s="10">
         <v>85.0</v>
       </c>
       <c r="I24" t="s" s="10">
-        <v>344</v>
+        <v>331</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="11">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="B25" t="s" s="4">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="C25" t="s" s="4">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="D25" t="inlineStr" s="15">
         <is>
@@ -5673,32 +5505,32 @@
         </is>
       </c>
       <c r="E25" t="s" s="11">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="F25" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_agent_scanner.py:87</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:87</t>
         </is>
       </c>
       <c r="G25" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H25" s="11">
         <v>85.0</v>
       </c>
       <c r="I25" t="s" s="11">
-        <v>346</v>
+        <v>333</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="10">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="D26" t="inlineStr" s="14">
         <is>
@@ -5706,32 +5538,32 @@
         </is>
       </c>
       <c r="E26" t="s" s="10">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="F26" t="inlineStr" s="14">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_agent_scanner.py:92</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_agent_scanner.py:92</t>
         </is>
       </c>
       <c r="G26" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H26" s="10">
         <v>85.0</v>
       </c>
       <c r="I26" t="s" s="10">
-        <v>348</v>
+        <v>335</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="11">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="B27" t="s" s="4">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="C27" t="s" s="4">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="D27" t="inlineStr" s="15">
         <is>
@@ -5739,87 +5571,54 @@
         </is>
       </c>
       <c r="E27" t="s" s="11">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="F27" t="inlineStr" s="15">
         <is>
-          <t>C:/Users/ADMIN/OneDrive/Desktop/AI scanner/Group-A-Y-S/System Scanner/tests/test_classifier.py:103</t>
+          <t>D:/College Work/Internship/Group A-Y-S/System Scanner/System Scanner/tests/test_classifier.py:103</t>
         </is>
       </c>
       <c r="G27" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H27" s="11">
         <v>85.0</v>
       </c>
       <c r="I27" t="s" s="11">
-        <v>350</v>
+        <v>337</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="10">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="D28" t="inlineStr" s="14">
         <is>
-          <t>Ollama local storage directory (~/.ollama) was found, but no active process is currently listening on port 11434.</t>
+          <t>An active service was detected listening on port 8080 (llama.cpp / LocalAI Server). This port is commonly used by local LLM APIs, services, or model servers.</t>
         </is>
       </c>
       <c r="E28" t="s" s="10">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F28" t="inlineStr" s="14">
         <is>
-          <t>ollama</t>
+          <t>127.0.0.1:8080</t>
         </is>
       </c>
       <c r="G28" t="s" s="7">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H28" s="10">
         <v>90.0</v>
       </c>
       <c r="I28" t="s" s="10">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="11">
-        <v>355</v>
-      </c>
-      <c r="B29" t="s" s="4">
-        <v>352</v>
-      </c>
-      <c r="C29" t="s" s="4">
-        <v>356</v>
-      </c>
-      <c r="D29" t="inlineStr" s="15">
-        <is>
-          <t>An active service was detected listening on port 8000 (vLLM / LocalAI / LiteLLM). This port is commonly used by local LLM APIs, services, or model servers.</t>
-        </is>
-      </c>
-      <c r="E29" t="s" s="11">
-        <v>281</v>
-      </c>
-      <c r="F29" t="inlineStr" s="15">
-        <is>
-          <t>127.0.0.1:8000</t>
-        </is>
-      </c>
-      <c r="G29" t="s" s="7">
-        <v>58</v>
-      </c>
-      <c r="H29" s="11">
-        <v>90.0</v>
-      </c>
-      <c r="I29" t="s" s="11">
-        <v>357</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
